--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877339</v>
+        <v>125877271</v>
       </c>
       <c r="B2" t="n">
-        <v>105348</v>
+        <v>80070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540959</v>
+        <v>540996</v>
       </c>
       <c r="R2" t="n">
-        <v>6964030</v>
+        <v>6964140</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877304</v>
+        <v>125877332</v>
       </c>
       <c r="B3" t="n">
-        <v>56834</v>
+        <v>98230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540740</v>
+        <v>540794</v>
       </c>
       <c r="R3" t="n">
-        <v>6964067</v>
+        <v>6964056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877296</v>
+        <v>125877322</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540787</v>
+        <v>540809</v>
       </c>
       <c r="R4" t="n">
-        <v>6964017</v>
+        <v>6964096</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877300</v>
+        <v>125877310</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>98230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540937</v>
+        <v>540890</v>
       </c>
       <c r="R5" t="n">
-        <v>6964110</v>
+        <v>6964145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877332</v>
+        <v>125877296</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540794</v>
+        <v>540787</v>
       </c>
       <c r="R6" t="n">
-        <v>6964056</v>
+        <v>6964017</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877322</v>
+        <v>125877300</v>
       </c>
       <c r="B7" t="n">
-        <v>98230</v>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540809</v>
+        <v>540937</v>
       </c>
       <c r="R7" t="n">
-        <v>6964096</v>
+        <v>6964110</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877310</v>
+        <v>125877304</v>
       </c>
       <c r="B8" t="n">
-        <v>98230</v>
+        <v>56834</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540890</v>
+        <v>540740</v>
       </c>
       <c r="R8" t="n">
-        <v>6964145</v>
+        <v>6964067</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877259</v>
+        <v>125877339</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>105348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540760</v>
+        <v>540959</v>
       </c>
       <c r="R9" t="n">
-        <v>6964020</v>
+        <v>6964030</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877271</v>
+        <v>125877259</v>
       </c>
       <c r="B10" t="n">
         <v>80070</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540996</v>
+        <v>540760</v>
       </c>
       <c r="R10" t="n">
-        <v>6964140</v>
+        <v>6964020</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877275</v>
+        <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>98230</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540780</v>
+        <v>540848</v>
       </c>
       <c r="R13" t="n">
-        <v>6963983</v>
+        <v>6964091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877277</v>
+        <v>125877275</v>
       </c>
       <c r="B14" t="n">
         <v>80070</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540786</v>
+        <v>540780</v>
       </c>
       <c r="R14" t="n">
-        <v>6963974</v>
+        <v>6963983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877264</v>
+        <v>125877277</v>
       </c>
       <c r="B15" t="n">
         <v>80070</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540828</v>
+        <v>540786</v>
       </c>
       <c r="R15" t="n">
-        <v>6964037</v>
+        <v>6963974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877315</v>
+        <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>98230</v>
+        <v>80070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540848</v>
+        <v>540828</v>
       </c>
       <c r="R16" t="n">
-        <v>6964091</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877240</v>
+        <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540848</v>
+        <v>540850</v>
       </c>
       <c r="R17" t="n">
-        <v>6964065</v>
+        <v>6964070</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877318</v>
+        <v>125877311</v>
       </c>
       <c r="B18" t="n">
         <v>98230</v>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540850</v>
+        <v>540889</v>
       </c>
       <c r="R18" t="n">
-        <v>6964070</v>
+        <v>6964139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877311</v>
+        <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98230</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540889</v>
+        <v>540848</v>
       </c>
       <c r="R19" t="n">
-        <v>6964139</v>
+        <v>6964065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877313</v>
+        <v>125877284</v>
       </c>
       <c r="B20" t="n">
-        <v>98230</v>
+        <v>80106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R20" t="n">
-        <v>6964119</v>
+        <v>6964031</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877284</v>
+        <v>125877260</v>
       </c>
       <c r="B21" t="n">
-        <v>80106</v>
+        <v>80070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540807</v>
+        <v>540800</v>
       </c>
       <c r="R21" t="n">
-        <v>6964031</v>
+        <v>6964021</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877260</v>
+        <v>125877313</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>98230</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540800</v>
+        <v>540882</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964119</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877298</v>
+        <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98324</v>
+        <v>98230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540912</v>
+        <v>540793</v>
       </c>
       <c r="R30" t="n">
-        <v>6964122</v>
+        <v>6964055</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,6 +3468,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3494,10 +3499,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877273</v>
+        <v>125877366</v>
       </c>
       <c r="B31" t="n">
-        <v>80070</v>
+        <v>88626</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3505,21 +3510,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540797</v>
+        <v>540874</v>
       </c>
       <c r="R31" t="n">
-        <v>6964057</v>
+        <v>6964114</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3591,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877266</v>
+        <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>80070</v>
+        <v>98230</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540868</v>
+        <v>540803</v>
       </c>
       <c r="R32" t="n">
-        <v>6964062</v>
+        <v>6964102</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3688,7 +3693,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877306</v>
+        <v>125877314</v>
       </c>
       <c r="B33" t="n">
         <v>98230</v>
@@ -3723,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540793</v>
+        <v>540853</v>
       </c>
       <c r="R33" t="n">
-        <v>6964055</v>
+        <v>6964095</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3759,11 +3764,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3790,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877366</v>
+        <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>88626</v>
+        <v>98230</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540874</v>
+        <v>540788</v>
       </c>
       <c r="R34" t="n">
-        <v>6964114</v>
+        <v>6964033</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877323</v>
+        <v>125877273</v>
       </c>
       <c r="B35" t="n">
-        <v>98230</v>
+        <v>80070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540803</v>
+        <v>540797</v>
       </c>
       <c r="R35" t="n">
-        <v>6964102</v>
+        <v>6964057</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,32 +3984,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877314</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
-        <v>98230</v>
+        <v>80070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540853</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964095</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877252</v>
+        <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98230</v>
+        <v>98324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540788</v>
+        <v>540912</v>
       </c>
       <c r="R37" t="n">
-        <v>6964033</v>
+        <v>6964122</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877307</v>
+        <v>125877267</v>
       </c>
       <c r="B41" t="n">
-        <v>98230</v>
+        <v>80070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540788</v>
+        <v>540893</v>
       </c>
       <c r="R41" t="n">
-        <v>6964042</v>
+        <v>6964069</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877267</v>
+        <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540893</v>
+        <v>540997</v>
       </c>
       <c r="R42" t="n">
-        <v>6964069</v>
+        <v>6964169</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877347</v>
+        <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>98230</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540997</v>
+        <v>540788</v>
       </c>
       <c r="R43" t="n">
-        <v>6964169</v>
+        <v>6964042</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877258</v>
+        <v>125877302</v>
       </c>
       <c r="B72" t="n">
-        <v>80070</v>
+        <v>98324</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540749</v>
+        <v>540970</v>
       </c>
       <c r="R72" t="n">
-        <v>6964056</v>
+        <v>6964115</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877301</v>
       </c>
       <c r="B73" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540963</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964113</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877290</v>
+        <v>125877258</v>
       </c>
       <c r="B74" t="n">
-        <v>80030</v>
+        <v>80070</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540819</v>
+        <v>540749</v>
       </c>
       <c r="R74" t="n">
-        <v>6964057</v>
+        <v>6964056</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877302</v>
+        <v>125877344</v>
       </c>
       <c r="B75" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540970</v>
+        <v>540975</v>
       </c>
       <c r="R75" t="n">
-        <v>6964115</v>
+        <v>6964085</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877301</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>98324</v>
+        <v>80030</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540963</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964113</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877271</v>
+        <v>125877332</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>98237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540996</v>
+        <v>540794</v>
       </c>
       <c r="R2" t="n">
-        <v>6964140</v>
+        <v>6964056</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877332</v>
+        <v>125877322</v>
       </c>
       <c r="B3" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540794</v>
+        <v>540809</v>
       </c>
       <c r="R3" t="n">
-        <v>6964056</v>
+        <v>6964096</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877322</v>
+        <v>125877310</v>
       </c>
       <c r="B4" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540809</v>
+        <v>540890</v>
       </c>
       <c r="R4" t="n">
-        <v>6964096</v>
+        <v>6964145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877310</v>
+        <v>125877259</v>
       </c>
       <c r="B5" t="n">
-        <v>98230</v>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540890</v>
+        <v>540760</v>
       </c>
       <c r="R5" t="n">
-        <v>6964145</v>
+        <v>6964020</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877296</v>
+        <v>125877271</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540787</v>
+        <v>540996</v>
       </c>
       <c r="R6" t="n">
-        <v>6964017</v>
+        <v>6964140</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877300</v>
+        <v>125877296</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540937</v>
+        <v>540787</v>
       </c>
       <c r="R7" t="n">
-        <v>6964110</v>
+        <v>6964017</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877304</v>
+        <v>125877300</v>
       </c>
       <c r="B8" t="n">
-        <v>56834</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540740</v>
+        <v>540937</v>
       </c>
       <c r="R8" t="n">
-        <v>6964067</v>
+        <v>6964110</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1328,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,7 +1357,7 @@
         <v>125877339</v>
       </c>
       <c r="B9" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1456,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877259</v>
+        <v>125877304</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>56834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540760</v>
+        <v>540740</v>
       </c>
       <c r="R10" t="n">
-        <v>6964020</v>
+        <v>6964067</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1527,6 +1522,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,7 +1556,7 @@
         <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125877311</v>
       </c>
       <c r="B18" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877284</v>
+        <v>125877295</v>
       </c>
       <c r="B20" t="n">
-        <v>80106</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540807</v>
+        <v>540765</v>
       </c>
       <c r="R20" t="n">
-        <v>6964031</v>
+        <v>6964025</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877260</v>
+        <v>125877313</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>98237</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540800</v>
+        <v>540882</v>
       </c>
       <c r="R21" t="n">
-        <v>6964021</v>
+        <v>6964119</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877313</v>
+        <v>125877284</v>
       </c>
       <c r="B22" t="n">
-        <v>98230</v>
+        <v>80106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R22" t="n">
-        <v>6964119</v>
+        <v>6964031</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877295</v>
+        <v>125877260</v>
       </c>
       <c r="B23" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540765</v>
+        <v>540800</v>
       </c>
       <c r="R23" t="n">
-        <v>6964025</v>
+        <v>6964021</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2818,7 +2818,7 @@
         <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>125877366</v>
       </c>
       <c r="B31" t="n">
-        <v>88626</v>
+        <v>88633</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125877314</v>
       </c>
       <c r="B33" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98324</v>
+        <v>98237</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98230</v>
+        <v>98331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B41" t="n">
-        <v>80070</v>
+        <v>98237</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R41" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R42" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B43" t="n">
-        <v>98230</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R43" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877242</v>
+        <v>125877299</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>98331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540803</v>
+        <v>540927</v>
       </c>
       <c r="R44" t="n">
-        <v>6964019</v>
+        <v>6964119</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,32 +4857,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877243</v>
+        <v>125877268</v>
       </c>
       <c r="B45" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540821</v>
+        <v>540907</v>
       </c>
       <c r="R45" t="n">
-        <v>6964051</v>
+        <v>6964097</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4957,7 +4957,7 @@
         <v>125877321</v>
       </c>
       <c r="B46" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>125877316</v>
       </c>
       <c r="B47" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,32 +5148,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877268</v>
+        <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R48" t="n">
-        <v>6964097</v>
+        <v>6964019</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877299</v>
+        <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98324</v>
+        <v>98352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540927</v>
+        <v>540821</v>
       </c>
       <c r="R49" t="n">
-        <v>6964119</v>
+        <v>6964051</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5442,7 +5442,7 @@
         <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98324</v>
+        <v>98237</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R57" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>98237</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R58" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98230</v>
+        <v>98331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98230</v>
+        <v>80030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6417,7 +6417,7 @@
         <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877326</v>
+        <v>125877246</v>
       </c>
       <c r="B66" t="n">
-        <v>98230</v>
+        <v>98352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6910,21 +6910,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540801</v>
+        <v>540789</v>
       </c>
       <c r="R66" t="n">
-        <v>6964059</v>
+        <v>6964012</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877235</v>
+        <v>125877326</v>
       </c>
       <c r="B67" t="n">
-        <v>98347</v>
+        <v>98237</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540804</v>
+        <v>540801</v>
       </c>
       <c r="R67" t="n">
-        <v>6964049</v>
+        <v>6964059</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877235</v>
       </c>
       <c r="B68" t="n">
-        <v>98345</v>
+        <v>98354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540804</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964049</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877247</v>
+        <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540780</v>
+        <v>540781</v>
       </c>
       <c r="R69" t="n">
-        <v>6963984</v>
+        <v>6963980</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R70" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877270</v>
+        <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540970</v>
+        <v>540780</v>
       </c>
       <c r="R71" t="n">
-        <v>6964115</v>
+        <v>6963984</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7484,7 +7484,7 @@
         <v>125877302</v>
       </c>
       <c r="B72" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>125877301</v>
       </c>
       <c r="B73" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877258</v>
+        <v>125877290</v>
       </c>
       <c r="B74" t="n">
-        <v>80070</v>
+        <v>80030</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540749</v>
+        <v>540819</v>
       </c>
       <c r="R74" t="n">
-        <v>6964056</v>
+        <v>6964057</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,10 +7772,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877344</v>
+        <v>125877258</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7783,21 +7783,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540975</v>
+        <v>540749</v>
       </c>
       <c r="R75" t="n">
-        <v>6964085</v>
+        <v>6964056</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877344</v>
       </c>
       <c r="B76" t="n">
-        <v>80030</v>
+        <v>78967</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540975</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964085</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877232</v>
+        <v>125877297</v>
       </c>
       <c r="B78" t="n">
-        <v>91220</v>
+        <v>98331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540989</v>
+        <v>540874</v>
       </c>
       <c r="R78" t="n">
-        <v>6964130</v>
+        <v>6964063</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877312</v>
+        <v>125877232</v>
       </c>
       <c r="B79" t="n">
-        <v>98230</v>
+        <v>91227</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540881</v>
+        <v>540989</v>
       </c>
       <c r="R79" t="n">
-        <v>6964135</v>
+        <v>6964130</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877272</v>
+        <v>125877312</v>
       </c>
       <c r="B80" t="n">
-        <v>80070</v>
+        <v>98237</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540806</v>
+        <v>540881</v>
       </c>
       <c r="R80" t="n">
-        <v>6964062</v>
+        <v>6964135</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877274</v>
+        <v>125877272</v>
       </c>
       <c r="B81" t="n">
         <v>80070</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540794</v>
+        <v>540806</v>
       </c>
       <c r="R81" t="n">
-        <v>6964003</v>
+        <v>6964062</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877297</v>
+        <v>125877274</v>
       </c>
       <c r="B82" t="n">
-        <v>98324</v>
+        <v>80070</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540874</v>
+        <v>540794</v>
       </c>
       <c r="R82" t="n">
-        <v>6964063</v>
+        <v>6964003</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8551,7 +8551,7 @@
         <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877318</v>
+        <v>125877240</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540850</v>
+        <v>540848</v>
       </c>
       <c r="R17" t="n">
-        <v>6964070</v>
+        <v>6964065</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,7 +2233,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877311</v>
+        <v>125877318</v>
       </c>
       <c r="B18" t="n">
         <v>98237</v>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540889</v>
+        <v>540850</v>
       </c>
       <c r="R18" t="n">
-        <v>6964139</v>
+        <v>6964070</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877240</v>
+        <v>125877311</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540848</v>
+        <v>540889</v>
       </c>
       <c r="R19" t="n">
-        <v>6964065</v>
+        <v>6964139</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2408,7 +2409,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877295</v>
+        <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>98237</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540765</v>
+        <v>540882</v>
       </c>
       <c r="R20" t="n">
-        <v>6964025</v>
+        <v>6964119</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877313</v>
+        <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>98237</v>
+        <v>80106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R21" t="n">
-        <v>6964119</v>
+        <v>6964031</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877284</v>
+        <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>80106</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540807</v>
+        <v>540800</v>
       </c>
       <c r="R22" t="n">
-        <v>6964031</v>
+        <v>6964021</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877260</v>
+        <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540800</v>
+        <v>540765</v>
       </c>
       <c r="R23" t="n">
-        <v>6964021</v>
+        <v>6964025</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877307</v>
+        <v>125877267</v>
       </c>
       <c r="B41" t="n">
-        <v>98237</v>
+        <v>80070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540788</v>
+        <v>540893</v>
       </c>
       <c r="R41" t="n">
-        <v>6964042</v>
+        <v>6964069</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877267</v>
+        <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540893</v>
+        <v>540997</v>
       </c>
       <c r="R42" t="n">
-        <v>6964069</v>
+        <v>6964169</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877347</v>
+        <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>98237</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540997</v>
+        <v>540788</v>
       </c>
       <c r="R43" t="n">
-        <v>6964169</v>
+        <v>6964042</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B57" t="n">
-        <v>98237</v>
+        <v>98331</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R57" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B58" t="n">
-        <v>98237</v>
+        <v>80030</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R58" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B59" t="n">
-        <v>98331</v>
+        <v>98237</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B60" t="n">
-        <v>80030</v>
+        <v>98237</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B61" t="n">
-        <v>98237</v>
+        <v>98354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R61" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B62" t="n">
-        <v>98354</v>
+        <v>98237</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R62" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877279</v>
+        <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>80070</v>
+        <v>98237</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540793</v>
+        <v>540801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963960</v>
+        <v>6964059</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877282</v>
+        <v>125877235</v>
       </c>
       <c r="B64" t="n">
-        <v>80070</v>
+        <v>98354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540758</v>
+        <v>540804</v>
       </c>
       <c r="R64" t="n">
-        <v>6963956</v>
+        <v>6964049</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877262</v>
+        <v>125877279</v>
       </c>
       <c r="B65" t="n">
         <v>80070</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540818</v>
+        <v>540793</v>
       </c>
       <c r="R65" t="n">
-        <v>6964054</v>
+        <v>6963960</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877246</v>
+        <v>125877282</v>
       </c>
       <c r="B66" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540789</v>
+        <v>540758</v>
       </c>
       <c r="R66" t="n">
-        <v>6964012</v>
+        <v>6963956</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B67" t="n">
-        <v>98237</v>
+        <v>80070</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R67" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877235</v>
+        <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98354</v>
+        <v>98352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540804</v>
+        <v>540789</v>
       </c>
       <c r="R68" t="n">
-        <v>6964049</v>
+        <v>6964012</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877302</v>
+        <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>98331</v>
+        <v>80070</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540970</v>
+        <v>540749</v>
       </c>
       <c r="R72" t="n">
-        <v>6964115</v>
+        <v>6964056</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877301</v>
+        <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540963</v>
+        <v>540975</v>
       </c>
       <c r="R73" t="n">
-        <v>6964113</v>
+        <v>6964085</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877290</v>
+        <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>80030</v>
+        <v>98331</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540819</v>
+        <v>540970</v>
       </c>
       <c r="R74" t="n">
-        <v>6964057</v>
+        <v>6964115</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877258</v>
+        <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>80070</v>
+        <v>98331</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540749</v>
+        <v>540963</v>
       </c>
       <c r="R75" t="n">
-        <v>6964056</v>
+        <v>6964113</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877344</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>78967</v>
+        <v>80030</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540975</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964085</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877332</v>
+        <v>125877259</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540794</v>
+        <v>540760</v>
       </c>
       <c r="R2" t="n">
-        <v>6964056</v>
+        <v>6964020</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877322</v>
+        <v>125877271</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540809</v>
+        <v>540996</v>
       </c>
       <c r="R3" t="n">
-        <v>6964096</v>
+        <v>6964140</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877310</v>
+        <v>125877296</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540890</v>
+        <v>540787</v>
       </c>
       <c r="R4" t="n">
-        <v>6964145</v>
+        <v>6964017</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877259</v>
+        <v>125877300</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>98332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540760</v>
+        <v>540937</v>
       </c>
       <c r="R5" t="n">
-        <v>6964020</v>
+        <v>6964110</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877271</v>
+        <v>125877339</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>105356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540996</v>
+        <v>540959</v>
       </c>
       <c r="R6" t="n">
-        <v>6964140</v>
+        <v>6964030</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877296</v>
+        <v>125877304</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>56834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540787</v>
+        <v>540740</v>
       </c>
       <c r="R7" t="n">
-        <v>6964017</v>
+        <v>6964067</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877300</v>
+        <v>125877332</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540937</v>
+        <v>540794</v>
       </c>
       <c r="R8" t="n">
-        <v>6964110</v>
+        <v>6964056</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877339</v>
+        <v>125877322</v>
       </c>
       <c r="B9" t="n">
-        <v>105355</v>
+        <v>98238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540959</v>
+        <v>540809</v>
       </c>
       <c r="R9" t="n">
-        <v>6964030</v>
+        <v>6964096</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1451,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877304</v>
+        <v>125877310</v>
       </c>
       <c r="B10" t="n">
-        <v>56834</v>
+        <v>98238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540740</v>
+        <v>540890</v>
       </c>
       <c r="R10" t="n">
-        <v>6964067</v>
+        <v>6964145</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1522,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,7 +1556,7 @@
         <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877315</v>
+        <v>125877275</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540848</v>
+        <v>540780</v>
       </c>
       <c r="R13" t="n">
-        <v>6964091</v>
+        <v>6963983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877275</v>
+        <v>125877277</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540780</v>
+        <v>540786</v>
       </c>
       <c r="R14" t="n">
-        <v>6963983</v>
+        <v>6963974</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877277</v>
+        <v>125877264</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540786</v>
+        <v>540828</v>
       </c>
       <c r="R15" t="n">
-        <v>6963974</v>
+        <v>6964037</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877264</v>
+        <v>125877315</v>
       </c>
       <c r="B16" t="n">
-        <v>80070</v>
+        <v>98238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540828</v>
+        <v>540848</v>
       </c>
       <c r="R16" t="n">
-        <v>6964037</v>
+        <v>6964091</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877240</v>
+        <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540848</v>
+        <v>540850</v>
       </c>
       <c r="R17" t="n">
-        <v>6964065</v>
+        <v>6964070</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877318</v>
+        <v>125877311</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540850</v>
+        <v>540889</v>
       </c>
       <c r="R18" t="n">
-        <v>6964070</v>
+        <v>6964139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877311</v>
+        <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>98353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540889</v>
+        <v>540848</v>
       </c>
       <c r="R19" t="n">
-        <v>6964139</v>
+        <v>6964065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877313</v>
+        <v>125877295</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>98332</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540882</v>
+        <v>540765</v>
       </c>
       <c r="R20" t="n">
-        <v>6964119</v>
+        <v>6964025</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2527,7 +2527,7 @@
         <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877295</v>
+        <v>125877313</v>
       </c>
       <c r="B23" t="n">
-        <v>98331</v>
+        <v>98238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540765</v>
+        <v>540882</v>
       </c>
       <c r="R23" t="n">
-        <v>6964025</v>
+        <v>6964119</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877320</v>
+        <v>125877276</v>
       </c>
       <c r="B24" t="n">
-        <v>98237</v>
+        <v>80071</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540882</v>
+        <v>540785</v>
       </c>
       <c r="R24" t="n">
-        <v>6964142</v>
+        <v>6963977</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877276</v>
+        <v>125877278</v>
       </c>
       <c r="B25" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540785</v>
+        <v>540790</v>
       </c>
       <c r="R25" t="n">
-        <v>6963977</v>
+        <v>6963972</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877278</v>
+        <v>125877269</v>
       </c>
       <c r="B26" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540790</v>
+        <v>540964</v>
       </c>
       <c r="R26" t="n">
-        <v>6963972</v>
+        <v>6964121</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877269</v>
+        <v>125877261</v>
       </c>
       <c r="B27" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540964</v>
+        <v>540807</v>
       </c>
       <c r="R27" t="n">
-        <v>6964121</v>
+        <v>6964030</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877261</v>
+        <v>125877320</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>98238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R28" t="n">
-        <v>6964030</v>
+        <v>6964142</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3303,7 +3303,7 @@
         <v>125877291</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>125877366</v>
       </c>
       <c r="B31" t="n">
-        <v>88633</v>
+        <v>88637</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125877314</v>
       </c>
       <c r="B33" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877273</v>
+        <v>125877298</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>98332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540797</v>
+        <v>540912</v>
       </c>
       <c r="R35" t="n">
-        <v>6964057</v>
+        <v>6964122</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877273</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540797</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877298</v>
+        <v>125877266</v>
       </c>
       <c r="B37" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540912</v>
+        <v>540868</v>
       </c>
       <c r="R37" t="n">
-        <v>6964122</v>
+        <v>6964062</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4181,7 +4181,7 @@
         <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>125877317</v>
       </c>
       <c r="B39" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>125877267</v>
       </c>
       <c r="B41" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877299</v>
+        <v>125877268</v>
       </c>
       <c r="B44" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540927</v>
+        <v>540907</v>
       </c>
       <c r="R44" t="n">
-        <v>6964119</v>
+        <v>6964097</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,32 +4857,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877268</v>
+        <v>125877321</v>
       </c>
       <c r="B45" t="n">
-        <v>80070</v>
+        <v>98238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540907</v>
+        <v>540855</v>
       </c>
       <c r="R45" t="n">
-        <v>6964097</v>
+        <v>6964125</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877321</v>
+        <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540855</v>
+        <v>540803</v>
       </c>
       <c r="R46" t="n">
-        <v>6964125</v>
+        <v>6964060</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877316</v>
+        <v>125877242</v>
       </c>
       <c r="B47" t="n">
-        <v>98237</v>
+        <v>98353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5062,21 +5062,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
         <v>540803</v>
       </c>
       <c r="R47" t="n">
-        <v>6964060</v>
+        <v>6964019</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877242</v>
+        <v>125877243</v>
       </c>
       <c r="B48" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540803</v>
+        <v>540821</v>
       </c>
       <c r="R48" t="n">
-        <v>6964019</v>
+        <v>6964051</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877243</v>
+        <v>125877299</v>
       </c>
       <c r="B49" t="n">
-        <v>98352</v>
+        <v>98332</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540821</v>
+        <v>540927</v>
       </c>
       <c r="R49" t="n">
-        <v>6964051</v>
+        <v>6964119</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B50" t="n">
-        <v>80070</v>
+        <v>98353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R50" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B51" t="n">
-        <v>98352</v>
+        <v>80071</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R51" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877341</v>
+        <v>125877285</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>80107</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540852</v>
+        <v>540907</v>
       </c>
       <c r="R52" t="n">
-        <v>6964074</v>
+        <v>6964097</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,32 +5633,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877350</v>
+        <v>125877238</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>98355</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540785</v>
+        <v>540793</v>
       </c>
       <c r="R53" t="n">
-        <v>6964039</v>
+        <v>6964055</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877285</v>
+        <v>125877350</v>
       </c>
       <c r="B54" t="n">
-        <v>80106</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540907</v>
+        <v>540785</v>
       </c>
       <c r="R54" t="n">
-        <v>6964097</v>
+        <v>6964039</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5929,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877238</v>
+        <v>125877341</v>
       </c>
       <c r="B56" t="n">
-        <v>98354</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540793</v>
+        <v>540852</v>
       </c>
       <c r="R56" t="n">
-        <v>6964055</v>
+        <v>6964074</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98331</v>
+        <v>98238</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R57" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>98238</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R58" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98237</v>
+        <v>98332</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98237</v>
+        <v>80031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98354</v>
+        <v>98238</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R61" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98237</v>
+        <v>98355</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R62" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877326</v>
+        <v>125877282</v>
       </c>
       <c r="B63" t="n">
-        <v>98237</v>
+        <v>80071</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540801</v>
+        <v>540758</v>
       </c>
       <c r="R63" t="n">
-        <v>6964059</v>
+        <v>6963956</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877235</v>
+        <v>125877262</v>
       </c>
       <c r="B64" t="n">
-        <v>98354</v>
+        <v>80071</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540804</v>
+        <v>540818</v>
       </c>
       <c r="R64" t="n">
-        <v>6964049</v>
+        <v>6964054</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6805,7 +6805,7 @@
         <v>125877279</v>
       </c>
       <c r="B65" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877282</v>
+        <v>125877246</v>
       </c>
       <c r="B66" t="n">
-        <v>80070</v>
+        <v>98353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540758</v>
+        <v>540789</v>
       </c>
       <c r="R66" t="n">
-        <v>6963956</v>
+        <v>6964012</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877262</v>
+        <v>125877326</v>
       </c>
       <c r="B67" t="n">
-        <v>80070</v>
+        <v>98238</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540818</v>
+        <v>540801</v>
       </c>
       <c r="R67" t="n">
-        <v>6964054</v>
+        <v>6964059</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877235</v>
       </c>
       <c r="B68" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540804</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964049</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R69" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877270</v>
+        <v>125877354</v>
       </c>
       <c r="B70" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540970</v>
+        <v>540781</v>
       </c>
       <c r="R70" t="n">
-        <v>6964115</v>
+        <v>6963980</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7387,7 +7387,7 @@
         <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B72" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7492,21 +7492,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R72" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877302</v>
       </c>
       <c r="B73" t="n">
-        <v>78967</v>
+        <v>98332</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540970</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964115</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,10 +7675,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877302</v>
+        <v>125877301</v>
       </c>
       <c r="B74" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540970</v>
+        <v>540963</v>
       </c>
       <c r="R74" t="n">
-        <v>6964115</v>
+        <v>6964113</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877301</v>
+        <v>125877290</v>
       </c>
       <c r="B75" t="n">
-        <v>98331</v>
+        <v>80031</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540963</v>
+        <v>540819</v>
       </c>
       <c r="R75" t="n">
-        <v>6964113</v>
+        <v>6964057</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877258</v>
       </c>
       <c r="B76" t="n">
-        <v>80030</v>
+        <v>80071</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540749</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964056</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877297</v>
+        <v>125877272</v>
       </c>
       <c r="B78" t="n">
-        <v>98331</v>
+        <v>80071</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540874</v>
+        <v>540806</v>
       </c>
       <c r="R78" t="n">
-        <v>6964063</v>
+        <v>6964062</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,10 +8160,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877232</v>
+        <v>125877274</v>
       </c>
       <c r="B79" t="n">
-        <v>91227</v>
+        <v>80071</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8171,21 +8171,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540989</v>
+        <v>540794</v>
       </c>
       <c r="R79" t="n">
-        <v>6964130</v>
+        <v>6964003</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877312</v>
+        <v>125877232</v>
       </c>
       <c r="B80" t="n">
-        <v>98237</v>
+        <v>91228</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540881</v>
+        <v>540989</v>
       </c>
       <c r="R80" t="n">
-        <v>6964135</v>
+        <v>6964130</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,32 +8354,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877272</v>
+        <v>125877312</v>
       </c>
       <c r="B81" t="n">
-        <v>80070</v>
+        <v>98238</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540806</v>
+        <v>540881</v>
       </c>
       <c r="R81" t="n">
-        <v>6964062</v>
+        <v>6964135</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877274</v>
+        <v>125877297</v>
       </c>
       <c r="B82" t="n">
-        <v>80070</v>
+        <v>98332</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540794</v>
+        <v>540874</v>
       </c>
       <c r="R82" t="n">
-        <v>6964003</v>
+        <v>6964063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8551,7 +8551,7 @@
         <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877259</v>
+        <v>125877339</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>105358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540760</v>
+        <v>540959</v>
       </c>
       <c r="R2" t="n">
-        <v>6964020</v>
+        <v>6964030</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877271</v>
+        <v>125877304</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>56834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540996</v>
+        <v>540740</v>
       </c>
       <c r="R3" t="n">
-        <v>6964140</v>
+        <v>6964067</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +877,7 @@
         <v>125877296</v>
       </c>
       <c r="B4" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +974,7 @@
         <v>125877300</v>
       </c>
       <c r="B5" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877339</v>
+        <v>125877332</v>
       </c>
       <c r="B6" t="n">
-        <v>105356</v>
+        <v>98240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540959</v>
+        <v>540794</v>
       </c>
       <c r="R6" t="n">
-        <v>6964030</v>
+        <v>6964056</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877304</v>
+        <v>125877322</v>
       </c>
       <c r="B7" t="n">
-        <v>56834</v>
+        <v>98240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540740</v>
+        <v>540809</v>
       </c>
       <c r="R7" t="n">
-        <v>6964067</v>
+        <v>6964096</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877332</v>
+        <v>125877310</v>
       </c>
       <c r="B8" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540794</v>
+        <v>540890</v>
       </c>
       <c r="R8" t="n">
-        <v>6964056</v>
+        <v>6964145</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877322</v>
+        <v>125877259</v>
       </c>
       <c r="B9" t="n">
-        <v>98238</v>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540809</v>
+        <v>540760</v>
       </c>
       <c r="R9" t="n">
-        <v>6964096</v>
+        <v>6964020</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877310</v>
+        <v>125877271</v>
       </c>
       <c r="B10" t="n">
-        <v>98238</v>
+        <v>80071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540890</v>
+        <v>540996</v>
       </c>
       <c r="R10" t="n">
-        <v>6964145</v>
+        <v>6964140</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1556,7 +1556,7 @@
         <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877275</v>
+        <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>98240</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540780</v>
+        <v>540848</v>
       </c>
       <c r="R13" t="n">
-        <v>6963983</v>
+        <v>6964091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877277</v>
+        <v>125877275</v>
       </c>
       <c r="B14" t="n">
         <v>80071</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540786</v>
+        <v>540780</v>
       </c>
       <c r="R14" t="n">
-        <v>6963974</v>
+        <v>6963983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877264</v>
+        <v>125877277</v>
       </c>
       <c r="B15" t="n">
         <v>80071</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540828</v>
+        <v>540786</v>
       </c>
       <c r="R15" t="n">
-        <v>6964037</v>
+        <v>6963974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877315</v>
+        <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>98238</v>
+        <v>80071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540848</v>
+        <v>540828</v>
       </c>
       <c r="R16" t="n">
-        <v>6964091</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2138,7 +2138,7 @@
         <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125877311</v>
       </c>
       <c r="B18" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877295</v>
+        <v>125877284</v>
       </c>
       <c r="B20" t="n">
-        <v>98332</v>
+        <v>80107</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540765</v>
+        <v>540807</v>
       </c>
       <c r="R20" t="n">
-        <v>6964025</v>
+        <v>6964031</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877284</v>
+        <v>125877260</v>
       </c>
       <c r="B21" t="n">
-        <v>80107</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540807</v>
+        <v>540800</v>
       </c>
       <c r="R21" t="n">
-        <v>6964031</v>
+        <v>6964021</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877260</v>
+        <v>125877313</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>98240</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540800</v>
+        <v>540882</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964119</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877313</v>
+        <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98238</v>
+        <v>98334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540882</v>
+        <v>540765</v>
       </c>
       <c r="R23" t="n">
-        <v>6964119</v>
+        <v>6964025</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877276</v>
+        <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>80071</v>
+        <v>98240</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540785</v>
+        <v>540882</v>
       </c>
       <c r="R24" t="n">
-        <v>6963977</v>
+        <v>6964142</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877278</v>
+        <v>125877276</v>
       </c>
       <c r="B25" t="n">
         <v>80071</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540790</v>
+        <v>540785</v>
       </c>
       <c r="R25" t="n">
-        <v>6963972</v>
+        <v>6963977</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877269</v>
+        <v>125877278</v>
       </c>
       <c r="B26" t="n">
         <v>80071</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540964</v>
+        <v>540790</v>
       </c>
       <c r="R26" t="n">
-        <v>6964121</v>
+        <v>6963972</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877261</v>
+        <v>125877269</v>
       </c>
       <c r="B27" t="n">
         <v>80071</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540807</v>
+        <v>540964</v>
       </c>
       <c r="R27" t="n">
-        <v>6964030</v>
+        <v>6964121</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877320</v>
+        <v>125877261</v>
       </c>
       <c r="B28" t="n">
-        <v>98238</v>
+        <v>80071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R28" t="n">
-        <v>6964142</v>
+        <v>6964030</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3400,7 +3400,7 @@
         <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125877314</v>
       </c>
       <c r="B33" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877298</v>
+        <v>125877273</v>
       </c>
       <c r="B35" t="n">
-        <v>98332</v>
+        <v>80071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540912</v>
+        <v>540797</v>
       </c>
       <c r="R35" t="n">
-        <v>6964122</v>
+        <v>6964057</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877273</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
         <v>80071</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540797</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964057</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877266</v>
+        <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540868</v>
+        <v>540912</v>
       </c>
       <c r="R37" t="n">
-        <v>6964062</v>
+        <v>6964122</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4181,7 +4181,7 @@
         <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>125877317</v>
       </c>
       <c r="B39" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877267</v>
+        <v>125877347</v>
       </c>
       <c r="B41" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540893</v>
+        <v>540997</v>
       </c>
       <c r="R41" t="n">
-        <v>6964069</v>
+        <v>6964169</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R42" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4666,7 +4666,7 @@
         <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>125877321</v>
       </c>
       <c r="B45" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877242</v>
+        <v>125877299</v>
       </c>
       <c r="B47" t="n">
-        <v>98353</v>
+        <v>98334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540803</v>
+        <v>540927</v>
       </c>
       <c r="R47" t="n">
-        <v>6964019</v>
+        <v>6964119</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877243</v>
+        <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540821</v>
+        <v>540803</v>
       </c>
       <c r="R48" t="n">
-        <v>6964051</v>
+        <v>6964019</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877299</v>
+        <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98332</v>
+        <v>98355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540927</v>
+        <v>540821</v>
       </c>
       <c r="R49" t="n">
-        <v>6964119</v>
+        <v>6964051</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B50" t="n">
-        <v>98353</v>
+        <v>80071</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R50" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>80071</v>
+        <v>98355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R51" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877285</v>
+        <v>125877238</v>
       </c>
       <c r="B52" t="n">
-        <v>80107</v>
+        <v>98357</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540907</v>
+        <v>540793</v>
       </c>
       <c r="R52" t="n">
-        <v>6964097</v>
+        <v>6964055</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,10 +5633,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877238</v>
+        <v>125877285</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>80107</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5644,21 +5644,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540793</v>
+        <v>540907</v>
       </c>
       <c r="R53" t="n">
-        <v>6964055</v>
+        <v>6964097</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877350</v>
+        <v>125877305</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>56834</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5741,21 +5741,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540785</v>
+        <v>540783</v>
       </c>
       <c r="R54" t="n">
-        <v>6964039</v>
+        <v>6964091</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5801,6 +5801,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5827,10 +5832,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877305</v>
+        <v>125877341</v>
       </c>
       <c r="B55" t="n">
-        <v>56834</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5838,21 +5843,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540783</v>
+        <v>540852</v>
       </c>
       <c r="R55" t="n">
-        <v>6964091</v>
+        <v>6964074</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,11 +5903,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5929,7 +5929,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877341</v>
+        <v>125877350</v>
       </c>
       <c r="B56" t="n">
         <v>78968</v>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540852</v>
+        <v>540785</v>
       </c>
       <c r="R56" t="n">
-        <v>6964074</v>
+        <v>6964039</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6029,7 +6029,7 @@
         <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877282</v>
+        <v>125877235</v>
       </c>
       <c r="B63" t="n">
-        <v>80071</v>
+        <v>98357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540758</v>
+        <v>540804</v>
       </c>
       <c r="R63" t="n">
-        <v>6963956</v>
+        <v>6964049</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877262</v>
+        <v>125877246</v>
       </c>
       <c r="B64" t="n">
-        <v>80071</v>
+        <v>98355</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540818</v>
+        <v>540789</v>
       </c>
       <c r="R64" t="n">
-        <v>6964054</v>
+        <v>6964012</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877246</v>
+        <v>125877282</v>
       </c>
       <c r="B66" t="n">
-        <v>98353</v>
+        <v>80071</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540789</v>
+        <v>540758</v>
       </c>
       <c r="R66" t="n">
-        <v>6964012</v>
+        <v>6963956</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B67" t="n">
-        <v>98238</v>
+        <v>80071</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R67" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877235</v>
+        <v>125877326</v>
       </c>
       <c r="B68" t="n">
-        <v>98355</v>
+        <v>98240</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540804</v>
+        <v>540801</v>
       </c>
       <c r="R68" t="n">
-        <v>6964049</v>
+        <v>6964059</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877270</v>
+        <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540970</v>
+        <v>540781</v>
       </c>
       <c r="R69" t="n">
-        <v>6964115</v>
+        <v>6963980</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R70" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7387,7 +7387,7 @@
         <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877344</v>
+        <v>125877302</v>
       </c>
       <c r="B72" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540975</v>
+        <v>540970</v>
       </c>
       <c r="R72" t="n">
-        <v>6964085</v>
+        <v>6964115</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877302</v>
+        <v>125877301</v>
       </c>
       <c r="B73" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540970</v>
+        <v>540963</v>
       </c>
       <c r="R73" t="n">
-        <v>6964115</v>
+        <v>6964113</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877301</v>
+        <v>125877290</v>
       </c>
       <c r="B74" t="n">
-        <v>98332</v>
+        <v>80031</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540963</v>
+        <v>540819</v>
       </c>
       <c r="R74" t="n">
-        <v>6964113</v>
+        <v>6964057</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877290</v>
+        <v>125877344</v>
       </c>
       <c r="B75" t="n">
-        <v>80031</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540819</v>
+        <v>540975</v>
       </c>
       <c r="R75" t="n">
-        <v>6964057</v>
+        <v>6964085</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,10 +8063,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877272</v>
+        <v>125877232</v>
       </c>
       <c r="B78" t="n">
-        <v>80071</v>
+        <v>91228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8074,21 +8074,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540806</v>
+        <v>540989</v>
       </c>
       <c r="R78" t="n">
-        <v>6964062</v>
+        <v>6964130</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877274</v>
+        <v>125877297</v>
       </c>
       <c r="B79" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540794</v>
+        <v>540874</v>
       </c>
       <c r="R79" t="n">
-        <v>6964003</v>
+        <v>6964063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877232</v>
+        <v>125877312</v>
       </c>
       <c r="B80" t="n">
-        <v>91228</v>
+        <v>98240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540989</v>
+        <v>540881</v>
       </c>
       <c r="R80" t="n">
-        <v>6964130</v>
+        <v>6964135</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,32 +8354,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877312</v>
+        <v>125877272</v>
       </c>
       <c r="B81" t="n">
-        <v>98238</v>
+        <v>80071</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540881</v>
+        <v>540806</v>
       </c>
       <c r="R81" t="n">
-        <v>6964135</v>
+        <v>6964062</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877297</v>
+        <v>125877274</v>
       </c>
       <c r="B82" t="n">
-        <v>98332</v>
+        <v>80071</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540874</v>
+        <v>540794</v>
       </c>
       <c r="R82" t="n">
-        <v>6964063</v>
+        <v>6964003</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8551,7 +8551,7 @@
         <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877339</v>
+        <v>125877332</v>
       </c>
       <c r="B2" t="n">
-        <v>105358</v>
+        <v>98240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540959</v>
+        <v>540794</v>
       </c>
       <c r="R2" t="n">
-        <v>6964030</v>
+        <v>6964056</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877304</v>
+        <v>125877322</v>
       </c>
       <c r="B3" t="n">
-        <v>56834</v>
+        <v>98240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540740</v>
+        <v>540809</v>
       </c>
       <c r="R3" t="n">
-        <v>6964067</v>
+        <v>6964096</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877296</v>
+        <v>125877310</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540787</v>
+        <v>540890</v>
       </c>
       <c r="R4" t="n">
-        <v>6964017</v>
+        <v>6964145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877300</v>
+        <v>125877259</v>
       </c>
       <c r="B5" t="n">
-        <v>98334</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540937</v>
+        <v>540760</v>
       </c>
       <c r="R5" t="n">
-        <v>6964110</v>
+        <v>6964020</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877332</v>
+        <v>125877271</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540794</v>
+        <v>540996</v>
       </c>
       <c r="R6" t="n">
-        <v>6964056</v>
+        <v>6964140</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877322</v>
+        <v>125877304</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>56834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540809</v>
+        <v>540740</v>
       </c>
       <c r="R7" t="n">
-        <v>6964096</v>
+        <v>6964067</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877310</v>
+        <v>125877296</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540890</v>
+        <v>540787</v>
       </c>
       <c r="R8" t="n">
-        <v>6964145</v>
+        <v>6964017</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877259</v>
+        <v>125877300</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540760</v>
+        <v>540937</v>
       </c>
       <c r="R9" t="n">
-        <v>6964020</v>
+        <v>6964110</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877271</v>
+        <v>125877339</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>105358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540996</v>
+        <v>540959</v>
       </c>
       <c r="R10" t="n">
-        <v>6964140</v>
+        <v>6964030</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877235</v>
+        <v>125877279</v>
       </c>
       <c r="B63" t="n">
-        <v>98357</v>
+        <v>80071</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540804</v>
+        <v>540793</v>
       </c>
       <c r="R63" t="n">
-        <v>6964049</v>
+        <v>6963960</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877246</v>
+        <v>125877282</v>
       </c>
       <c r="B64" t="n">
-        <v>98355</v>
+        <v>80071</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540789</v>
+        <v>540758</v>
       </c>
       <c r="R64" t="n">
-        <v>6964012</v>
+        <v>6963956</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877279</v>
+        <v>125877262</v>
       </c>
       <c r="B65" t="n">
         <v>80071</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540793</v>
+        <v>540818</v>
       </c>
       <c r="R65" t="n">
-        <v>6963960</v>
+        <v>6964054</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877282</v>
+        <v>125877326</v>
       </c>
       <c r="B66" t="n">
-        <v>80071</v>
+        <v>98240</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540758</v>
+        <v>540801</v>
       </c>
       <c r="R66" t="n">
-        <v>6963956</v>
+        <v>6964059</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877262</v>
+        <v>125877235</v>
       </c>
       <c r="B67" t="n">
-        <v>80071</v>
+        <v>98357</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540818</v>
+        <v>540804</v>
       </c>
       <c r="R67" t="n">
-        <v>6964054</v>
+        <v>6964049</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877326</v>
+        <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98240</v>
+        <v>98355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540801</v>
+        <v>540789</v>
       </c>
       <c r="R68" t="n">
-        <v>6964059</v>
+        <v>6964012</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877332</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125877322</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125877310</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125877259</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125877271</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877296</v>
+        <v>125877339</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>105362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540787</v>
+        <v>540959</v>
       </c>
       <c r="R8" t="n">
-        <v>6964017</v>
+        <v>6964030</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877300</v>
+        <v>125877296</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540937</v>
+        <v>540787</v>
       </c>
       <c r="R9" t="n">
-        <v>6964110</v>
+        <v>6964017</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877339</v>
+        <v>125877300</v>
       </c>
       <c r="B10" t="n">
-        <v>105358</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540959</v>
+        <v>540937</v>
       </c>
       <c r="R10" t="n">
-        <v>6964030</v>
+        <v>6964110</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R11" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>98244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R12" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877315</v>
+        <v>125877275</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540848</v>
+        <v>540780</v>
       </c>
       <c r="R13" t="n">
-        <v>6964091</v>
+        <v>6963983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877275</v>
+        <v>125877277</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540780</v>
+        <v>540786</v>
       </c>
       <c r="R14" t="n">
-        <v>6963983</v>
+        <v>6963974</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877277</v>
+        <v>125877264</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540786</v>
+        <v>540828</v>
       </c>
       <c r="R15" t="n">
-        <v>6963974</v>
+        <v>6964037</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877264</v>
+        <v>125877315</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>98244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540828</v>
+        <v>540848</v>
       </c>
       <c r="R16" t="n">
-        <v>6964037</v>
+        <v>6964091</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877318</v>
+        <v>125877240</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
+        <v>98359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540850</v>
+        <v>540848</v>
       </c>
       <c r="R17" t="n">
-        <v>6964070</v>
+        <v>6964065</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877311</v>
+        <v>125877318</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540889</v>
+        <v>540850</v>
       </c>
       <c r="R18" t="n">
-        <v>6964139</v>
+        <v>6964070</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877240</v>
+        <v>125877311</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540848</v>
+        <v>540889</v>
       </c>
       <c r="R19" t="n">
-        <v>6964065</v>
+        <v>6964139</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2408,7 +2409,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877284</v>
+        <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>80107</v>
+        <v>98244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R20" t="n">
-        <v>6964031</v>
+        <v>6964119</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877260</v>
+        <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>80111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540800</v>
+        <v>540807</v>
       </c>
       <c r="R21" t="n">
-        <v>6964021</v>
+        <v>6964031</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877313</v>
+        <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>98240</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540882</v>
+        <v>540800</v>
       </c>
       <c r="R22" t="n">
-        <v>6964119</v>
+        <v>6964021</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>125877276</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>125877278</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>125877269</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>125877261</v>
       </c>
       <c r="B28" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>125877291</v>
       </c>
       <c r="B29" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877306</v>
+        <v>125877298</v>
       </c>
       <c r="B30" t="n">
-        <v>98240</v>
+        <v>98338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540793</v>
+        <v>540912</v>
       </c>
       <c r="R30" t="n">
-        <v>6964055</v>
+        <v>6964122</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,11 +3468,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3499,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877366</v>
+        <v>125877306</v>
       </c>
       <c r="B31" t="n">
-        <v>88637</v>
+        <v>98244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540874</v>
+        <v>540793</v>
       </c>
       <c r="R31" t="n">
-        <v>6964114</v>
+        <v>6964055</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3570,6 +3565,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877323</v>
+        <v>125877366</v>
       </c>
       <c r="B32" t="n">
-        <v>98240</v>
+        <v>88641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540803</v>
+        <v>540874</v>
       </c>
       <c r="R32" t="n">
-        <v>6964102</v>
+        <v>6964114</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877314</v>
+        <v>125877323</v>
       </c>
       <c r="B33" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540853</v>
+        <v>540803</v>
       </c>
       <c r="R33" t="n">
-        <v>6964095</v>
+        <v>6964102</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877252</v>
+        <v>125877314</v>
       </c>
       <c r="B34" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540788</v>
+        <v>540853</v>
       </c>
       <c r="R34" t="n">
-        <v>6964033</v>
+        <v>6964095</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877273</v>
+        <v>125877252</v>
       </c>
       <c r="B35" t="n">
-        <v>80071</v>
+        <v>98244</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540797</v>
+        <v>540788</v>
       </c>
       <c r="R35" t="n">
-        <v>6964057</v>
+        <v>6964033</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877273</v>
       </c>
       <c r="B36" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540797</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877298</v>
+        <v>125877266</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540912</v>
+        <v>540868</v>
       </c>
       <c r="R37" t="n">
-        <v>6964122</v>
+        <v>6964062</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877303</v>
       </c>
       <c r="B38" t="n">
-        <v>98240</v>
+        <v>98338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540785</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6963977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877335</v>
       </c>
       <c r="B39" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540781</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877317</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>98244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540850</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877347</v>
+        <v>125877307</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>98244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540997</v>
+        <v>540788</v>
       </c>
       <c r="R41" t="n">
-        <v>6964169</v>
+        <v>6964042</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4569,7 +4569,7 @@
         <v>125877267</v>
       </c>
       <c r="B42" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B43" t="n">
-        <v>98240</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R43" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877268</v>
+        <v>125877299</v>
       </c>
       <c r="B44" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540907</v>
+        <v>540927</v>
       </c>
       <c r="R44" t="n">
-        <v>6964097</v>
+        <v>6964119</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4860,7 +4860,7 @@
         <v>125877321</v>
       </c>
       <c r="B45" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877299</v>
+        <v>125877268</v>
       </c>
       <c r="B47" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540927</v>
+        <v>540907</v>
       </c>
       <c r="R47" t="n">
-        <v>6964119</v>
+        <v>6964097</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
         <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>125877263</v>
       </c>
       <c r="B50" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877238</v>
+        <v>125877341</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540793</v>
+        <v>540852</v>
       </c>
       <c r="R52" t="n">
-        <v>6964055</v>
+        <v>6964074</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,32 +5633,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877285</v>
+        <v>125877350</v>
       </c>
       <c r="B53" t="n">
-        <v>80107</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540907</v>
+        <v>540785</v>
       </c>
       <c r="R53" t="n">
-        <v>6964097</v>
+        <v>6964039</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877305</v>
+        <v>125877285</v>
       </c>
       <c r="B54" t="n">
-        <v>56834</v>
+        <v>80111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540783</v>
+        <v>540907</v>
       </c>
       <c r="R54" t="n">
-        <v>6964091</v>
+        <v>6964097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5801,11 +5801,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5832,10 +5827,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877341</v>
+        <v>125877305</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>56834</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5838,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540852</v>
+        <v>540783</v>
       </c>
       <c r="R55" t="n">
-        <v>6964074</v>
+        <v>6964091</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5903,6 +5898,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5929,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877350</v>
+        <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>98361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540785</v>
+        <v>540793</v>
       </c>
       <c r="R56" t="n">
-        <v>6964039</v>
+        <v>6964055</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877309</v>
+        <v>125877292</v>
       </c>
       <c r="B57" t="n">
-        <v>98240</v>
+        <v>80035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540880</v>
+        <v>540811</v>
       </c>
       <c r="R57" t="n">
-        <v>6964142</v>
+        <v>6964057</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877330</v>
+        <v>125877294</v>
       </c>
       <c r="B58" t="n">
-        <v>98240</v>
+        <v>98338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540792</v>
+        <v>540750</v>
       </c>
       <c r="R58" t="n">
-        <v>6964061</v>
+        <v>6964085</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B59" t="n">
-        <v>98334</v>
+        <v>98244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B60" t="n">
-        <v>80031</v>
+        <v>98244</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B61" t="n">
-        <v>98240</v>
+        <v>98361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R61" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B62" t="n">
-        <v>98357</v>
+        <v>98244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R62" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877279</v>
+        <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>80071</v>
+        <v>98244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540793</v>
+        <v>540801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963960</v>
+        <v>6964059</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B64" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R64" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B65" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R65" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B66" t="n">
-        <v>98240</v>
+        <v>80075</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R66" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6999,7 +6999,7 @@
         <v>125877235</v>
       </c>
       <c r="B67" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877302</v>
+        <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>98334</v>
+        <v>80075</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540970</v>
+        <v>540749</v>
       </c>
       <c r="R72" t="n">
-        <v>6964115</v>
+        <v>6964056</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877301</v>
+        <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540963</v>
+        <v>540975</v>
       </c>
       <c r="R73" t="n">
-        <v>6964113</v>
+        <v>6964085</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7678,7 +7678,7 @@
         <v>125877290</v>
       </c>
       <c r="B74" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877344</v>
+        <v>125877302</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540975</v>
+        <v>540970</v>
       </c>
       <c r="R75" t="n">
-        <v>6964085</v>
+        <v>6964115</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877258</v>
+        <v>125877301</v>
       </c>
       <c r="B76" t="n">
-        <v>80071</v>
+        <v>98338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540749</v>
+        <v>540963</v>
       </c>
       <c r="R76" t="n">
-        <v>6964056</v>
+        <v>6964113</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>125877232</v>
       </c>
       <c r="B78" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877297</v>
+        <v>125877312</v>
       </c>
       <c r="B79" t="n">
-        <v>98334</v>
+        <v>98244</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540874</v>
+        <v>540881</v>
       </c>
       <c r="R79" t="n">
-        <v>6964063</v>
+        <v>6964135</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877312</v>
+        <v>125877297</v>
       </c>
       <c r="B80" t="n">
-        <v>98240</v>
+        <v>98338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540881</v>
+        <v>540874</v>
       </c>
       <c r="R80" t="n">
-        <v>6964135</v>
+        <v>6964063</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8357,7 +8357,7 @@
         <v>125877272</v>
       </c>
       <c r="B81" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         <v>125877274</v>
       </c>
       <c r="B82" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R11" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>98361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R12" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877298</v>
+        <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98338</v>
+        <v>98244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540912</v>
+        <v>540793</v>
       </c>
       <c r="R30" t="n">
-        <v>6964122</v>
+        <v>6964055</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,6 +3468,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3494,32 +3499,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877306</v>
+        <v>125877366</v>
       </c>
       <c r="B31" t="n">
-        <v>98244</v>
+        <v>88641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540793</v>
+        <v>540874</v>
       </c>
       <c r="R31" t="n">
-        <v>6964055</v>
+        <v>6964114</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3565,11 +3570,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877366</v>
+        <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>88641</v>
+        <v>98244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540874</v>
+        <v>540803</v>
       </c>
       <c r="R32" t="n">
-        <v>6964114</v>
+        <v>6964102</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877323</v>
+        <v>125877314</v>
       </c>
       <c r="B33" t="n">
         <v>98244</v>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540803</v>
+        <v>540853</v>
       </c>
       <c r="R33" t="n">
-        <v>6964102</v>
+        <v>6964095</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877314</v>
+        <v>125877252</v>
       </c>
       <c r="B34" t="n">
         <v>98244</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540853</v>
+        <v>540788</v>
       </c>
       <c r="R34" t="n">
-        <v>6964095</v>
+        <v>6964033</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877252</v>
+        <v>125877273</v>
       </c>
       <c r="B35" t="n">
-        <v>98244</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540788</v>
+        <v>540797</v>
       </c>
       <c r="R35" t="n">
-        <v>6964033</v>
+        <v>6964057</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877273</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
         <v>80075</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540797</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964057</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877266</v>
+        <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540868</v>
+        <v>540912</v>
       </c>
       <c r="R37" t="n">
-        <v>6964062</v>
+        <v>6964122</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98361</v>
+        <v>98244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R61" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98244</v>
+        <v>98361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R62" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125877332</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125877322</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125877310</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877304</v>
+        <v>125877296</v>
       </c>
       <c r="B7" t="n">
-        <v>56834</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540740</v>
+        <v>540787</v>
       </c>
       <c r="R7" t="n">
-        <v>6964067</v>
+        <v>6964017</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877339</v>
+        <v>125877300</v>
       </c>
       <c r="B8" t="n">
-        <v>105362</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540959</v>
+        <v>540937</v>
       </c>
       <c r="R8" t="n">
-        <v>6964030</v>
+        <v>6964110</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877296</v>
+        <v>125877304</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>56834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540787</v>
+        <v>540740</v>
       </c>
       <c r="R9" t="n">
-        <v>6964017</v>
+        <v>6964067</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1430,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877300</v>
+        <v>125877339</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>105363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540937</v>
+        <v>540959</v>
       </c>
       <c r="R10" t="n">
-        <v>6964110</v>
+        <v>6964030</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>98362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R11" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R12" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877275</v>
+        <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>98245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540780</v>
+        <v>540848</v>
       </c>
       <c r="R13" t="n">
-        <v>6963983</v>
+        <v>6964091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877277</v>
+        <v>125877275</v>
       </c>
       <c r="B14" t="n">
         <v>80075</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540786</v>
+        <v>540780</v>
       </c>
       <c r="R14" t="n">
-        <v>6963974</v>
+        <v>6963983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877264</v>
+        <v>125877277</v>
       </c>
       <c r="B15" t="n">
         <v>80075</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540828</v>
+        <v>540786</v>
       </c>
       <c r="R15" t="n">
-        <v>6964037</v>
+        <v>6963974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877315</v>
+        <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540848</v>
+        <v>540828</v>
       </c>
       <c r="R16" t="n">
-        <v>6964091</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877240</v>
+        <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98359</v>
+        <v>98245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540848</v>
+        <v>540850</v>
       </c>
       <c r="R17" t="n">
-        <v>6964065</v>
+        <v>6964070</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877318</v>
+        <v>125877311</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540850</v>
+        <v>540889</v>
       </c>
       <c r="R18" t="n">
-        <v>6964070</v>
+        <v>6964139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877311</v>
+        <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98244</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540889</v>
+        <v>540848</v>
       </c>
       <c r="R19" t="n">
-        <v>6964139</v>
+        <v>6964065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125877314</v>
       </c>
       <c r="B33" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98338</v>
+        <v>98245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98244</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B41" t="n">
-        <v>98244</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R41" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B42" t="n">
-        <v>80075</v>
+        <v>98245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R42" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4674,21 +4674,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R43" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877299</v>
+        <v>125877268</v>
       </c>
       <c r="B44" t="n">
-        <v>98338</v>
+        <v>80075</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540927</v>
+        <v>540907</v>
       </c>
       <c r="R44" t="n">
-        <v>6964119</v>
+        <v>6964097</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4860,7 +4860,7 @@
         <v>125877321</v>
       </c>
       <c r="B45" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877268</v>
+        <v>125877242</v>
       </c>
       <c r="B47" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R47" t="n">
-        <v>6964097</v>
+        <v>6964019</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,10 +5148,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877242</v>
+        <v>125877243</v>
       </c>
       <c r="B48" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540803</v>
+        <v>540821</v>
       </c>
       <c r="R48" t="n">
-        <v>6964019</v>
+        <v>6964051</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877243</v>
+        <v>125877299</v>
       </c>
       <c r="B49" t="n">
-        <v>98359</v>
+        <v>98339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540821</v>
+        <v>540927</v>
       </c>
       <c r="R49" t="n">
-        <v>6964051</v>
+        <v>6964119</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B50" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R50" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B51" t="n">
-        <v>98359</v>
+        <v>80075</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R51" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877341</v>
+        <v>125877238</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540852</v>
+        <v>540793</v>
       </c>
       <c r="R52" t="n">
-        <v>6964074</v>
+        <v>6964055</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877350</v>
+        <v>125877341</v>
       </c>
       <c r="B53" t="n">
         <v>78972</v>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540785</v>
+        <v>540852</v>
       </c>
       <c r="R53" t="n">
-        <v>6964039</v>
+        <v>6964074</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877285</v>
+        <v>125877350</v>
       </c>
       <c r="B54" t="n">
-        <v>80111</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540907</v>
+        <v>540785</v>
       </c>
       <c r="R54" t="n">
-        <v>6964097</v>
+        <v>6964039</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5827,32 +5827,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877305</v>
+        <v>125877285</v>
       </c>
       <c r="B55" t="n">
-        <v>56834</v>
+        <v>80111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540783</v>
+        <v>540907</v>
       </c>
       <c r="R55" t="n">
-        <v>6964091</v>
+        <v>6964097</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,11 +5898,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5929,32 +5924,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877238</v>
+        <v>125877305</v>
       </c>
       <c r="B56" t="n">
-        <v>98361</v>
+        <v>56834</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5959,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540793</v>
+        <v>540783</v>
       </c>
       <c r="R56" t="n">
-        <v>6964055</v>
+        <v>6964091</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6000,6 +5995,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877292</v>
+        <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>80035</v>
+        <v>98245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540811</v>
+        <v>540880</v>
       </c>
       <c r="R57" t="n">
-        <v>6964057</v>
+        <v>6964142</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877294</v>
+        <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>98338</v>
+        <v>98245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540750</v>
+        <v>540792</v>
       </c>
       <c r="R58" t="n">
-        <v>6964085</v>
+        <v>6964061</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98244</v>
+        <v>98339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98244</v>
+        <v>80035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6417,7 +6417,7 @@
         <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>125877235</v>
       </c>
       <c r="B67" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B72" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7492,21 +7492,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R72" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877258</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540749</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964056</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877290</v>
+        <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>80035</v>
+        <v>98339</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540819</v>
+        <v>540970</v>
       </c>
       <c r="R74" t="n">
-        <v>6964057</v>
+        <v>6964115</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,10 +7772,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877302</v>
+        <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540970</v>
+        <v>540963</v>
       </c>
       <c r="R75" t="n">
-        <v>6964115</v>
+        <v>6964113</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877301</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>98338</v>
+        <v>80035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540963</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964113</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>125877312</v>
       </c>
       <c r="B79" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>125877297</v>
       </c>
       <c r="B80" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877313</v>
+        <v>125877295</v>
       </c>
       <c r="B20" t="n">
-        <v>98245</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540882</v>
+        <v>540765</v>
       </c>
       <c r="R20" t="n">
-        <v>6964119</v>
+        <v>6964025</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877295</v>
+        <v>125877313</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540765</v>
+        <v>540882</v>
       </c>
       <c r="R23" t="n">
-        <v>6964025</v>
+        <v>6964119</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877238</v>
+        <v>125877285</v>
       </c>
       <c r="B52" t="n">
-        <v>98362</v>
+        <v>80111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540793</v>
+        <v>540907</v>
       </c>
       <c r="R52" t="n">
-        <v>6964055</v>
+        <v>6964097</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5827,32 +5827,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877285</v>
+        <v>125877305</v>
       </c>
       <c r="B55" t="n">
-        <v>80111</v>
+        <v>56834</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540907</v>
+        <v>540783</v>
       </c>
       <c r="R55" t="n">
-        <v>6964097</v>
+        <v>6964091</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,6 +5898,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5924,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877305</v>
+        <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>56834</v>
+        <v>98362</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5959,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540783</v>
+        <v>540793</v>
       </c>
       <c r="R56" t="n">
-        <v>6964091</v>
+        <v>6964055</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -5995,11 +6000,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877344</v>
+        <v>125877302</v>
       </c>
       <c r="B72" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540975</v>
+        <v>540970</v>
       </c>
       <c r="R72" t="n">
-        <v>6964085</v>
+        <v>6964115</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877258</v>
+        <v>125877301</v>
       </c>
       <c r="B73" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540749</v>
+        <v>540963</v>
       </c>
       <c r="R73" t="n">
-        <v>6964056</v>
+        <v>6964113</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877302</v>
+        <v>125877290</v>
       </c>
       <c r="B74" t="n">
-        <v>98339</v>
+        <v>80035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540970</v>
+        <v>540819</v>
       </c>
       <c r="R74" t="n">
-        <v>6964115</v>
+        <v>6964057</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877301</v>
+        <v>125877344</v>
       </c>
       <c r="B75" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540963</v>
+        <v>540975</v>
       </c>
       <c r="R75" t="n">
-        <v>6964113</v>
+        <v>6964085</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877258</v>
       </c>
       <c r="B76" t="n">
-        <v>80035</v>
+        <v>80075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540749</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964056</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98362</v>
+        <v>98245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R11" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98245</v>
+        <v>98362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R12" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877347</v>
+        <v>125877307</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>98245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540997</v>
+        <v>540788</v>
       </c>
       <c r="R41" t="n">
-        <v>6964169</v>
+        <v>6964042</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>98245</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R42" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877285</v>
+        <v>125877305</v>
       </c>
       <c r="B52" t="n">
-        <v>80111</v>
+        <v>56834</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540907</v>
+        <v>540783</v>
       </c>
       <c r="R52" t="n">
-        <v>6964097</v>
+        <v>6964091</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5607,6 +5607,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5827,32 +5832,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877305</v>
+        <v>125877285</v>
       </c>
       <c r="B55" t="n">
-        <v>56834</v>
+        <v>80111</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540783</v>
+        <v>540907</v>
       </c>
       <c r="R55" t="n">
-        <v>6964091</v>
+        <v>6964097</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,11 +5903,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877297</v>
+        <v>125877272</v>
       </c>
       <c r="B80" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540874</v>
+        <v>540806</v>
       </c>
       <c r="R80" t="n">
-        <v>6964063</v>
+        <v>6964062</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877272</v>
+        <v>125877274</v>
       </c>
       <c r="B81" t="n">
         <v>80075</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540806</v>
+        <v>540794</v>
       </c>
       <c r="R81" t="n">
-        <v>6964062</v>
+        <v>6964003</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877274</v>
+        <v>125877297</v>
       </c>
       <c r="B82" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540794</v>
+        <v>540874</v>
       </c>
       <c r="R82" t="n">
-        <v>6964003</v>
+        <v>6964063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877332</v>
+        <v>125877322</v>
       </c>
       <c r="B2" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540794</v>
+        <v>540809</v>
       </c>
       <c r="R2" t="n">
-        <v>6964056</v>
+        <v>6964096</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877322</v>
+        <v>125877332</v>
       </c>
       <c r="B3" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540809</v>
+        <v>540794</v>
       </c>
       <c r="R3" t="n">
-        <v>6964096</v>
+        <v>6964056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,7 +872,7 @@
         <v>125877310</v>
       </c>
       <c r="B4" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877259</v>
+        <v>125877271</v>
       </c>
       <c r="B5" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540760</v>
+        <v>540996</v>
       </c>
       <c r="R5" t="n">
-        <v>6964020</v>
+        <v>6964140</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877271</v>
+        <v>125877304</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>56835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540996</v>
+        <v>540740</v>
       </c>
       <c r="R6" t="n">
-        <v>6964140</v>
+        <v>6964067</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1134,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1163,7 +1168,7 @@
         <v>125877296</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1265,7 @@
         <v>125877300</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877304</v>
+        <v>125877259</v>
       </c>
       <c r="B9" t="n">
-        <v>56834</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540740</v>
+        <v>540760</v>
       </c>
       <c r="R9" t="n">
-        <v>6964067</v>
+        <v>6964020</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1425,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,7 +1459,7 @@
         <v>125877339</v>
       </c>
       <c r="B10" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125877275</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125877277</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877318</v>
+        <v>125877240</v>
       </c>
       <c r="B17" t="n">
-        <v>98245</v>
+        <v>98362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540850</v>
+        <v>540848</v>
       </c>
       <c r="R17" t="n">
-        <v>6964070</v>
+        <v>6964065</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877311</v>
+        <v>125877318</v>
       </c>
       <c r="B18" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540889</v>
+        <v>540850</v>
       </c>
       <c r="R18" t="n">
-        <v>6964139</v>
+        <v>6964070</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877240</v>
+        <v>125877311</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540848</v>
+        <v>540889</v>
       </c>
       <c r="R19" t="n">
-        <v>6964065</v>
+        <v>6964139</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2408,7 +2409,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>125877295</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877284</v>
+        <v>125877313</v>
       </c>
       <c r="B21" t="n">
-        <v>80111</v>
+        <v>98247</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R21" t="n">
-        <v>6964031</v>
+        <v>6964119</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877260</v>
+        <v>125877284</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540800</v>
+        <v>540807</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964031</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877313</v>
+        <v>125877260</v>
       </c>
       <c r="B23" t="n">
-        <v>98245</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540882</v>
+        <v>540800</v>
       </c>
       <c r="R23" t="n">
-        <v>6964119</v>
+        <v>6964021</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2818,7 +2818,7 @@
         <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>125877276</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>125877278</v>
       </c>
       <c r="B26" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>125877269</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>125877261</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>125877291</v>
       </c>
       <c r="B29" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877366</v>
+        <v>125877273</v>
       </c>
       <c r="B31" t="n">
-        <v>88641</v>
+        <v>80076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540874</v>
+        <v>540797</v>
       </c>
       <c r="R31" t="n">
-        <v>6964114</v>
+        <v>6964057</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877323</v>
+        <v>125877266</v>
       </c>
       <c r="B32" t="n">
-        <v>98245</v>
+        <v>80076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540803</v>
+        <v>540868</v>
       </c>
       <c r="R32" t="n">
-        <v>6964102</v>
+        <v>6964062</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877314</v>
+        <v>125877366</v>
       </c>
       <c r="B33" t="n">
-        <v>98245</v>
+        <v>88643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540853</v>
+        <v>540874</v>
       </c>
       <c r="R33" t="n">
-        <v>6964095</v>
+        <v>6964114</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877252</v>
+        <v>125877323</v>
       </c>
       <c r="B34" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540788</v>
+        <v>540803</v>
       </c>
       <c r="R34" t="n">
-        <v>6964033</v>
+        <v>6964102</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877273</v>
+        <v>125877314</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>98247</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540797</v>
+        <v>540853</v>
       </c>
       <c r="R35" t="n">
-        <v>6964057</v>
+        <v>6964095</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,32 +3984,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877252</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>98247</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540788</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964033</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4084,7 +4084,7 @@
         <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877303</v>
       </c>
       <c r="B38" t="n">
-        <v>98245</v>
+        <v>98341</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540785</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6963977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877335</v>
       </c>
       <c r="B39" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540781</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877317</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98247</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540850</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B41" t="n">
-        <v>98245</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R41" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R42" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>80075</v>
+        <v>98247</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R43" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877268</v>
+        <v>125877242</v>
       </c>
       <c r="B44" t="n">
-        <v>80075</v>
+        <v>98362</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R44" t="n">
-        <v>6964097</v>
+        <v>6964019</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877321</v>
+        <v>125877243</v>
       </c>
       <c r="B45" t="n">
-        <v>98245</v>
+        <v>98362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4868,21 +4868,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540855</v>
+        <v>540821</v>
       </c>
       <c r="R45" t="n">
-        <v>6964125</v>
+        <v>6964051</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,10 +4954,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877316</v>
+        <v>125877321</v>
       </c>
       <c r="B46" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540803</v>
+        <v>540855</v>
       </c>
       <c r="R46" t="n">
-        <v>6964060</v>
+        <v>6964125</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,10 +5051,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877242</v>
+        <v>125877316</v>
       </c>
       <c r="B47" t="n">
-        <v>98360</v>
+        <v>98247</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5062,21 +5062,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
         <v>540803</v>
       </c>
       <c r="R47" t="n">
-        <v>6964019</v>
+        <v>6964060</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,32 +5148,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877243</v>
+        <v>125877268</v>
       </c>
       <c r="B48" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540821</v>
+        <v>540907</v>
       </c>
       <c r="R48" t="n">
-        <v>6964051</v>
+        <v>6964097</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5248,7 +5248,7 @@
         <v>125877299</v>
       </c>
       <c r="B49" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B50" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R50" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>80075</v>
+        <v>98362</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R51" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877305</v>
+        <v>125877341</v>
       </c>
       <c r="B52" t="n">
-        <v>56834</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540783</v>
+        <v>540852</v>
       </c>
       <c r="R52" t="n">
-        <v>6964091</v>
+        <v>6964074</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5607,11 +5607,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5638,10 +5633,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877341</v>
+        <v>125877350</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5673,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540852</v>
+        <v>540785</v>
       </c>
       <c r="R53" t="n">
-        <v>6964074</v>
+        <v>6964039</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877350</v>
+        <v>125877285</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>80112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540785</v>
+        <v>540907</v>
       </c>
       <c r="R54" t="n">
-        <v>6964039</v>
+        <v>6964097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,32 +5827,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877285</v>
+        <v>125877305</v>
       </c>
       <c r="B55" t="n">
-        <v>80111</v>
+        <v>56835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540907</v>
+        <v>540783</v>
       </c>
       <c r="R55" t="n">
-        <v>6964097</v>
+        <v>6964091</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5903,6 +5898,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5932,7 +5932,7 @@
         <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877326</v>
+        <v>125877235</v>
       </c>
       <c r="B63" t="n">
-        <v>98245</v>
+        <v>98364</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540801</v>
+        <v>540804</v>
       </c>
       <c r="R63" t="n">
-        <v>6964059</v>
+        <v>6964049</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877279</v>
+        <v>125877326</v>
       </c>
       <c r="B64" t="n">
-        <v>80075</v>
+        <v>98247</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540793</v>
+        <v>540801</v>
       </c>
       <c r="R64" t="n">
-        <v>6963960</v>
+        <v>6964059</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B65" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R65" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B66" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R66" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877235</v>
+        <v>125877262</v>
       </c>
       <c r="B67" t="n">
-        <v>98362</v>
+        <v>80076</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540804</v>
+        <v>540818</v>
       </c>
       <c r="R67" t="n">
-        <v>6964049</v>
+        <v>6964054</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7096,7 +7096,7 @@
         <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877302</v>
+        <v>125877344</v>
       </c>
       <c r="B72" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540970</v>
+        <v>540975</v>
       </c>
       <c r="R72" t="n">
-        <v>6964115</v>
+        <v>6964085</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877301</v>
+        <v>125877258</v>
       </c>
       <c r="B73" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540963</v>
+        <v>540749</v>
       </c>
       <c r="R73" t="n">
-        <v>6964113</v>
+        <v>6964056</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877290</v>
+        <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>80035</v>
+        <v>98341</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540819</v>
+        <v>540970</v>
       </c>
       <c r="R74" t="n">
-        <v>6964057</v>
+        <v>6964115</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877344</v>
+        <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540975</v>
+        <v>540963</v>
       </c>
       <c r="R75" t="n">
-        <v>6964085</v>
+        <v>6964113</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877258</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>80075</v>
+        <v>80036</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540749</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964056</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877232</v>
+        <v>125877312</v>
       </c>
       <c r="B78" t="n">
-        <v>91232</v>
+        <v>98247</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540989</v>
+        <v>540881</v>
       </c>
       <c r="R78" t="n">
-        <v>6964130</v>
+        <v>6964135</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877312</v>
+        <v>125877232</v>
       </c>
       <c r="B79" t="n">
-        <v>98245</v>
+        <v>91234</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540881</v>
+        <v>540989</v>
       </c>
       <c r="R79" t="n">
-        <v>6964135</v>
+        <v>6964130</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8260,7 +8260,7 @@
         <v>125877272</v>
       </c>
       <c r="B80" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>125877274</v>
       </c>
       <c r="B81" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877297</v>
+        <v>125877241</v>
       </c>
       <c r="B82" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540874</v>
+        <v>540752</v>
       </c>
       <c r="R82" t="n">
-        <v>6964063</v>
+        <v>6964040</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877241</v>
+        <v>125877245</v>
       </c>
       <c r="B83" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540752</v>
+        <v>540964</v>
       </c>
       <c r="R83" t="n">
-        <v>6964040</v>
+        <v>6964121</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877245</v>
+        <v>125877297</v>
       </c>
       <c r="B84" t="n">
-        <v>98360</v>
+        <v>98341</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540964</v>
+        <v>540874</v>
       </c>
       <c r="R84" t="n">
-        <v>6964121</v>
+        <v>6964063</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B11" t="n">
-        <v>98247</v>
+        <v>98364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R11" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B12" t="n">
-        <v>98364</v>
+        <v>98247</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R12" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877295</v>
+        <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>98247</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540765</v>
+        <v>540882</v>
       </c>
       <c r="R20" t="n">
-        <v>6964025</v>
+        <v>6964119</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877313</v>
+        <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>98247</v>
+        <v>80112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R21" t="n">
-        <v>6964119</v>
+        <v>6964031</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877284</v>
+        <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540807</v>
+        <v>540800</v>
       </c>
       <c r="R22" t="n">
-        <v>6964031</v>
+        <v>6964021</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877260</v>
+        <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540800</v>
+        <v>540765</v>
       </c>
       <c r="R23" t="n">
-        <v>6964021</v>
+        <v>6964025</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98341</v>
+        <v>98247</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
         <v>98247</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98247</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877341</v>
+        <v>125877305</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>56835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540852</v>
+        <v>540783</v>
       </c>
       <c r="R52" t="n">
-        <v>6964074</v>
+        <v>6964091</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5607,6 +5607,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5633,7 +5638,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877350</v>
+        <v>125877341</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5668,10 +5673,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540785</v>
+        <v>540852</v>
       </c>
       <c r="R53" t="n">
-        <v>6964039</v>
+        <v>6964074</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5735,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877285</v>
+        <v>125877350</v>
       </c>
       <c r="B54" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5770,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540907</v>
+        <v>540785</v>
       </c>
       <c r="R54" t="n">
-        <v>6964097</v>
+        <v>6964039</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5827,32 +5832,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877305</v>
+        <v>125877285</v>
       </c>
       <c r="B55" t="n">
-        <v>56835</v>
+        <v>80112</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5867,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540783</v>
+        <v>540907</v>
       </c>
       <c r="R55" t="n">
-        <v>6964091</v>
+        <v>6964097</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,11 +5903,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B57" t="n">
-        <v>98247</v>
+        <v>98341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R57" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B58" t="n">
-        <v>98247</v>
+        <v>80036</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R58" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B59" t="n">
-        <v>98341</v>
+        <v>98247</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B60" t="n">
-        <v>80036</v>
+        <v>98247</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877235</v>
+        <v>125877246</v>
       </c>
       <c r="B63" t="n">
-        <v>98364</v>
+        <v>98362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540804</v>
+        <v>540789</v>
       </c>
       <c r="R63" t="n">
-        <v>6964049</v>
+        <v>6964012</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877326</v>
+        <v>125877235</v>
       </c>
       <c r="B64" t="n">
-        <v>98247</v>
+        <v>98364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6716,21 +6716,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540801</v>
+        <v>540804</v>
       </c>
       <c r="R64" t="n">
-        <v>6964059</v>
+        <v>6964049</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,32 +6802,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877279</v>
+        <v>125877326</v>
       </c>
       <c r="B65" t="n">
-        <v>80076</v>
+        <v>98247</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540793</v>
+        <v>540801</v>
       </c>
       <c r="R65" t="n">
-        <v>6963960</v>
+        <v>6964059</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,7 +6899,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B66" t="n">
         <v>80076</v>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R66" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B67" t="n">
         <v>80076</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R67" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,32 +7093,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877262</v>
       </c>
       <c r="B68" t="n">
-        <v>98362</v>
+        <v>80076</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540818</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964054</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877354</v>
+        <v>125877247</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>98362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540781</v>
+        <v>540780</v>
       </c>
       <c r="R69" t="n">
-        <v>6963980</v>
+        <v>6963984</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877270</v>
+        <v>125877354</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540970</v>
+        <v>540781</v>
       </c>
       <c r="R70" t="n">
-        <v>6964115</v>
+        <v>6963980</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877247</v>
+        <v>125877270</v>
       </c>
       <c r="B71" t="n">
-        <v>98362</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540780</v>
+        <v>540970</v>
       </c>
       <c r="R71" t="n">
-        <v>6963984</v>
+        <v>6964115</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877302</v>
+        <v>125877290</v>
       </c>
       <c r="B74" t="n">
-        <v>98341</v>
+        <v>80036</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540970</v>
+        <v>540819</v>
       </c>
       <c r="R74" t="n">
-        <v>6964115</v>
+        <v>6964057</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,7 +7772,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877301</v>
+        <v>125877302</v>
       </c>
       <c r="B75" t="n">
         <v>98341</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540963</v>
+        <v>540970</v>
       </c>
       <c r="R75" t="n">
-        <v>6964113</v>
+        <v>6964115</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877301</v>
       </c>
       <c r="B76" t="n">
-        <v>80036</v>
+        <v>98341</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540963</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964113</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877322</v>
+        <v>125877304</v>
       </c>
       <c r="B2" t="n">
-        <v>98247</v>
+        <v>56835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>504</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540809</v>
+        <v>540740</v>
       </c>
       <c r="R2" t="n">
-        <v>6964096</v>
+        <v>6964067</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877332</v>
+        <v>125877296</v>
       </c>
       <c r="B3" t="n">
-        <v>98247</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540794</v>
+        <v>540787</v>
       </c>
       <c r="R3" t="n">
-        <v>6964056</v>
+        <v>6964017</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877310</v>
+        <v>125877300</v>
       </c>
       <c r="B4" t="n">
-        <v>98247</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540890</v>
+        <v>540937</v>
       </c>
       <c r="R4" t="n">
-        <v>6964145</v>
+        <v>6964110</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877271</v>
+        <v>125877339</v>
       </c>
       <c r="B5" t="n">
-        <v>80076</v>
+        <v>105367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540996</v>
+        <v>540959</v>
       </c>
       <c r="R5" t="n">
-        <v>6964140</v>
+        <v>6964030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877304</v>
+        <v>125877332</v>
       </c>
       <c r="B6" t="n">
-        <v>56835</v>
+        <v>98249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540740</v>
+        <v>540794</v>
       </c>
       <c r="R6" t="n">
-        <v>6964067</v>
+        <v>6964056</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877296</v>
+        <v>125877322</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540787</v>
+        <v>540809</v>
       </c>
       <c r="R7" t="n">
-        <v>6964017</v>
+        <v>6964096</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877300</v>
+        <v>125877310</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540937</v>
+        <v>540890</v>
       </c>
       <c r="R8" t="n">
-        <v>6964110</v>
+        <v>6964145</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877339</v>
+        <v>125877271</v>
       </c>
       <c r="B10" t="n">
-        <v>105365</v>
+        <v>80076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540959</v>
+        <v>540996</v>
       </c>
       <c r="R10" t="n">
-        <v>6964030</v>
+        <v>6964140</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98364</v>
+        <v>98249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R11" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98247</v>
+        <v>98366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R12" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1750,7 +1750,7 @@
         <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125877240</v>
       </c>
       <c r="B17" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>125877318</v>
       </c>
       <c r="B18" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>125877311</v>
       </c>
       <c r="B19" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877313</v>
+        <v>125877284</v>
       </c>
       <c r="B20" t="n">
-        <v>98247</v>
+        <v>80112</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R20" t="n">
-        <v>6964119</v>
+        <v>6964031</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877284</v>
+        <v>125877260</v>
       </c>
       <c r="B21" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540807</v>
+        <v>540800</v>
       </c>
       <c r="R21" t="n">
-        <v>6964031</v>
+        <v>6964021</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877260</v>
+        <v>125877313</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>98249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540800</v>
+        <v>540882</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964119</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877273</v>
+        <v>125877366</v>
       </c>
       <c r="B31" t="n">
-        <v>80076</v>
+        <v>88645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540797</v>
+        <v>540874</v>
       </c>
       <c r="R31" t="n">
-        <v>6964057</v>
+        <v>6964114</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877266</v>
+        <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>80076</v>
+        <v>98249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540868</v>
+        <v>540803</v>
       </c>
       <c r="R32" t="n">
-        <v>6964062</v>
+        <v>6964102</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877366</v>
+        <v>125877314</v>
       </c>
       <c r="B33" t="n">
-        <v>88643</v>
+        <v>98249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540874</v>
+        <v>540853</v>
       </c>
       <c r="R33" t="n">
-        <v>6964114</v>
+        <v>6964095</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877323</v>
+        <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540803</v>
+        <v>540788</v>
       </c>
       <c r="R34" t="n">
-        <v>6964102</v>
+        <v>6964033</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877314</v>
+        <v>125877273</v>
       </c>
       <c r="B35" t="n">
-        <v>98247</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540853</v>
+        <v>540797</v>
       </c>
       <c r="R35" t="n">
-        <v>6964095</v>
+        <v>6964057</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,32 +3984,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877252</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
-        <v>98247</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540788</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964033</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4084,7 +4084,7 @@
         <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877303</v>
       </c>
       <c r="B38" t="n">
-        <v>98247</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540785</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6963977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877335</v>
       </c>
       <c r="B39" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540781</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877317</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540850</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R41" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877267</v>
+        <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540893</v>
+        <v>540997</v>
       </c>
       <c r="R42" t="n">
-        <v>6964069</v>
+        <v>6964169</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4666,7 +4666,7 @@
         <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877242</v>
+        <v>125877321</v>
       </c>
       <c r="B44" t="n">
-        <v>98362</v>
+        <v>98249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4771,21 +4771,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540803</v>
+        <v>540855</v>
       </c>
       <c r="R44" t="n">
-        <v>6964019</v>
+        <v>6964125</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877243</v>
+        <v>125877316</v>
       </c>
       <c r="B45" t="n">
-        <v>98362</v>
+        <v>98249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4868,21 +4868,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540821</v>
+        <v>540803</v>
       </c>
       <c r="R45" t="n">
-        <v>6964051</v>
+        <v>6964060</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877321</v>
+        <v>125877268</v>
       </c>
       <c r="B46" t="n">
-        <v>98247</v>
+        <v>80076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540855</v>
+        <v>540907</v>
       </c>
       <c r="R46" t="n">
-        <v>6964125</v>
+        <v>6964097</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877316</v>
+        <v>125877299</v>
       </c>
       <c r="B47" t="n">
-        <v>98247</v>
+        <v>98343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540803</v>
+        <v>540927</v>
       </c>
       <c r="R47" t="n">
-        <v>6964060</v>
+        <v>6964119</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,32 +5148,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877268</v>
+        <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R48" t="n">
-        <v>6964097</v>
+        <v>6964019</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877299</v>
+        <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540927</v>
+        <v>540821</v>
       </c>
       <c r="R49" t="n">
-        <v>6964119</v>
+        <v>6964051</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5442,7 +5442,7 @@
         <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98341</v>
+        <v>98249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R57" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>80036</v>
+        <v>98249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R58" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98247</v>
+        <v>98343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98247</v>
+        <v>80036</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B61" t="n">
-        <v>98247</v>
+        <v>98366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R61" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B62" t="n">
-        <v>98364</v>
+        <v>98249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R62" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877246</v>
+        <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>98362</v>
+        <v>98249</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540789</v>
+        <v>540801</v>
       </c>
       <c r="R63" t="n">
-        <v>6964012</v>
+        <v>6964059</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877235</v>
+        <v>125877282</v>
       </c>
       <c r="B64" t="n">
-        <v>98364</v>
+        <v>80076</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540804</v>
+        <v>540758</v>
       </c>
       <c r="R64" t="n">
-        <v>6964049</v>
+        <v>6963956</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,32 +6802,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B65" t="n">
-        <v>98247</v>
+        <v>80076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R65" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877282</v>
+        <v>125877235</v>
       </c>
       <c r="B67" t="n">
-        <v>80076</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540758</v>
+        <v>540804</v>
       </c>
       <c r="R67" t="n">
-        <v>6963956</v>
+        <v>6964049</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,32 +7093,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877262</v>
+        <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540818</v>
+        <v>540789</v>
       </c>
       <c r="R68" t="n">
-        <v>6964054</v>
+        <v>6964012</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877247</v>
+        <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540780</v>
+        <v>540781</v>
       </c>
       <c r="R69" t="n">
-        <v>6963984</v>
+        <v>6963980</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R70" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877270</v>
+        <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540970</v>
+        <v>540780</v>
       </c>
       <c r="R71" t="n">
-        <v>6964115</v>
+        <v>6963984</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877344</v>
+        <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7492,21 +7492,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540975</v>
+        <v>540749</v>
       </c>
       <c r="R72" t="n">
-        <v>6964085</v>
+        <v>6964056</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R73" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877290</v>
+        <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>80036</v>
+        <v>98343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540819</v>
+        <v>540970</v>
       </c>
       <c r="R74" t="n">
-        <v>6964057</v>
+        <v>6964115</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,10 +7772,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877302</v>
+        <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540970</v>
+        <v>540963</v>
       </c>
       <c r="R75" t="n">
-        <v>6964115</v>
+        <v>6964113</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877301</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>98341</v>
+        <v>80036</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540963</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964113</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877312</v>
+        <v>125877232</v>
       </c>
       <c r="B78" t="n">
-        <v>98247</v>
+        <v>91236</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>504</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540881</v>
+        <v>540989</v>
       </c>
       <c r="R78" t="n">
-        <v>6964135</v>
+        <v>6964130</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877232</v>
+        <v>125877312</v>
       </c>
       <c r="B79" t="n">
-        <v>91234</v>
+        <v>98249</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540989</v>
+        <v>540881</v>
       </c>
       <c r="R79" t="n">
-        <v>6964130</v>
+        <v>6964135</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877241</v>
+        <v>125877297</v>
       </c>
       <c r="B82" t="n">
-        <v>98362</v>
+        <v>98343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540752</v>
+        <v>540874</v>
       </c>
       <c r="R82" t="n">
-        <v>6964040</v>
+        <v>6964063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877245</v>
+        <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540964</v>
+        <v>540752</v>
       </c>
       <c r="R83" t="n">
-        <v>6964121</v>
+        <v>6964040</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877297</v>
+        <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540874</v>
+        <v>540964</v>
       </c>
       <c r="R84" t="n">
-        <v>6964063</v>
+        <v>6964121</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877284</v>
+        <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>80112</v>
+        <v>98249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R20" t="n">
-        <v>6964031</v>
+        <v>6964119</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877260</v>
+        <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540800</v>
+        <v>540807</v>
       </c>
       <c r="R21" t="n">
-        <v>6964021</v>
+        <v>6964031</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877313</v>
+        <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540882</v>
+        <v>540800</v>
       </c>
       <c r="R22" t="n">
-        <v>6964119</v>
+        <v>6964021</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3499,32 +3499,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877366</v>
+        <v>125877314</v>
       </c>
       <c r="B31" t="n">
-        <v>88645</v>
+        <v>98249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540874</v>
+        <v>540853</v>
       </c>
       <c r="R31" t="n">
-        <v>6964114</v>
+        <v>6964095</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877323</v>
+        <v>125877252</v>
       </c>
       <c r="B32" t="n">
         <v>98249</v>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540803</v>
+        <v>540788</v>
       </c>
       <c r="R32" t="n">
-        <v>6964102</v>
+        <v>6964033</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877314</v>
+        <v>125877273</v>
       </c>
       <c r="B33" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540853</v>
+        <v>540797</v>
       </c>
       <c r="R33" t="n">
-        <v>6964095</v>
+        <v>6964057</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877252</v>
+        <v>125877266</v>
       </c>
       <c r="B34" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540788</v>
+        <v>540868</v>
       </c>
       <c r="R34" t="n">
-        <v>6964033</v>
+        <v>6964062</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877273</v>
+        <v>125877298</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540797</v>
+        <v>540912</v>
       </c>
       <c r="R35" t="n">
-        <v>6964057</v>
+        <v>6964122</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877366</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>88645</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540874</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964114</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877298</v>
+        <v>125877323</v>
       </c>
       <c r="B37" t="n">
-        <v>98343</v>
+        <v>98249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540912</v>
+        <v>540803</v>
       </c>
       <c r="R37" t="n">
-        <v>6964122</v>
+        <v>6964102</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98343</v>
+        <v>98249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
         <v>98249</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98249</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877347</v>
+        <v>125877307</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>98249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540997</v>
+        <v>540788</v>
       </c>
       <c r="R42" t="n">
-        <v>6964169</v>
+        <v>6964042</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B43" t="n">
-        <v>98249</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R43" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877321</v>
+        <v>125877299</v>
       </c>
       <c r="B44" t="n">
-        <v>98249</v>
+        <v>98343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540855</v>
+        <v>540927</v>
       </c>
       <c r="R44" t="n">
-        <v>6964125</v>
+        <v>6964119</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877316</v>
+        <v>125877321</v>
       </c>
       <c r="B45" t="n">
         <v>98249</v>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540803</v>
+        <v>540855</v>
       </c>
       <c r="R45" t="n">
-        <v>6964060</v>
+        <v>6964125</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877268</v>
+        <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>80076</v>
+        <v>98249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R46" t="n">
-        <v>6964097</v>
+        <v>6964060</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877299</v>
+        <v>125877268</v>
       </c>
       <c r="B47" t="n">
-        <v>98343</v>
+        <v>80076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540927</v>
+        <v>540907</v>
       </c>
       <c r="R47" t="n">
-        <v>6964119</v>
+        <v>6964097</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B64" t="n">
         <v>80076</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R64" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B65" t="n">
         <v>80076</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R65" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,7 +6899,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877279</v>
+        <v>125877262</v>
       </c>
       <c r="B66" t="n">
         <v>80076</v>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540793</v>
+        <v>540818</v>
       </c>
       <c r="R66" t="n">
-        <v>6963960</v>
+        <v>6964054</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877235</v>
+        <v>125877246</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>98364</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540804</v>
+        <v>540789</v>
       </c>
       <c r="R67" t="n">
-        <v>6964049</v>
+        <v>6964012</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877235</v>
       </c>
       <c r="B68" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540804</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964049</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877354</v>
+        <v>125877247</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540781</v>
+        <v>540780</v>
       </c>
       <c r="R69" t="n">
-        <v>6963980</v>
+        <v>6963984</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877270</v>
+        <v>125877354</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540970</v>
+        <v>540781</v>
       </c>
       <c r="R70" t="n">
-        <v>6964115</v>
+        <v>6963980</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877247</v>
+        <v>125877270</v>
       </c>
       <c r="B71" t="n">
-        <v>98364</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540780</v>
+        <v>540970</v>
       </c>
       <c r="R71" t="n">
-        <v>6963984</v>
+        <v>6964115</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877258</v>
+        <v>125877290</v>
       </c>
       <c r="B72" t="n">
-        <v>80076</v>
+        <v>80036</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540749</v>
+        <v>540819</v>
       </c>
       <c r="R72" t="n">
-        <v>6964056</v>
+        <v>6964057</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877258</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540749</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964056</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877302</v>
+        <v>125877344</v>
       </c>
       <c r="B74" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540970</v>
+        <v>540975</v>
       </c>
       <c r="R74" t="n">
-        <v>6964115</v>
+        <v>6964085</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,7 +7772,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877301</v>
+        <v>125877302</v>
       </c>
       <c r="B75" t="n">
         <v>98343</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540963</v>
+        <v>540970</v>
       </c>
       <c r="R75" t="n">
-        <v>6964113</v>
+        <v>6964115</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877301</v>
       </c>
       <c r="B76" t="n">
-        <v>80036</v>
+        <v>98343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540963</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964113</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8257,7 +8257,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877272</v>
+        <v>125877274</v>
       </c>
       <c r="B80" t="n">
         <v>80076</v>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540806</v>
+        <v>540794</v>
       </c>
       <c r="R80" t="n">
-        <v>6964062</v>
+        <v>6964003</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877274</v>
+        <v>125877272</v>
       </c>
       <c r="B81" t="n">
         <v>80076</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540794</v>
+        <v>540806</v>
       </c>
       <c r="R81" t="n">
-        <v>6964003</v>
+        <v>6964062</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877296</v>
+        <v>125877332</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98251</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540787</v>
+        <v>540794</v>
       </c>
       <c r="R3" t="n">
-        <v>6964017</v>
+        <v>6964056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877300</v>
+        <v>125877322</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540937</v>
+        <v>540809</v>
       </c>
       <c r="R4" t="n">
-        <v>6964110</v>
+        <v>6964096</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877339</v>
+        <v>125877310</v>
       </c>
       <c r="B5" t="n">
-        <v>105367</v>
+        <v>98251</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540959</v>
+        <v>540890</v>
       </c>
       <c r="R5" t="n">
-        <v>6964030</v>
+        <v>6964145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877332</v>
+        <v>125877259</v>
       </c>
       <c r="B6" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540794</v>
+        <v>540760</v>
       </c>
       <c r="R6" t="n">
-        <v>6964056</v>
+        <v>6964020</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877322</v>
+        <v>125877271</v>
       </c>
       <c r="B7" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540809</v>
+        <v>540996</v>
       </c>
       <c r="R7" t="n">
-        <v>6964096</v>
+        <v>6964140</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877310</v>
+        <v>125877339</v>
       </c>
       <c r="B8" t="n">
-        <v>98249</v>
+        <v>105371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540890</v>
+        <v>540959</v>
       </c>
       <c r="R8" t="n">
-        <v>6964145</v>
+        <v>6964030</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877259</v>
+        <v>125877296</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540760</v>
+        <v>540787</v>
       </c>
       <c r="R9" t="n">
-        <v>6964020</v>
+        <v>6964017</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877271</v>
+        <v>125877300</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540996</v>
+        <v>540937</v>
       </c>
       <c r="R10" t="n">
-        <v>6964140</v>
+        <v>6964110</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B11" t="n">
-        <v>98249</v>
+        <v>98368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R11" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B12" t="n">
-        <v>98366</v>
+        <v>98251</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R12" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877315</v>
+        <v>125877275</v>
       </c>
       <c r="B13" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540848</v>
+        <v>540780</v>
       </c>
       <c r="R13" t="n">
-        <v>6964091</v>
+        <v>6963983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877275</v>
+        <v>125877277</v>
       </c>
       <c r="B14" t="n">
         <v>80076</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540780</v>
+        <v>540786</v>
       </c>
       <c r="R14" t="n">
-        <v>6963983</v>
+        <v>6963974</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877277</v>
+        <v>125877264</v>
       </c>
       <c r="B15" t="n">
         <v>80076</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540786</v>
+        <v>540828</v>
       </c>
       <c r="R15" t="n">
-        <v>6963974</v>
+        <v>6964037</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877264</v>
+        <v>125877315</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>98251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540828</v>
+        <v>540848</v>
       </c>
       <c r="R16" t="n">
-        <v>6964037</v>
+        <v>6964091</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877240</v>
+        <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98364</v>
+        <v>98251</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540848</v>
+        <v>540850</v>
       </c>
       <c r="R17" t="n">
-        <v>6964065</v>
+        <v>6964070</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877318</v>
+        <v>125877311</v>
       </c>
       <c r="B18" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540850</v>
+        <v>540889</v>
       </c>
       <c r="R18" t="n">
-        <v>6964070</v>
+        <v>6964139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877311</v>
+        <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98249</v>
+        <v>98366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540889</v>
+        <v>540848</v>
       </c>
       <c r="R19" t="n">
-        <v>6964139</v>
+        <v>6964065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877320</v>
+        <v>125877276</v>
       </c>
       <c r="B24" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540882</v>
+        <v>540785</v>
       </c>
       <c r="R24" t="n">
-        <v>6964142</v>
+        <v>6963977</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877276</v>
+        <v>125877278</v>
       </c>
       <c r="B25" t="n">
         <v>80076</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540785</v>
+        <v>540790</v>
       </c>
       <c r="R25" t="n">
-        <v>6963977</v>
+        <v>6963972</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877278</v>
+        <v>125877269</v>
       </c>
       <c r="B26" t="n">
         <v>80076</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540790</v>
+        <v>540964</v>
       </c>
       <c r="R26" t="n">
-        <v>6963972</v>
+        <v>6964121</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877269</v>
+        <v>125877261</v>
       </c>
       <c r="B27" t="n">
         <v>80076</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540964</v>
+        <v>540807</v>
       </c>
       <c r="R27" t="n">
-        <v>6964121</v>
+        <v>6964030</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877261</v>
+        <v>125877320</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>98251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R28" t="n">
-        <v>6964030</v>
+        <v>6964142</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877306</v>
+        <v>125877314</v>
       </c>
       <c r="B30" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540793</v>
+        <v>540853</v>
       </c>
       <c r="R30" t="n">
-        <v>6964055</v>
+        <v>6964095</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,11 +3468,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3499,10 +3494,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877314</v>
+        <v>125877306</v>
       </c>
       <c r="B31" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540853</v>
+        <v>540793</v>
       </c>
       <c r="R31" t="n">
-        <v>6964095</v>
+        <v>6964055</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3570,6 +3565,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877252</v>
+        <v>125877366</v>
       </c>
       <c r="B32" t="n">
-        <v>98249</v>
+        <v>88647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540788</v>
+        <v>540874</v>
       </c>
       <c r="R32" t="n">
-        <v>6964033</v>
+        <v>6964114</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877273</v>
+        <v>125877323</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>98251</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540797</v>
+        <v>540803</v>
       </c>
       <c r="R33" t="n">
-        <v>6964057</v>
+        <v>6964102</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877266</v>
+        <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>98251</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540868</v>
+        <v>540788</v>
       </c>
       <c r="R34" t="n">
-        <v>6964062</v>
+        <v>6964033</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3890,7 +3890,7 @@
         <v>125877298</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877366</v>
+        <v>125877273</v>
       </c>
       <c r="B36" t="n">
-        <v>88645</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540874</v>
+        <v>540797</v>
       </c>
       <c r="R36" t="n">
-        <v>6964114</v>
+        <v>6964057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877323</v>
+        <v>125877266</v>
       </c>
       <c r="B37" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540803</v>
+        <v>540868</v>
       </c>
       <c r="R37" t="n">
-        <v>6964102</v>
+        <v>6964062</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4181,7 +4181,7 @@
         <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>125877317</v>
       </c>
       <c r="B39" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>98249</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R42" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877347</v>
+        <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>98251</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540997</v>
+        <v>540788</v>
       </c>
       <c r="R43" t="n">
-        <v>6964169</v>
+        <v>6964042</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4763,7 +4763,7 @@
         <v>125877299</v>
       </c>
       <c r="B44" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>125877321</v>
       </c>
       <c r="B45" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5536,10 +5536,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877305</v>
+        <v>125877341</v>
       </c>
       <c r="B52" t="n">
-        <v>56835</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5547,21 +5547,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540783</v>
+        <v>540852</v>
       </c>
       <c r="R52" t="n">
-        <v>6964091</v>
+        <v>6964074</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5607,11 +5607,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5638,7 +5633,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877341</v>
+        <v>125877350</v>
       </c>
       <c r="B53" t="n">
         <v>78973</v>
@@ -5673,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540852</v>
+        <v>540785</v>
       </c>
       <c r="R53" t="n">
-        <v>6964074</v>
+        <v>6964039</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5735,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877350</v>
+        <v>125877285</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5770,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540785</v>
+        <v>540907</v>
       </c>
       <c r="R54" t="n">
-        <v>6964039</v>
+        <v>6964097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5832,10 +5827,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877285</v>
+        <v>125877238</v>
       </c>
       <c r="B55" t="n">
-        <v>80112</v>
+        <v>98368</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5843,21 +5838,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5867,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540907</v>
+        <v>540793</v>
       </c>
       <c r="R55" t="n">
-        <v>6964097</v>
+        <v>6964055</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5929,32 +5924,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877238</v>
+        <v>125877305</v>
       </c>
       <c r="B56" t="n">
-        <v>98366</v>
+        <v>56835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5959,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540793</v>
+        <v>540783</v>
       </c>
       <c r="R56" t="n">
-        <v>6964055</v>
+        <v>6964091</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6000,6 +5995,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6029,7 +6029,7 @@
         <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98366</v>
+        <v>98251</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R61" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98249</v>
+        <v>98368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R62" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877326</v>
+        <v>125877279</v>
       </c>
       <c r="B63" t="n">
-        <v>98249</v>
+        <v>80076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540801</v>
+        <v>540793</v>
       </c>
       <c r="R63" t="n">
-        <v>6964059</v>
+        <v>6963960</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877279</v>
+        <v>125877282</v>
       </c>
       <c r="B64" t="n">
         <v>80076</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540793</v>
+        <v>540758</v>
       </c>
       <c r="R64" t="n">
-        <v>6963960</v>
+        <v>6963956</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877282</v>
+        <v>125877262</v>
       </c>
       <c r="B65" t="n">
         <v>80076</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540758</v>
+        <v>540818</v>
       </c>
       <c r="R65" t="n">
-        <v>6963956</v>
+        <v>6964054</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877262</v>
+        <v>125877326</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>98251</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540818</v>
+        <v>540801</v>
       </c>
       <c r="R66" t="n">
-        <v>6964054</v>
+        <v>6964059</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877246</v>
+        <v>125877235</v>
       </c>
       <c r="B67" t="n">
-        <v>98364</v>
+        <v>98368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540789</v>
+        <v>540804</v>
       </c>
       <c r="R67" t="n">
-        <v>6964012</v>
+        <v>6964049</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,7 +7093,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877235</v>
+        <v>125877246</v>
       </c>
       <c r="B68" t="n">
         <v>98366</v>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540804</v>
+        <v>540789</v>
       </c>
       <c r="R68" t="n">
-        <v>6964049</v>
+        <v>6964012</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877247</v>
+        <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540780</v>
+        <v>540781</v>
       </c>
       <c r="R69" t="n">
-        <v>6963984</v>
+        <v>6963980</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R70" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877270</v>
+        <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>98366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540970</v>
+        <v>540780</v>
       </c>
       <c r="R71" t="n">
-        <v>6964115</v>
+        <v>6963984</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877290</v>
+        <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>80036</v>
+        <v>80076</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540819</v>
+        <v>540749</v>
       </c>
       <c r="R72" t="n">
-        <v>6964057</v>
+        <v>6964056</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R73" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877344</v>
+        <v>125877290</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>80036</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540975</v>
+        <v>540819</v>
       </c>
       <c r="R74" t="n">
-        <v>6964085</v>
+        <v>6964057</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7775,7 +7775,7 @@
         <v>125877302</v>
       </c>
       <c r="B75" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>125877301</v>
       </c>
       <c r="B76" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877232</v>
+        <v>125877241</v>
       </c>
       <c r="B78" t="n">
-        <v>91236</v>
+        <v>98366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540989</v>
+        <v>540752</v>
       </c>
       <c r="R78" t="n">
-        <v>6964130</v>
+        <v>6964040</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,10 +8160,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877312</v>
+        <v>125877245</v>
       </c>
       <c r="B79" t="n">
-        <v>98249</v>
+        <v>98366</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8171,21 +8171,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540881</v>
+        <v>540964</v>
       </c>
       <c r="R79" t="n">
-        <v>6964135</v>
+        <v>6964121</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877274</v>
+        <v>125877297</v>
       </c>
       <c r="B80" t="n">
-        <v>80076</v>
+        <v>98345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540794</v>
+        <v>540874</v>
       </c>
       <c r="R80" t="n">
-        <v>6964003</v>
+        <v>6964063</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,10 +8354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877272</v>
+        <v>125877232</v>
       </c>
       <c r="B81" t="n">
-        <v>80076</v>
+        <v>91238</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8365,21 +8365,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540806</v>
+        <v>540989</v>
       </c>
       <c r="R81" t="n">
-        <v>6964062</v>
+        <v>6964130</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877297</v>
+        <v>125877312</v>
       </c>
       <c r="B82" t="n">
-        <v>98343</v>
+        <v>98251</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540874</v>
+        <v>540881</v>
       </c>
       <c r="R82" t="n">
-        <v>6964063</v>
+        <v>6964135</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,32 +8548,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877241</v>
+        <v>125877272</v>
       </c>
       <c r="B83" t="n">
-        <v>98364</v>
+        <v>80076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540752</v>
+        <v>540806</v>
       </c>
       <c r="R83" t="n">
-        <v>6964040</v>
+        <v>6964062</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877245</v>
+        <v>125877274</v>
       </c>
       <c r="B84" t="n">
-        <v>98364</v>
+        <v>80076</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540964</v>
+        <v>540794</v>
       </c>
       <c r="R84" t="n">
-        <v>6964121</v>
+        <v>6964003</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B50" t="n">
-        <v>80076</v>
+        <v>98366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R50" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B51" t="n">
-        <v>98366</v>
+        <v>80076</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R51" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877309</v>
+        <v>125877292</v>
       </c>
       <c r="B57" t="n">
-        <v>98251</v>
+        <v>80036</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540880</v>
+        <v>540811</v>
       </c>
       <c r="R57" t="n">
-        <v>6964142</v>
+        <v>6964057</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877330</v>
+        <v>125877294</v>
       </c>
       <c r="B58" t="n">
-        <v>98251</v>
+        <v>98345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540792</v>
+        <v>540750</v>
       </c>
       <c r="R58" t="n">
-        <v>6964061</v>
+        <v>6964085</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B59" t="n">
-        <v>98345</v>
+        <v>98251</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B60" t="n">
-        <v>80036</v>
+        <v>98251</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B61" t="n">
-        <v>98251</v>
+        <v>98368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R61" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B62" t="n">
-        <v>98368</v>
+        <v>98251</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R62" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877279</v>
+        <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>80076</v>
+        <v>98251</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540793</v>
+        <v>540801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963960</v>
+        <v>6964059</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B64" t="n">
         <v>80076</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R64" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B65" t="n">
         <v>80076</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R65" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B66" t="n">
-        <v>98251</v>
+        <v>80076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R66" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877304</v>
+        <v>125877332</v>
       </c>
       <c r="B2" t="n">
-        <v>56835</v>
+        <v>98255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540740</v>
+        <v>540794</v>
       </c>
       <c r="R2" t="n">
-        <v>6964067</v>
+        <v>6964056</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877332</v>
+        <v>125877322</v>
       </c>
       <c r="B3" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540794</v>
+        <v>540809</v>
       </c>
       <c r="R3" t="n">
-        <v>6964056</v>
+        <v>6964096</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877322</v>
+        <v>125877310</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540809</v>
+        <v>540890</v>
       </c>
       <c r="R4" t="n">
-        <v>6964096</v>
+        <v>6964145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877310</v>
+        <v>125877259</v>
       </c>
       <c r="B5" t="n">
-        <v>98251</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540890</v>
+        <v>540760</v>
       </c>
       <c r="R5" t="n">
-        <v>6964145</v>
+        <v>6964020</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877259</v>
+        <v>125877271</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540760</v>
+        <v>540996</v>
       </c>
       <c r="R6" t="n">
-        <v>6964020</v>
+        <v>6964140</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877271</v>
+        <v>125877304</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>56839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540996</v>
+        <v>540740</v>
       </c>
       <c r="R7" t="n">
-        <v>6964140</v>
+        <v>6964067</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877339</v>
+        <v>125877296</v>
       </c>
       <c r="B8" t="n">
-        <v>105371</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540959</v>
+        <v>540787</v>
       </c>
       <c r="R8" t="n">
-        <v>6964030</v>
+        <v>6964017</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877296</v>
+        <v>125877300</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540787</v>
+        <v>540937</v>
       </c>
       <c r="R9" t="n">
-        <v>6964017</v>
+        <v>6964110</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877300</v>
+        <v>125877339</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>105384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540937</v>
+        <v>540959</v>
       </c>
       <c r="R10" t="n">
-        <v>6964110</v>
+        <v>6964030</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877236</v>
+        <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98255</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540802</v>
+        <v>540804</v>
       </c>
       <c r="R11" t="n">
-        <v>6964109</v>
+        <v>6964092</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877324</v>
+        <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98251</v>
+        <v>98372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R12" t="n">
-        <v>6964092</v>
+        <v>6964109</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877275</v>
+        <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>98255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540780</v>
+        <v>540848</v>
       </c>
       <c r="R13" t="n">
-        <v>6963983</v>
+        <v>6964091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877277</v>
+        <v>125877275</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540786</v>
+        <v>540780</v>
       </c>
       <c r="R14" t="n">
-        <v>6963974</v>
+        <v>6963983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877264</v>
+        <v>125877277</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540828</v>
+        <v>540786</v>
       </c>
       <c r="R15" t="n">
-        <v>6964037</v>
+        <v>6963974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877315</v>
+        <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>98251</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540848</v>
+        <v>540828</v>
       </c>
       <c r="R16" t="n">
-        <v>6964091</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2138,7 +2138,7 @@
         <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125877311</v>
       </c>
       <c r="B18" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>125877276</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>125877278</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>125877269</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>125877261</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>125877320</v>
       </c>
       <c r="B28" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>125877291</v>
       </c>
       <c r="B29" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877314</v>
+        <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540853</v>
+        <v>540793</v>
       </c>
       <c r="R30" t="n">
-        <v>6964095</v>
+        <v>6964055</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,6 +3468,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3494,32 +3499,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877306</v>
+        <v>125877366</v>
       </c>
       <c r="B31" t="n">
-        <v>98251</v>
+        <v>88651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540793</v>
+        <v>540874</v>
       </c>
       <c r="R31" t="n">
-        <v>6964055</v>
+        <v>6964114</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3565,11 +3570,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877366</v>
+        <v>125877323</v>
       </c>
       <c r="B32" t="n">
-        <v>88647</v>
+        <v>98255</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540874</v>
+        <v>540803</v>
       </c>
       <c r="R32" t="n">
-        <v>6964114</v>
+        <v>6964102</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877323</v>
+        <v>125877252</v>
       </c>
       <c r="B33" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540803</v>
+        <v>540788</v>
       </c>
       <c r="R33" t="n">
-        <v>6964102</v>
+        <v>6964033</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877252</v>
+        <v>125877273</v>
       </c>
       <c r="B34" t="n">
-        <v>98251</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540788</v>
+        <v>540797</v>
       </c>
       <c r="R34" t="n">
-        <v>6964033</v>
+        <v>6964057</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3890,7 +3890,7 @@
         <v>125877298</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877273</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540797</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964057</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877266</v>
+        <v>125877314</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>98255</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540868</v>
+        <v>540853</v>
       </c>
       <c r="R37" t="n">
-        <v>6964062</v>
+        <v>6964095</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877303</v>
       </c>
       <c r="B38" t="n">
-        <v>98251</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540785</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6963977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877335</v>
       </c>
       <c r="B39" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540781</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877317</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98255</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540850</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4472,7 +4472,7 @@
         <v>125877267</v>
       </c>
       <c r="B41" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877299</v>
+        <v>125877321</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>98255</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540927</v>
+        <v>540855</v>
       </c>
       <c r="R44" t="n">
-        <v>6964119</v>
+        <v>6964125</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877321</v>
+        <v>125877316</v>
       </c>
       <c r="B45" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540855</v>
+        <v>540803</v>
       </c>
       <c r="R45" t="n">
-        <v>6964125</v>
+        <v>6964060</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877316</v>
+        <v>125877268</v>
       </c>
       <c r="B46" t="n">
-        <v>98251</v>
+        <v>80080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540803</v>
+        <v>540907</v>
       </c>
       <c r="R46" t="n">
-        <v>6964060</v>
+        <v>6964097</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877268</v>
+        <v>125877299</v>
       </c>
       <c r="B47" t="n">
-        <v>80076</v>
+        <v>98349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540907</v>
+        <v>540927</v>
       </c>
       <c r="R47" t="n">
-        <v>6964097</v>
+        <v>6964119</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
         <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B50" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R50" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R51" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5539,7 +5539,7 @@
         <v>125877341</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>125877350</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>125877285</v>
       </c>
       <c r="B54" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5827,32 +5827,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877238</v>
+        <v>125877305</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>56839</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540793</v>
+        <v>540783</v>
       </c>
       <c r="R55" t="n">
-        <v>6964055</v>
+        <v>6964091</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,6 +5898,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5924,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877305</v>
+        <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>56835</v>
+        <v>98372</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5959,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540783</v>
+        <v>540793</v>
       </c>
       <c r="R56" t="n">
-        <v>6964091</v>
+        <v>6964055</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -5995,11 +6000,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B57" t="n">
-        <v>80036</v>
+        <v>98255</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R57" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B58" t="n">
-        <v>98345</v>
+        <v>98255</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R58" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98251</v>
+        <v>98349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98251</v>
+        <v>80040</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98368</v>
+        <v>98255</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R61" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98251</v>
+        <v>98372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R62" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877326</v>
+        <v>125877235</v>
       </c>
       <c r="B63" t="n">
-        <v>98251</v>
+        <v>98372</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540801</v>
+        <v>540804</v>
       </c>
       <c r="R63" t="n">
-        <v>6964059</v>
+        <v>6964049</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877279</v>
+        <v>125877246</v>
       </c>
       <c r="B64" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540793</v>
+        <v>540789</v>
       </c>
       <c r="R64" t="n">
-        <v>6963960</v>
+        <v>6964012</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,32 +6802,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877282</v>
+        <v>125877326</v>
       </c>
       <c r="B65" t="n">
-        <v>80076</v>
+        <v>98255</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540758</v>
+        <v>540801</v>
       </c>
       <c r="R65" t="n">
-        <v>6963956</v>
+        <v>6964059</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877262</v>
+        <v>125877279</v>
       </c>
       <c r="B66" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540818</v>
+        <v>540793</v>
       </c>
       <c r="R66" t="n">
-        <v>6964054</v>
+        <v>6963960</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877235</v>
+        <v>125877282</v>
       </c>
       <c r="B67" t="n">
-        <v>98368</v>
+        <v>80080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540804</v>
+        <v>540758</v>
       </c>
       <c r="R67" t="n">
-        <v>6964049</v>
+        <v>6963956</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,32 +7093,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877262</v>
       </c>
       <c r="B68" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540818</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964054</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877354</v>
+        <v>125877247</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>98370</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540781</v>
+        <v>540780</v>
       </c>
       <c r="R69" t="n">
-        <v>6963980</v>
+        <v>6963984</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877270</v>
+        <v>125877354</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540970</v>
+        <v>540781</v>
       </c>
       <c r="R70" t="n">
-        <v>6964115</v>
+        <v>6963980</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877247</v>
+        <v>125877270</v>
       </c>
       <c r="B71" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540780</v>
+        <v>540970</v>
       </c>
       <c r="R71" t="n">
-        <v>6963984</v>
+        <v>6964115</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7484,7 +7484,7 @@
         <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877290</v>
+        <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>80036</v>
+        <v>98349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540819</v>
+        <v>540970</v>
       </c>
       <c r="R74" t="n">
-        <v>6964057</v>
+        <v>6964115</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,10 +7772,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877302</v>
+        <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540970</v>
+        <v>540963</v>
       </c>
       <c r="R75" t="n">
-        <v>6964115</v>
+        <v>6964113</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877301</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>98345</v>
+        <v>80040</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540963</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964113</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877241</v>
+        <v>125877232</v>
       </c>
       <c r="B78" t="n">
-        <v>98366</v>
+        <v>91242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540752</v>
+        <v>540989</v>
       </c>
       <c r="R78" t="n">
-        <v>6964040</v>
+        <v>6964130</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,10 +8160,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877245</v>
+        <v>125877312</v>
       </c>
       <c r="B79" t="n">
-        <v>98366</v>
+        <v>98255</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8171,21 +8171,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540964</v>
+        <v>540881</v>
       </c>
       <c r="R79" t="n">
-        <v>6964121</v>
+        <v>6964135</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877297</v>
+        <v>125877272</v>
       </c>
       <c r="B80" t="n">
-        <v>98345</v>
+        <v>80080</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540874</v>
+        <v>540806</v>
       </c>
       <c r="R80" t="n">
-        <v>6964063</v>
+        <v>6964062</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,10 +8354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877232</v>
+        <v>125877274</v>
       </c>
       <c r="B81" t="n">
-        <v>91238</v>
+        <v>80080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8365,21 +8365,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540989</v>
+        <v>540794</v>
       </c>
       <c r="R81" t="n">
-        <v>6964130</v>
+        <v>6964003</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877312</v>
+        <v>125877297</v>
       </c>
       <c r="B82" t="n">
-        <v>98251</v>
+        <v>98349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540881</v>
+        <v>540874</v>
       </c>
       <c r="R82" t="n">
-        <v>6964135</v>
+        <v>6964063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,32 +8548,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877272</v>
+        <v>125877241</v>
       </c>
       <c r="B83" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540806</v>
+        <v>540752</v>
       </c>
       <c r="R83" t="n">
-        <v>6964062</v>
+        <v>6964040</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877274</v>
+        <v>125877245</v>
       </c>
       <c r="B84" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540794</v>
+        <v>540964</v>
       </c>
       <c r="R84" t="n">
-        <v>6964003</v>
+        <v>6964121</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877332</v>
+        <v>125877296</v>
       </c>
       <c r="B2" t="n">
-        <v>98255</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540794</v>
+        <v>540787</v>
       </c>
       <c r="R2" t="n">
-        <v>6964056</v>
+        <v>6964017</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877322</v>
+        <v>125877300</v>
       </c>
       <c r="B3" t="n">
-        <v>98255</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540809</v>
+        <v>540937</v>
       </c>
       <c r="R3" t="n">
-        <v>6964096</v>
+        <v>6964110</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877310</v>
+        <v>125877339</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>105384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540890</v>
+        <v>540959</v>
       </c>
       <c r="R4" t="n">
-        <v>6964145</v>
+        <v>6964030</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877259</v>
+        <v>125877332</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>98255</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540760</v>
+        <v>540794</v>
       </c>
       <c r="R5" t="n">
-        <v>6964020</v>
+        <v>6964056</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877271</v>
+        <v>125877322</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>98255</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540996</v>
+        <v>540809</v>
       </c>
       <c r="R6" t="n">
-        <v>6964140</v>
+        <v>6964096</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877304</v>
+        <v>125877310</v>
       </c>
       <c r="B7" t="n">
-        <v>56839</v>
+        <v>98255</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540740</v>
+        <v>540890</v>
       </c>
       <c r="R7" t="n">
-        <v>6964067</v>
+        <v>6964145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877296</v>
+        <v>125877259</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540787</v>
+        <v>540760</v>
       </c>
       <c r="R8" t="n">
-        <v>6964017</v>
+        <v>6964020</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877300</v>
+        <v>125877271</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540937</v>
+        <v>540996</v>
       </c>
       <c r="R9" t="n">
-        <v>6964110</v>
+        <v>6964140</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877339</v>
+        <v>125877304</v>
       </c>
       <c r="B10" t="n">
-        <v>105384</v>
+        <v>56839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540959</v>
+        <v>540740</v>
       </c>
       <c r="R10" t="n">
-        <v>6964030</v>
+        <v>6964067</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1527,6 +1522,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3397,7 +3397,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877306</v>
+        <v>125877314</v>
       </c>
       <c r="B30" t="n">
         <v>98255</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540793</v>
+        <v>540853</v>
       </c>
       <c r="R30" t="n">
-        <v>6964055</v>
+        <v>6964095</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,11 +3468,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3499,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877366</v>
+        <v>125877306</v>
       </c>
       <c r="B31" t="n">
-        <v>88651</v>
+        <v>98255</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540874</v>
+        <v>540793</v>
       </c>
       <c r="R31" t="n">
-        <v>6964114</v>
+        <v>6964055</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3570,6 +3565,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877323</v>
+        <v>125877366</v>
       </c>
       <c r="B32" t="n">
-        <v>98255</v>
+        <v>88651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540803</v>
+        <v>540874</v>
       </c>
       <c r="R32" t="n">
-        <v>6964102</v>
+        <v>6964114</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877252</v>
+        <v>125877323</v>
       </c>
       <c r="B33" t="n">
         <v>98255</v>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540788</v>
+        <v>540803</v>
       </c>
       <c r="R33" t="n">
-        <v>6964033</v>
+        <v>6964102</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,32 +3790,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877273</v>
+        <v>125877252</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>98255</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540797</v>
+        <v>540788</v>
       </c>
       <c r="R34" t="n">
-        <v>6964057</v>
+        <v>6964033</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877298</v>
+        <v>125877273</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540912</v>
+        <v>540797</v>
       </c>
       <c r="R35" t="n">
-        <v>6964122</v>
+        <v>6964057</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877314</v>
+        <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98255</v>
+        <v>98349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540853</v>
+        <v>540912</v>
       </c>
       <c r="R37" t="n">
-        <v>6964095</v>
+        <v>6964122</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98255</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
         <v>98255</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98255</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877296</v>
+        <v>125877304</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>56839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540787</v>
+        <v>540740</v>
       </c>
       <c r="R2" t="n">
-        <v>6964017</v>
+        <v>6964067</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877300</v>
+        <v>125877296</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540937</v>
+        <v>540787</v>
       </c>
       <c r="R3" t="n">
-        <v>6964110</v>
+        <v>6964017</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877339</v>
+        <v>125877300</v>
       </c>
       <c r="B4" t="n">
-        <v>105384</v>
+        <v>98352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540959</v>
+        <v>540937</v>
       </c>
       <c r="R4" t="n">
-        <v>6964030</v>
+        <v>6964110</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877332</v>
+        <v>125877259</v>
       </c>
       <c r="B5" t="n">
-        <v>98255</v>
+        <v>80080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540794</v>
+        <v>540760</v>
       </c>
       <c r="R5" t="n">
-        <v>6964056</v>
+        <v>6964020</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877322</v>
+        <v>125877271</v>
       </c>
       <c r="B6" t="n">
-        <v>98255</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540809</v>
+        <v>540996</v>
       </c>
       <c r="R6" t="n">
-        <v>6964096</v>
+        <v>6964140</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877310</v>
+        <v>125877332</v>
       </c>
       <c r="B7" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540890</v>
+        <v>540794</v>
       </c>
       <c r="R7" t="n">
-        <v>6964145</v>
+        <v>6964056</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877259</v>
+        <v>125877322</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540760</v>
+        <v>540809</v>
       </c>
       <c r="R8" t="n">
-        <v>6964020</v>
+        <v>6964096</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877271</v>
+        <v>125877310</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540996</v>
+        <v>540890</v>
       </c>
       <c r="R9" t="n">
-        <v>6964140</v>
+        <v>6964145</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1451,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877304</v>
+        <v>125877339</v>
       </c>
       <c r="B10" t="n">
-        <v>56839</v>
+        <v>105387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540740</v>
+        <v>540959</v>
       </c>
       <c r="R10" t="n">
-        <v>6964067</v>
+        <v>6964030</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1522,11 +1527,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,7 +1556,7 @@
         <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877318</v>
+        <v>125877240</v>
       </c>
       <c r="B17" t="n">
-        <v>98255</v>
+        <v>98373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540850</v>
+        <v>540848</v>
       </c>
       <c r="R17" t="n">
-        <v>6964070</v>
+        <v>6964065</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877311</v>
+        <v>125877318</v>
       </c>
       <c r="B18" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540889</v>
+        <v>540850</v>
       </c>
       <c r="R18" t="n">
-        <v>6964139</v>
+        <v>6964070</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877240</v>
+        <v>125877311</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540848</v>
+        <v>540889</v>
       </c>
       <c r="R19" t="n">
-        <v>6964065</v>
+        <v>6964139</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2408,7 +2409,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877313</v>
+        <v>125877284</v>
       </c>
       <c r="B20" t="n">
-        <v>98255</v>
+        <v>80116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R20" t="n">
-        <v>6964119</v>
+        <v>6964031</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877284</v>
+        <v>125877260</v>
       </c>
       <c r="B21" t="n">
-        <v>80116</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540807</v>
+        <v>540800</v>
       </c>
       <c r="R21" t="n">
-        <v>6964031</v>
+        <v>6964021</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877260</v>
+        <v>125877313</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540800</v>
+        <v>540882</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964119</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>125877320</v>
       </c>
       <c r="B28" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877314</v>
+        <v>125877273</v>
       </c>
       <c r="B30" t="n">
-        <v>98255</v>
+        <v>80080</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540853</v>
+        <v>540797</v>
       </c>
       <c r="R30" t="n">
-        <v>6964095</v>
+        <v>6964057</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877306</v>
+        <v>125877266</v>
       </c>
       <c r="B31" t="n">
-        <v>98255</v>
+        <v>80080</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540793</v>
+        <v>540868</v>
       </c>
       <c r="R31" t="n">
-        <v>6964055</v>
+        <v>6964062</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3565,11 +3565,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3591,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877366</v>
+        <v>125877306</v>
       </c>
       <c r="B32" t="n">
-        <v>88651</v>
+        <v>98258</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3626,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540874</v>
+        <v>540793</v>
       </c>
       <c r="R32" t="n">
-        <v>6964114</v>
+        <v>6964055</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3667,6 +3662,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877323</v>
+        <v>125877366</v>
       </c>
       <c r="B33" t="n">
-        <v>98255</v>
+        <v>88651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540803</v>
+        <v>540874</v>
       </c>
       <c r="R33" t="n">
-        <v>6964102</v>
+        <v>6964114</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,10 +3790,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877252</v>
+        <v>125877323</v>
       </c>
       <c r="B34" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540788</v>
+        <v>540803</v>
       </c>
       <c r="R34" t="n">
-        <v>6964033</v>
+        <v>6964102</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877273</v>
+        <v>125877314</v>
       </c>
       <c r="B35" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540797</v>
+        <v>540853</v>
       </c>
       <c r="R35" t="n">
-        <v>6964057</v>
+        <v>6964095</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,32 +3984,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877252</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540788</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964033</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4084,7 +4084,7 @@
         <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877303</v>
       </c>
       <c r="B38" t="n">
-        <v>98255</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540785</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6963977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877335</v>
       </c>
       <c r="B39" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540781</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877317</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98258</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540850</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4666,7 +4666,7 @@
         <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877321</v>
+        <v>125877299</v>
       </c>
       <c r="B44" t="n">
-        <v>98255</v>
+        <v>98352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540855</v>
+        <v>540927</v>
       </c>
       <c r="R44" t="n">
-        <v>6964125</v>
+        <v>6964119</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,32 +4857,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877316</v>
+        <v>125877268</v>
       </c>
       <c r="B45" t="n">
-        <v>98255</v>
+        <v>80080</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540803</v>
+        <v>540907</v>
       </c>
       <c r="R45" t="n">
-        <v>6964060</v>
+        <v>6964097</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877268</v>
+        <v>125877321</v>
       </c>
       <c r="B46" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540907</v>
+        <v>540855</v>
       </c>
       <c r="R46" t="n">
-        <v>6964097</v>
+        <v>6964125</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877299</v>
+        <v>125877316</v>
       </c>
       <c r="B47" t="n">
-        <v>98349</v>
+        <v>98258</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540927</v>
+        <v>540803</v>
       </c>
       <c r="R47" t="n">
-        <v>6964119</v>
+        <v>6964060</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5151,7 +5151,7 @@
         <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877330</v>
+        <v>125877294</v>
       </c>
       <c r="B57" t="n">
-        <v>98255</v>
+        <v>98352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540792</v>
+        <v>540750</v>
       </c>
       <c r="R57" t="n">
-        <v>6964061</v>
+        <v>6964085</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877309</v>
+        <v>125877292</v>
       </c>
       <c r="B58" t="n">
-        <v>98255</v>
+        <v>80040</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540880</v>
+        <v>540811</v>
       </c>
       <c r="R58" t="n">
-        <v>6964142</v>
+        <v>6964057</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B59" t="n">
-        <v>98349</v>
+        <v>98258</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B60" t="n">
-        <v>80040</v>
+        <v>98258</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6417,7 +6417,7 @@
         <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>125877235</v>
       </c>
       <c r="B63" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877246</v>
+        <v>125877279</v>
       </c>
       <c r="B64" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540789</v>
+        <v>540793</v>
       </c>
       <c r="R64" t="n">
-        <v>6964012</v>
+        <v>6963960</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,32 +6802,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877326</v>
+        <v>125877282</v>
       </c>
       <c r="B65" t="n">
-        <v>98255</v>
+        <v>80080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540801</v>
+        <v>540758</v>
       </c>
       <c r="R65" t="n">
-        <v>6964059</v>
+        <v>6963956</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,7 +6899,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877279</v>
+        <v>125877262</v>
       </c>
       <c r="B66" t="n">
         <v>80080</v>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540793</v>
+        <v>540818</v>
       </c>
       <c r="R66" t="n">
-        <v>6963960</v>
+        <v>6964054</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877282</v>
+        <v>125877326</v>
       </c>
       <c r="B67" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540758</v>
+        <v>540801</v>
       </c>
       <c r="R67" t="n">
-        <v>6963956</v>
+        <v>6964059</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,32 +7093,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877262</v>
+        <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540818</v>
+        <v>540789</v>
       </c>
       <c r="R68" t="n">
-        <v>6964054</v>
+        <v>6964012</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7193,7 +7193,7 @@
         <v>125877247</v>
       </c>
       <c r="B69" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B72" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7492,21 +7492,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R72" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877258</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540749</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964056</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7678,7 +7678,7 @@
         <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877232</v>
+        <v>125877312</v>
       </c>
       <c r="B78" t="n">
-        <v>91242</v>
+        <v>98258</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540989</v>
+        <v>540881</v>
       </c>
       <c r="R78" t="n">
-        <v>6964130</v>
+        <v>6964135</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,10 +8160,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877312</v>
+        <v>125877241</v>
       </c>
       <c r="B79" t="n">
-        <v>98255</v>
+        <v>98373</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8171,21 +8171,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540881</v>
+        <v>540752</v>
       </c>
       <c r="R79" t="n">
-        <v>6964135</v>
+        <v>6964040</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877272</v>
+        <v>125877245</v>
       </c>
       <c r="B80" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540806</v>
+        <v>540964</v>
       </c>
       <c r="R80" t="n">
-        <v>6964062</v>
+        <v>6964121</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,32 +8354,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877274</v>
+        <v>125877297</v>
       </c>
       <c r="B81" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540794</v>
+        <v>540874</v>
       </c>
       <c r="R81" t="n">
-        <v>6964003</v>
+        <v>6964063</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877297</v>
+        <v>125877272</v>
       </c>
       <c r="B82" t="n">
-        <v>98349</v>
+        <v>80080</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540874</v>
+        <v>540806</v>
       </c>
       <c r="R82" t="n">
-        <v>6964063</v>
+        <v>6964062</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,32 +8548,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877241</v>
+        <v>125877274</v>
       </c>
       <c r="B83" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540752</v>
+        <v>540794</v>
       </c>
       <c r="R83" t="n">
-        <v>6964040</v>
+        <v>6964003</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877245</v>
+        <v>125877232</v>
       </c>
       <c r="B84" t="n">
-        <v>98370</v>
+        <v>91242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540964</v>
+        <v>540989</v>
       </c>
       <c r="R84" t="n">
-        <v>6964121</v>
+        <v>6964130</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877296</v>
+        <v>125877332</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540787</v>
+        <v>540794</v>
       </c>
       <c r="R3" t="n">
-        <v>6964017</v>
+        <v>6964056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877300</v>
+        <v>125877322</v>
       </c>
       <c r="B4" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540937</v>
+        <v>540809</v>
       </c>
       <c r="R4" t="n">
-        <v>6964110</v>
+        <v>6964096</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877259</v>
+        <v>125877310</v>
       </c>
       <c r="B5" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540760</v>
+        <v>540890</v>
       </c>
       <c r="R5" t="n">
-        <v>6964020</v>
+        <v>6964145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877271</v>
+        <v>125877259</v>
       </c>
       <c r="B6" t="n">
         <v>80080</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540996</v>
+        <v>540760</v>
       </c>
       <c r="R6" t="n">
-        <v>6964140</v>
+        <v>6964020</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877332</v>
+        <v>125877271</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540794</v>
+        <v>540996</v>
       </c>
       <c r="R7" t="n">
-        <v>6964056</v>
+        <v>6964140</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877322</v>
+        <v>125877296</v>
       </c>
       <c r="B8" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540809</v>
+        <v>540787</v>
       </c>
       <c r="R8" t="n">
-        <v>6964096</v>
+        <v>6964017</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877310</v>
+        <v>125877300</v>
       </c>
       <c r="B9" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540890</v>
+        <v>540937</v>
       </c>
       <c r="R9" t="n">
-        <v>6964145</v>
+        <v>6964110</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877315</v>
+        <v>125877275</v>
       </c>
       <c r="B13" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540848</v>
+        <v>540780</v>
       </c>
       <c r="R13" t="n">
-        <v>6964091</v>
+        <v>6963983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877275</v>
+        <v>125877277</v>
       </c>
       <c r="B14" t="n">
         <v>80080</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540780</v>
+        <v>540786</v>
       </c>
       <c r="R14" t="n">
-        <v>6963983</v>
+        <v>6963974</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877277</v>
+        <v>125877264</v>
       </c>
       <c r="B15" t="n">
         <v>80080</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540786</v>
+        <v>540828</v>
       </c>
       <c r="R15" t="n">
-        <v>6963974</v>
+        <v>6964037</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877264</v>
+        <v>125877315</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540828</v>
+        <v>540848</v>
       </c>
       <c r="R16" t="n">
-        <v>6964037</v>
+        <v>6964091</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877313</v>
+        <v>125877295</v>
       </c>
       <c r="B22" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540882</v>
+        <v>540765</v>
       </c>
       <c r="R22" t="n">
-        <v>6964119</v>
+        <v>6964025</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877295</v>
+        <v>125877313</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540765</v>
+        <v>540882</v>
       </c>
       <c r="R23" t="n">
-        <v>6964025</v>
+        <v>6964119</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B41" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R41" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4577,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R42" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B43" t="n">
-        <v>98258</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R43" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -6026,32 +6026,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877294</v>
+        <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540750</v>
+        <v>540880</v>
       </c>
       <c r="R57" t="n">
-        <v>6964085</v>
+        <v>6964142</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877292</v>
+        <v>125877330</v>
       </c>
       <c r="B58" t="n">
-        <v>80040</v>
+        <v>98258</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540811</v>
+        <v>540792</v>
       </c>
       <c r="R58" t="n">
-        <v>6964057</v>
+        <v>6964061</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877309</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540880</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964142</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,10 +6317,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877330</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98258</v>
+        <v>80040</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540792</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964061</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877304</v>
+        <v>125877332</v>
       </c>
       <c r="B2" t="n">
-        <v>56839</v>
+        <v>98258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540740</v>
+        <v>540794</v>
       </c>
       <c r="R2" t="n">
-        <v>6964067</v>
+        <v>6964056</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877332</v>
+        <v>125877322</v>
       </c>
       <c r="B3" t="n">
         <v>98258</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540794</v>
+        <v>540809</v>
       </c>
       <c r="R3" t="n">
-        <v>6964056</v>
+        <v>6964096</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877322</v>
+        <v>125877304</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>56839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>504</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540809</v>
+        <v>540740</v>
       </c>
       <c r="R4" t="n">
-        <v>6964096</v>
+        <v>6964067</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877310</v>
+        <v>125877339</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>105387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540890</v>
+        <v>540959</v>
       </c>
       <c r="R5" t="n">
-        <v>6964145</v>
+        <v>6964030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877259</v>
+        <v>125877310</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540760</v>
+        <v>540890</v>
       </c>
       <c r="R6" t="n">
-        <v>6964020</v>
+        <v>6964145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877296</v>
+        <v>125877259</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540787</v>
+        <v>540760</v>
       </c>
       <c r="R8" t="n">
-        <v>6964017</v>
+        <v>6964020</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877300</v>
+        <v>125877296</v>
       </c>
       <c r="B9" t="n">
         <v>98352</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540937</v>
+        <v>540787</v>
       </c>
       <c r="R9" t="n">
-        <v>6964110</v>
+        <v>6964017</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877339</v>
+        <v>125877300</v>
       </c>
       <c r="B10" t="n">
-        <v>105387</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540959</v>
+        <v>540937</v>
       </c>
       <c r="R10" t="n">
-        <v>6964030</v>
+        <v>6964110</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877275</v>
+        <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540780</v>
+        <v>540848</v>
       </c>
       <c r="R13" t="n">
-        <v>6963983</v>
+        <v>6964091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877264</v>
+        <v>125877275</v>
       </c>
       <c r="B15" t="n">
         <v>80080</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540828</v>
+        <v>540780</v>
       </c>
       <c r="R15" t="n">
-        <v>6964037</v>
+        <v>6963983</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877315</v>
+        <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540848</v>
+        <v>540828</v>
       </c>
       <c r="R16" t="n">
-        <v>6964091</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877240</v>
+        <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98373</v>
+        <v>98258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540848</v>
+        <v>540850</v>
       </c>
       <c r="R17" t="n">
-        <v>6964065</v>
+        <v>6964070</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877318</v>
+        <v>125877311</v>
       </c>
       <c r="B18" t="n">
         <v>98258</v>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540850</v>
+        <v>540889</v>
       </c>
       <c r="R18" t="n">
-        <v>6964070</v>
+        <v>6964139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877311</v>
+        <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98258</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540889</v>
+        <v>540848</v>
       </c>
       <c r="R19" t="n">
-        <v>6964139</v>
+        <v>6964065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877295</v>
+        <v>125877313</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540765</v>
+        <v>540882</v>
       </c>
       <c r="R22" t="n">
-        <v>6964025</v>
+        <v>6964119</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877313</v>
+        <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540882</v>
+        <v>540765</v>
       </c>
       <c r="R23" t="n">
-        <v>6964119</v>
+        <v>6964025</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877276</v>
+        <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540785</v>
+        <v>540882</v>
       </c>
       <c r="R24" t="n">
-        <v>6963977</v>
+        <v>6964142</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877269</v>
+        <v>125877276</v>
       </c>
       <c r="B26" t="n">
         <v>80080</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540964</v>
+        <v>540785</v>
       </c>
       <c r="R26" t="n">
-        <v>6964121</v>
+        <v>6963977</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877320</v>
+        <v>125877269</v>
       </c>
       <c r="B28" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540882</v>
+        <v>540964</v>
       </c>
       <c r="R28" t="n">
-        <v>6964142</v>
+        <v>6964121</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877273</v>
+        <v>125877298</v>
       </c>
       <c r="B30" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540797</v>
+        <v>540912</v>
       </c>
       <c r="R30" t="n">
-        <v>6964057</v>
+        <v>6964122</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3494,32 +3494,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877266</v>
+        <v>125877306</v>
       </c>
       <c r="B31" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540868</v>
+        <v>540793</v>
       </c>
       <c r="R31" t="n">
-        <v>6964062</v>
+        <v>6964055</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3565,6 +3565,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3591,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877306</v>
+        <v>125877366</v>
       </c>
       <c r="B32" t="n">
-        <v>98258</v>
+        <v>88651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3626,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540793</v>
+        <v>540874</v>
       </c>
       <c r="R32" t="n">
-        <v>6964055</v>
+        <v>6964114</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3662,11 +3667,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877366</v>
+        <v>125877323</v>
       </c>
       <c r="B33" t="n">
-        <v>88651</v>
+        <v>98258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540874</v>
+        <v>540803</v>
       </c>
       <c r="R33" t="n">
-        <v>6964114</v>
+        <v>6964102</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877323</v>
+        <v>125877314</v>
       </c>
       <c r="B34" t="n">
         <v>98258</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540803</v>
+        <v>540853</v>
       </c>
       <c r="R34" t="n">
-        <v>6964102</v>
+        <v>6964095</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877314</v>
+        <v>125877252</v>
       </c>
       <c r="B35" t="n">
         <v>98258</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540853</v>
+        <v>540788</v>
       </c>
       <c r="R35" t="n">
-        <v>6964095</v>
+        <v>6964033</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,32 +3984,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877252</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540788</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964033</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877298</v>
+        <v>125877273</v>
       </c>
       <c r="B37" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540912</v>
+        <v>540797</v>
       </c>
       <c r="R37" t="n">
-        <v>6964122</v>
+        <v>6964057</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
         <v>98258</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877299</v>
+        <v>125877321</v>
       </c>
       <c r="B44" t="n">
-        <v>98352</v>
+        <v>98258</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540927</v>
+        <v>540855</v>
       </c>
       <c r="R44" t="n">
-        <v>6964119</v>
+        <v>6964125</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,32 +4857,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877268</v>
+        <v>125877316</v>
       </c>
       <c r="B45" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R45" t="n">
-        <v>6964097</v>
+        <v>6964060</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877321</v>
+        <v>125877268</v>
       </c>
       <c r="B46" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540855</v>
+        <v>540907</v>
       </c>
       <c r="R46" t="n">
-        <v>6964125</v>
+        <v>6964097</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877316</v>
+        <v>125877299</v>
       </c>
       <c r="B47" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540803</v>
+        <v>540927</v>
       </c>
       <c r="R47" t="n">
-        <v>6964060</v>
+        <v>6964119</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B50" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R50" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R51" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877341</v>
+        <v>125877238</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>98375</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540852</v>
+        <v>540793</v>
       </c>
       <c r="R52" t="n">
-        <v>6964074</v>
+        <v>6964055</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,32 +5633,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877350</v>
+        <v>125877285</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>80116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540785</v>
+        <v>540907</v>
       </c>
       <c r="R53" t="n">
-        <v>6964039</v>
+        <v>6964097</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877285</v>
+        <v>125877341</v>
       </c>
       <c r="B54" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540907</v>
+        <v>540852</v>
       </c>
       <c r="R54" t="n">
-        <v>6964097</v>
+        <v>6964074</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877305</v>
+        <v>125877350</v>
       </c>
       <c r="B55" t="n">
-        <v>56839</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5838,21 +5838,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540783</v>
+        <v>540785</v>
       </c>
       <c r="R55" t="n">
-        <v>6964091</v>
+        <v>6964039</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,11 +5898,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5929,32 +5924,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877238</v>
+        <v>125877305</v>
       </c>
       <c r="B56" t="n">
-        <v>98375</v>
+        <v>56839</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5959,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540793</v>
+        <v>540783</v>
       </c>
       <c r="R56" t="n">
-        <v>6964055</v>
+        <v>6964091</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6000,6 +5995,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6608,10 +6608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877235</v>
+        <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>98375</v>
+        <v>98258</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540804</v>
+        <v>540801</v>
       </c>
       <c r="R63" t="n">
-        <v>6964049</v>
+        <v>6964059</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877279</v>
+        <v>125877235</v>
       </c>
       <c r="B64" t="n">
-        <v>80080</v>
+        <v>98375</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540793</v>
+        <v>540804</v>
       </c>
       <c r="R64" t="n">
-        <v>6963960</v>
+        <v>6964049</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B65" t="n">
         <v>80080</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R65" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,7 +6899,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B66" t="n">
         <v>80080</v>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R66" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B67" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R67" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7190,32 +7190,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877247</v>
+        <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540780</v>
+        <v>540781</v>
       </c>
       <c r="R69" t="n">
-        <v>6963984</v>
+        <v>6963980</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R70" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7384,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877270</v>
+        <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540970</v>
+        <v>540780</v>
       </c>
       <c r="R71" t="n">
-        <v>6964115</v>
+        <v>6963984</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877344</v>
+        <v>125877290</v>
       </c>
       <c r="B72" t="n">
-        <v>78977</v>
+        <v>80040</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540975</v>
+        <v>540819</v>
       </c>
       <c r="R72" t="n">
-        <v>6964085</v>
+        <v>6964057</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R73" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877302</v>
+        <v>125877258</v>
       </c>
       <c r="B74" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540970</v>
+        <v>540749</v>
       </c>
       <c r="R74" t="n">
-        <v>6964115</v>
+        <v>6964056</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877302</v>
       </c>
       <c r="B76" t="n">
-        <v>80040</v>
+        <v>98352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540970</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964115</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877312</v>
+        <v>125877297</v>
       </c>
       <c r="B78" t="n">
-        <v>98258</v>
+        <v>98352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540881</v>
+        <v>540874</v>
       </c>
       <c r="R78" t="n">
-        <v>6964135</v>
+        <v>6964063</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8354,32 +8354,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877297</v>
+        <v>125877274</v>
       </c>
       <c r="B81" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540874</v>
+        <v>540794</v>
       </c>
       <c r="R81" t="n">
-        <v>6964063</v>
+        <v>6964003</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877274</v>
+        <v>125877232</v>
       </c>
       <c r="B83" t="n">
-        <v>80080</v>
+        <v>91242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8559,21 +8559,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540794</v>
+        <v>540989</v>
       </c>
       <c r="R83" t="n">
-        <v>6964003</v>
+        <v>6964130</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877232</v>
+        <v>125877312</v>
       </c>
       <c r="B84" t="n">
-        <v>91242</v>
+        <v>98258</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>504</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540989</v>
+        <v>540881</v>
       </c>
       <c r="R84" t="n">
-        <v>6964130</v>
+        <v>6964135</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B41" t="n">
-        <v>98258</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R41" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B42" t="n">
-        <v>80080</v>
+        <v>98258</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R42" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,10 +4663,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4674,21 +4674,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R43" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5342,32 +5342,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877244</v>
+        <v>125877263</v>
       </c>
       <c r="B50" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540927</v>
+        <v>540824</v>
       </c>
       <c r="R50" t="n">
-        <v>6964119</v>
+        <v>6964042</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5439,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877263</v>
+        <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5474,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540824</v>
+        <v>540927</v>
       </c>
       <c r="R51" t="n">
-        <v>6964042</v>
+        <v>6964119</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877238</v>
+        <v>125877341</v>
       </c>
       <c r="B52" t="n">
-        <v>98375</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540793</v>
+        <v>540852</v>
       </c>
       <c r="R52" t="n">
-        <v>6964055</v>
+        <v>6964074</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,32 +5633,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877285</v>
+        <v>125877350</v>
       </c>
       <c r="B53" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540907</v>
+        <v>540785</v>
       </c>
       <c r="R53" t="n">
-        <v>6964097</v>
+        <v>6964039</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877341</v>
+        <v>125877285</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>80116</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540852</v>
+        <v>540907</v>
       </c>
       <c r="R54" t="n">
-        <v>6964074</v>
+        <v>6964097</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877350</v>
+        <v>125877305</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>56839</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5838,21 +5838,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540785</v>
+        <v>540783</v>
       </c>
       <c r="R55" t="n">
-        <v>6964039</v>
+        <v>6964091</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,6 +5898,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5924,32 +5929,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877305</v>
+        <v>125877238</v>
       </c>
       <c r="B56" t="n">
-        <v>56839</v>
+        <v>98375</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5959,10 +5964,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540783</v>
+        <v>540793</v>
       </c>
       <c r="R56" t="n">
-        <v>6964091</v>
+        <v>6964055</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -5995,11 +6000,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B61" t="n">
-        <v>98258</v>
+        <v>98375</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R61" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B62" t="n">
-        <v>98375</v>
+        <v>98258</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R62" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877326</v>
+        <v>125877235</v>
       </c>
       <c r="B63" t="n">
-        <v>98258</v>
+        <v>98375</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6619,21 +6619,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540801</v>
+        <v>540804</v>
       </c>
       <c r="R63" t="n">
-        <v>6964059</v>
+        <v>6964049</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,10 +6705,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877235</v>
+        <v>125877326</v>
       </c>
       <c r="B64" t="n">
-        <v>98375</v>
+        <v>98258</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6716,21 +6716,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540804</v>
+        <v>540801</v>
       </c>
       <c r="R64" t="n">
-        <v>6964049</v>
+        <v>6964059</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7481,32 +7481,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877290</v>
+        <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540819</v>
+        <v>540749</v>
       </c>
       <c r="R72" t="n">
-        <v>6964057</v>
+        <v>6964056</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877301</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540963</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964113</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,32 +7675,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877258</v>
+        <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540749</v>
+        <v>540970</v>
       </c>
       <c r="R74" t="n">
-        <v>6964056</v>
+        <v>6964115</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877301</v>
+        <v>125877344</v>
       </c>
       <c r="B75" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540963</v>
+        <v>540975</v>
       </c>
       <c r="R75" t="n">
-        <v>6964113</v>
+        <v>6964085</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7869,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877302</v>
+        <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>98352</v>
+        <v>80040</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540970</v>
+        <v>540819</v>
       </c>
       <c r="R76" t="n">
-        <v>6964115</v>
+        <v>6964057</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8063,32 +8063,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877297</v>
+        <v>125877232</v>
       </c>
       <c r="B78" t="n">
-        <v>98352</v>
+        <v>91242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540874</v>
+        <v>540989</v>
       </c>
       <c r="R78" t="n">
-        <v>6964063</v>
+        <v>6964130</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,10 +8160,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877241</v>
+        <v>125877312</v>
       </c>
       <c r="B79" t="n">
-        <v>98373</v>
+        <v>98258</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8171,21 +8171,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540752</v>
+        <v>540881</v>
       </c>
       <c r="R79" t="n">
-        <v>6964040</v>
+        <v>6964135</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877245</v>
+        <v>125877297</v>
       </c>
       <c r="B80" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540964</v>
+        <v>540874</v>
       </c>
       <c r="R80" t="n">
-        <v>6964121</v>
+        <v>6964063</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,32 +8354,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877274</v>
+        <v>125877241</v>
       </c>
       <c r="B81" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540794</v>
+        <v>540752</v>
       </c>
       <c r="R81" t="n">
-        <v>6964003</v>
+        <v>6964040</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877272</v>
+        <v>125877245</v>
       </c>
       <c r="B82" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540806</v>
+        <v>540964</v>
       </c>
       <c r="R82" t="n">
-        <v>6964062</v>
+        <v>6964121</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,10 +8548,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877232</v>
+        <v>125877274</v>
       </c>
       <c r="B83" t="n">
-        <v>91242</v>
+        <v>80080</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8559,21 +8559,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540989</v>
+        <v>540794</v>
       </c>
       <c r="R83" t="n">
-        <v>6964130</v>
+        <v>6964003</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877312</v>
+        <v>125877272</v>
       </c>
       <c r="B84" t="n">
-        <v>98258</v>
+        <v>80080</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540881</v>
+        <v>540806</v>
       </c>
       <c r="R84" t="n">
-        <v>6964135</v>
+        <v>6964062</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877332</v>
+        <v>125877259</v>
       </c>
       <c r="B2" t="n">
-        <v>98258</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540794</v>
+        <v>540760</v>
       </c>
       <c r="R2" t="n">
-        <v>6964056</v>
+        <v>6964020</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877322</v>
+        <v>125877271</v>
       </c>
       <c r="B3" t="n">
-        <v>98258</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540809</v>
+        <v>540996</v>
       </c>
       <c r="R3" t="n">
-        <v>6964096</v>
+        <v>6964140</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877304</v>
+        <v>125877332</v>
       </c>
       <c r="B4" t="n">
-        <v>56839</v>
+        <v>98267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540740</v>
+        <v>540794</v>
       </c>
       <c r="R4" t="n">
-        <v>6964067</v>
+        <v>6964056</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877339</v>
+        <v>125877322</v>
       </c>
       <c r="B5" t="n">
-        <v>105387</v>
+        <v>98267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540959</v>
+        <v>540809</v>
       </c>
       <c r="R5" t="n">
-        <v>6964030</v>
+        <v>6964096</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1071,7 +1066,7 @@
         <v>125877310</v>
       </c>
       <c r="B6" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877271</v>
+        <v>125877304</v>
       </c>
       <c r="B7" t="n">
-        <v>80080</v>
+        <v>56840</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540996</v>
+        <v>540740</v>
       </c>
       <c r="R7" t="n">
-        <v>6964140</v>
+        <v>6964067</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877259</v>
+        <v>125877339</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>105396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540760</v>
+        <v>540959</v>
       </c>
       <c r="R8" t="n">
-        <v>6964020</v>
+        <v>6964030</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1362,7 +1362,7 @@
         <v>125877296</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125877300</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125877324</v>
       </c>
       <c r="B11" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125877236</v>
       </c>
       <c r="B12" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877277</v>
+        <v>125877275</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540786</v>
+        <v>540780</v>
       </c>
       <c r="R14" t="n">
-        <v>6963974</v>
+        <v>6963983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877275</v>
+        <v>125877277</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540780</v>
+        <v>540786</v>
       </c>
       <c r="R15" t="n">
-        <v>6963983</v>
+        <v>6963974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2041,7 +2041,7 @@
         <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877318</v>
+        <v>125877240</v>
       </c>
       <c r="B17" t="n">
-        <v>98258</v>
+        <v>98382</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540850</v>
+        <v>540848</v>
       </c>
       <c r="R17" t="n">
-        <v>6964070</v>
+        <v>6964065</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,6 +2214,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2232,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877311</v>
+        <v>125877318</v>
       </c>
       <c r="B18" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540889</v>
+        <v>540850</v>
       </c>
       <c r="R18" t="n">
-        <v>6964139</v>
+        <v>6964070</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2329,10 +2330,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877240</v>
+        <v>125877311</v>
       </c>
       <c r="B19" t="n">
-        <v>98373</v>
+        <v>98267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2341,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2365,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540848</v>
+        <v>540889</v>
       </c>
       <c r="R19" t="n">
-        <v>6964065</v>
+        <v>6964139</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2408,7 +2409,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877284</v>
+        <v>125877313</v>
       </c>
       <c r="B20" t="n">
-        <v>80116</v>
+        <v>98267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2438,21 +2438,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R20" t="n">
-        <v>6964031</v>
+        <v>6964119</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,32 +2524,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877260</v>
+        <v>125877284</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>80119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540800</v>
+        <v>540807</v>
       </c>
       <c r="R21" t="n">
-        <v>6964021</v>
+        <v>6964031</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877313</v>
+        <v>125877260</v>
       </c>
       <c r="B22" t="n">
-        <v>98258</v>
+        <v>80083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540882</v>
+        <v>540800</v>
       </c>
       <c r="R22" t="n">
-        <v>6964119</v>
+        <v>6964021</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2721,7 +2721,7 @@
         <v>125877295</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877278</v>
+        <v>125877276</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540790</v>
+        <v>540785</v>
       </c>
       <c r="R25" t="n">
-        <v>6963972</v>
+        <v>6963977</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,10 +3009,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877276</v>
+        <v>125877278</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540785</v>
+        <v>540790</v>
       </c>
       <c r="R26" t="n">
-        <v>6963977</v>
+        <v>6963972</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,10 +3106,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877261</v>
+        <v>125877269</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540807</v>
+        <v>540964</v>
       </c>
       <c r="R27" t="n">
-        <v>6964030</v>
+        <v>6964121</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,10 +3203,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877269</v>
+        <v>125877261</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540964</v>
+        <v>540807</v>
       </c>
       <c r="R28" t="n">
-        <v>6964121</v>
+        <v>6964030</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3303,7 +3303,7 @@
         <v>125877291</v>
       </c>
       <c r="B29" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>125877298</v>
       </c>
       <c r="B30" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>125877306</v>
       </c>
       <c r="B31" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>125877366</v>
       </c>
       <c r="B32" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>125877323</v>
       </c>
       <c r="B33" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125877314</v>
       </c>
       <c r="B34" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>125877252</v>
       </c>
       <c r="B35" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877273</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540797</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964057</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877273</v>
+        <v>125877266</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540797</v>
+        <v>540868</v>
       </c>
       <c r="R37" t="n">
-        <v>6964057</v>
+        <v>6964062</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4181,7 +4181,7 @@
         <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>125877317</v>
       </c>
       <c r="B39" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877347</v>
+        <v>125877267</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540997</v>
+        <v>540893</v>
       </c>
       <c r="R41" t="n">
-        <v>6964169</v>
+        <v>6964069</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877307</v>
+        <v>125877347</v>
       </c>
       <c r="B42" t="n">
-        <v>98258</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540788</v>
+        <v>540997</v>
       </c>
       <c r="R42" t="n">
-        <v>6964042</v>
+        <v>6964169</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B43" t="n">
-        <v>80080</v>
+        <v>98267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R43" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877321</v>
+        <v>125877268</v>
       </c>
       <c r="B44" t="n">
-        <v>98258</v>
+        <v>80083</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540855</v>
+        <v>540907</v>
       </c>
       <c r="R44" t="n">
-        <v>6964125</v>
+        <v>6964097</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877316</v>
+        <v>125877321</v>
       </c>
       <c r="B45" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540803</v>
+        <v>540855</v>
       </c>
       <c r="R45" t="n">
-        <v>6964060</v>
+        <v>6964125</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877268</v>
+        <v>125877316</v>
       </c>
       <c r="B46" t="n">
-        <v>80080</v>
+        <v>98267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540907</v>
+        <v>540803</v>
       </c>
       <c r="R46" t="n">
-        <v>6964097</v>
+        <v>6964060</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5054,7 +5054,7 @@
         <v>125877299</v>
       </c>
       <c r="B47" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>125877242</v>
       </c>
       <c r="B48" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>125877243</v>
       </c>
       <c r="B49" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>125877263</v>
       </c>
       <c r="B50" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>125877244</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>125877341</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>125877350</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>125877285</v>
       </c>
       <c r="B54" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5827,32 +5827,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877305</v>
+        <v>125877238</v>
       </c>
       <c r="B55" t="n">
-        <v>56839</v>
+        <v>98384</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102612</v>
+        <v>219847</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540783</v>
+        <v>540793</v>
       </c>
       <c r="R55" t="n">
-        <v>6964091</v>
+        <v>6964055</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5898,11 +5898,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5929,32 +5924,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877238</v>
+        <v>125877305</v>
       </c>
       <c r="B56" t="n">
-        <v>98375</v>
+        <v>56840</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5964,10 +5959,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540793</v>
+        <v>540783</v>
       </c>
       <c r="R56" t="n">
-        <v>6964055</v>
+        <v>6964091</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6000,6 +5995,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877309</v>
+        <v>125877292</v>
       </c>
       <c r="B57" t="n">
-        <v>98258</v>
+        <v>80043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540880</v>
+        <v>540811</v>
       </c>
       <c r="R57" t="n">
-        <v>6964142</v>
+        <v>6964057</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,10 +6123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877330</v>
+        <v>125877309</v>
       </c>
       <c r="B58" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540792</v>
+        <v>540880</v>
       </c>
       <c r="R58" t="n">
-        <v>6964061</v>
+        <v>6964142</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877330</v>
       </c>
       <c r="B59" t="n">
-        <v>98352</v>
+        <v>98267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540792</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964061</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,32 +6317,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877294</v>
       </c>
       <c r="B60" t="n">
-        <v>80040</v>
+        <v>98361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540750</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964085</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6414,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877237</v>
+        <v>125877308</v>
       </c>
       <c r="B61" t="n">
-        <v>98375</v>
+        <v>98267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6425,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6449,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540794</v>
+        <v>540863</v>
       </c>
       <c r="R61" t="n">
-        <v>6964056</v>
+        <v>6964152</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877308</v>
+        <v>125877237</v>
       </c>
       <c r="B62" t="n">
-        <v>98258</v>
+        <v>98384</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6522,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540863</v>
+        <v>540794</v>
       </c>
       <c r="R62" t="n">
-        <v>6964152</v>
+        <v>6964056</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877235</v>
+        <v>125877279</v>
       </c>
       <c r="B63" t="n">
-        <v>98375</v>
+        <v>80083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540804</v>
+        <v>540793</v>
       </c>
       <c r="R63" t="n">
-        <v>6964049</v>
+        <v>6963960</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,32 +6705,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877326</v>
+        <v>125877282</v>
       </c>
       <c r="B64" t="n">
-        <v>98258</v>
+        <v>80083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540801</v>
+        <v>540758</v>
       </c>
       <c r="R64" t="n">
-        <v>6964059</v>
+        <v>6963956</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877279</v>
+        <v>125877262</v>
       </c>
       <c r="B65" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540793</v>
+        <v>540818</v>
       </c>
       <c r="R65" t="n">
-        <v>6963960</v>
+        <v>6964054</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877282</v>
+        <v>125877326</v>
       </c>
       <c r="B66" t="n">
-        <v>80080</v>
+        <v>98267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540758</v>
+        <v>540801</v>
       </c>
       <c r="R66" t="n">
-        <v>6963956</v>
+        <v>6964059</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,32 +6996,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877262</v>
+        <v>125877235</v>
       </c>
       <c r="B67" t="n">
-        <v>80080</v>
+        <v>98384</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540818</v>
+        <v>540804</v>
       </c>
       <c r="R67" t="n">
-        <v>6964054</v>
+        <v>6964049</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7096,7 +7096,7 @@
         <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>125877354</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>125877270</v>
       </c>
       <c r="B70" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>125877247</v>
       </c>
       <c r="B71" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>125877258</v>
       </c>
       <c r="B72" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7578,32 +7578,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877301</v>
+        <v>125877344</v>
       </c>
       <c r="B73" t="n">
-        <v>98352</v>
+        <v>78980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540963</v>
+        <v>540975</v>
       </c>
       <c r="R73" t="n">
-        <v>6964113</v>
+        <v>6964085</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7678,7 +7678,7 @@
         <v>125877302</v>
       </c>
       <c r="B74" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7772,32 +7772,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877344</v>
+        <v>125877301</v>
       </c>
       <c r="B75" t="n">
-        <v>78977</v>
+        <v>98361</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540975</v>
+        <v>540963</v>
       </c>
       <c r="R75" t="n">
-        <v>6964085</v>
+        <v>6964113</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7872,7 +7872,7 @@
         <v>125877290</v>
       </c>
       <c r="B76" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>125877319</v>
       </c>
       <c r="B77" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>125877232</v>
       </c>
       <c r="B78" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877312</v>
+        <v>125877297</v>
       </c>
       <c r="B79" t="n">
-        <v>98258</v>
+        <v>98361</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540881</v>
+        <v>540874</v>
       </c>
       <c r="R79" t="n">
-        <v>6964135</v>
+        <v>6964063</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,32 +8257,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877297</v>
+        <v>125877245</v>
       </c>
       <c r="B80" t="n">
-        <v>98352</v>
+        <v>98382</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540874</v>
+        <v>540964</v>
       </c>
       <c r="R80" t="n">
-        <v>6964063</v>
+        <v>6964121</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8357,7 +8357,7 @@
         <v>125877241</v>
       </c>
       <c r="B81" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877245</v>
+        <v>125877272</v>
       </c>
       <c r="B82" t="n">
-        <v>98373</v>
+        <v>80083</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540964</v>
+        <v>540806</v>
       </c>
       <c r="R82" t="n">
-        <v>6964121</v>
+        <v>6964062</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8551,7 +8551,7 @@
         <v>125877274</v>
       </c>
       <c r="B83" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877272</v>
+        <v>125877312</v>
       </c>
       <c r="B84" t="n">
-        <v>80080</v>
+        <v>98267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540806</v>
+        <v>540881</v>
       </c>
       <c r="R84" t="n">
-        <v>6964062</v>
+        <v>6964135</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877315</v>
+        <v>125877275</v>
       </c>
       <c r="B13" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540848</v>
+        <v>540780</v>
       </c>
       <c r="R13" t="n">
-        <v>6964091</v>
+        <v>6963983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877275</v>
+        <v>125877277</v>
       </c>
       <c r="B14" t="n">
         <v>80083</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540780</v>
+        <v>540786</v>
       </c>
       <c r="R14" t="n">
-        <v>6963983</v>
+        <v>6963974</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877277</v>
+        <v>125877264</v>
       </c>
       <c r="B15" t="n">
         <v>80083</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540786</v>
+        <v>540828</v>
       </c>
       <c r="R15" t="n">
-        <v>6963974</v>
+        <v>6964037</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877264</v>
+        <v>125877315</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540828</v>
+        <v>540848</v>
       </c>
       <c r="R16" t="n">
-        <v>6964037</v>
+        <v>6964091</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877320</v>
+        <v>125877276</v>
       </c>
       <c r="B24" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540882</v>
+        <v>540785</v>
       </c>
       <c r="R24" t="n">
-        <v>6964142</v>
+        <v>6963977</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877276</v>
+        <v>125877278</v>
       </c>
       <c r="B25" t="n">
         <v>80083</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540785</v>
+        <v>540790</v>
       </c>
       <c r="R25" t="n">
-        <v>6963977</v>
+        <v>6963972</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877278</v>
+        <v>125877269</v>
       </c>
       <c r="B26" t="n">
         <v>80083</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540790</v>
+        <v>540964</v>
       </c>
       <c r="R26" t="n">
-        <v>6963972</v>
+        <v>6964121</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877269</v>
+        <v>125877261</v>
       </c>
       <c r="B27" t="n">
         <v>80083</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540964</v>
+        <v>540807</v>
       </c>
       <c r="R27" t="n">
-        <v>6964121</v>
+        <v>6964030</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877261</v>
+        <v>125877320</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R28" t="n">
-        <v>6964030</v>
+        <v>6964142</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877303</v>
       </c>
       <c r="B38" t="n">
-        <v>98267</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540785</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6963977</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877335</v>
       </c>
       <c r="B39" t="n">
         <v>98267</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540781</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964010</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877317</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>98267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540850</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964055</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4760,32 +4760,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877268</v>
+        <v>125877321</v>
       </c>
       <c r="B44" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540907</v>
+        <v>540855</v>
       </c>
       <c r="R44" t="n">
-        <v>6964097</v>
+        <v>6964125</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877321</v>
+        <v>125877316</v>
       </c>
       <c r="B45" t="n">
         <v>98267</v>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540855</v>
+        <v>540803</v>
       </c>
       <c r="R45" t="n">
-        <v>6964125</v>
+        <v>6964060</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877316</v>
+        <v>125877299</v>
       </c>
       <c r="B46" t="n">
-        <v>98267</v>
+        <v>98361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540803</v>
+        <v>540927</v>
       </c>
       <c r="R46" t="n">
-        <v>6964060</v>
+        <v>6964119</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5051,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877299</v>
+        <v>125877242</v>
       </c>
       <c r="B47" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540927</v>
+        <v>540803</v>
       </c>
       <c r="R47" t="n">
-        <v>6964119</v>
+        <v>6964019</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877242</v>
+        <v>125877243</v>
       </c>
       <c r="B48" t="n">
         <v>98382</v>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540803</v>
+        <v>540821</v>
       </c>
       <c r="R48" t="n">
-        <v>6964019</v>
+        <v>6964051</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877243</v>
+        <v>125877268</v>
       </c>
       <c r="B49" t="n">
-        <v>98382</v>
+        <v>80083</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540821</v>
+        <v>540907</v>
       </c>
       <c r="R49" t="n">
-        <v>6964051</v>
+        <v>6964097</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877292</v>
+        <v>125877309</v>
       </c>
       <c r="B57" t="n">
-        <v>80043</v>
+        <v>98267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>504</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540811</v>
+        <v>540880</v>
       </c>
       <c r="R57" t="n">
-        <v>6964057</v>
+        <v>6964142</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,7 +6123,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877309</v>
+        <v>125877330</v>
       </c>
       <c r="B58" t="n">
         <v>98267</v>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540880</v>
+        <v>540792</v>
       </c>
       <c r="R58" t="n">
-        <v>6964142</v>
+        <v>6964061</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877330</v>
+        <v>125877294</v>
       </c>
       <c r="B59" t="n">
-        <v>98267</v>
+        <v>98361</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540792</v>
+        <v>540750</v>
       </c>
       <c r="R59" t="n">
-        <v>6964061</v>
+        <v>6964085</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,32 +6317,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877294</v>
+        <v>125877292</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>80043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540750</v>
+        <v>540811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964085</v>
+        <v>6964057</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877279</v>
+        <v>125877326</v>
       </c>
       <c r="B63" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540793</v>
+        <v>540801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963960</v>
+        <v>6964059</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877282</v>
+        <v>125877279</v>
       </c>
       <c r="B64" t="n">
         <v>80083</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540758</v>
+        <v>540793</v>
       </c>
       <c r="R64" t="n">
-        <v>6963956</v>
+        <v>6963960</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877262</v>
+        <v>125877282</v>
       </c>
       <c r="B65" t="n">
         <v>80083</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540818</v>
+        <v>540758</v>
       </c>
       <c r="R65" t="n">
-        <v>6964054</v>
+        <v>6963956</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877326</v>
+        <v>125877262</v>
       </c>
       <c r="B66" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540801</v>
+        <v>540818</v>
       </c>
       <c r="R66" t="n">
-        <v>6964059</v>
+        <v>6964054</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877235</v>
+        <v>125877246</v>
       </c>
       <c r="B67" t="n">
-        <v>98384</v>
+        <v>98382</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540804</v>
+        <v>540789</v>
       </c>
       <c r="R67" t="n">
-        <v>6964049</v>
+        <v>6964012</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877235</v>
       </c>
       <c r="B68" t="n">
-        <v>98382</v>
+        <v>98384</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540804</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964049</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877259</v>
+        <v>125877322</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540760</v>
+        <v>540809</v>
       </c>
       <c r="R2" t="n">
-        <v>6964020</v>
+        <v>6964096</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877271</v>
+        <v>125877332</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540996</v>
+        <v>540794</v>
       </c>
       <c r="R3" t="n">
-        <v>6964140</v>
+        <v>6964056</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877332</v>
+        <v>125877310</v>
       </c>
       <c r="B4" t="n">
         <v>98267</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540794</v>
+        <v>540890</v>
       </c>
       <c r="R4" t="n">
-        <v>6964056</v>
+        <v>6964145</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877322</v>
+        <v>125877304</v>
       </c>
       <c r="B5" t="n">
-        <v>98267</v>
+        <v>56840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>504</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540809</v>
+        <v>540740</v>
       </c>
       <c r="R5" t="n">
-        <v>6964096</v>
+        <v>6964067</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877310</v>
+        <v>125877296</v>
       </c>
       <c r="B6" t="n">
-        <v>98267</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540890</v>
+        <v>540787</v>
       </c>
       <c r="R6" t="n">
-        <v>6964145</v>
+        <v>6964017</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877304</v>
+        <v>125877300</v>
       </c>
       <c r="B7" t="n">
-        <v>56840</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540740</v>
+        <v>540937</v>
       </c>
       <c r="R7" t="n">
-        <v>6964067</v>
+        <v>6964110</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1231,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877296</v>
+        <v>125877259</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540787</v>
+        <v>540760</v>
       </c>
       <c r="R9" t="n">
-        <v>6964017</v>
+        <v>6964020</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877300</v>
+        <v>125877271</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540937</v>
+        <v>540996</v>
       </c>
       <c r="R10" t="n">
-        <v>6964110</v>
+        <v>6964140</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877275</v>
+        <v>125877315</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540780</v>
+        <v>540848</v>
       </c>
       <c r="R13" t="n">
-        <v>6963983</v>
+        <v>6964091</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877277</v>
+        <v>125877275</v>
       </c>
       <c r="B14" t="n">
         <v>80083</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540786</v>
+        <v>540780</v>
       </c>
       <c r="R14" t="n">
-        <v>6963974</v>
+        <v>6963983</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877264</v>
+        <v>125877277</v>
       </c>
       <c r="B15" t="n">
         <v>80083</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540828</v>
+        <v>540786</v>
       </c>
       <c r="R15" t="n">
-        <v>6964037</v>
+        <v>6963974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877315</v>
+        <v>125877264</v>
       </c>
       <c r="B16" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540848</v>
+        <v>540828</v>
       </c>
       <c r="R16" t="n">
-        <v>6964091</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877240</v>
+        <v>125877318</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>98267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2146,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540848</v>
+        <v>540850</v>
       </c>
       <c r="R17" t="n">
-        <v>6964065</v>
+        <v>6964070</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2214,7 +2214,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2233,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877318</v>
+        <v>125877311</v>
       </c>
       <c r="B18" t="n">
         <v>98267</v>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540850</v>
+        <v>540889</v>
       </c>
       <c r="R18" t="n">
-        <v>6964070</v>
+        <v>6964139</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2330,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877311</v>
+        <v>125877240</v>
       </c>
       <c r="B19" t="n">
-        <v>98267</v>
+        <v>98382</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2341,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2365,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540889</v>
+        <v>540848</v>
       </c>
       <c r="R19" t="n">
-        <v>6964139</v>
+        <v>6964065</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2409,6 +2408,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877313</v>
+        <v>125877295</v>
       </c>
       <c r="B20" t="n">
-        <v>98267</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540882</v>
+        <v>540765</v>
       </c>
       <c r="R20" t="n">
-        <v>6964119</v>
+        <v>6964025</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877284</v>
+        <v>125877313</v>
       </c>
       <c r="B21" t="n">
-        <v>80119</v>
+        <v>98267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2559,10 +2559,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540807</v>
+        <v>540882</v>
       </c>
       <c r="R21" t="n">
-        <v>6964031</v>
+        <v>6964119</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,32 +2621,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877260</v>
+        <v>125877284</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540800</v>
+        <v>540807</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964031</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2718,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877295</v>
+        <v>125877260</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540765</v>
+        <v>540800</v>
       </c>
       <c r="R23" t="n">
-        <v>6964025</v>
+        <v>6964021</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2815,32 +2815,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877276</v>
+        <v>125877320</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540785</v>
+        <v>540882</v>
       </c>
       <c r="R24" t="n">
-        <v>6963977</v>
+        <v>6964142</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877278</v>
+        <v>125877276</v>
       </c>
       <c r="B25" t="n">
         <v>80083</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540790</v>
+        <v>540785</v>
       </c>
       <c r="R25" t="n">
-        <v>6963972</v>
+        <v>6963977</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877269</v>
+        <v>125877278</v>
       </c>
       <c r="B26" t="n">
         <v>80083</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540964</v>
+        <v>540790</v>
       </c>
       <c r="R26" t="n">
-        <v>6964121</v>
+        <v>6963972</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877261</v>
+        <v>125877269</v>
       </c>
       <c r="B27" t="n">
         <v>80083</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540807</v>
+        <v>540964</v>
       </c>
       <c r="R27" t="n">
-        <v>6964030</v>
+        <v>6964121</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,32 +3203,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877320</v>
+        <v>125877261</v>
       </c>
       <c r="B28" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3238,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540882</v>
+        <v>540807</v>
       </c>
       <c r="R28" t="n">
-        <v>6964142</v>
+        <v>6964030</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3397,32 +3397,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877298</v>
+        <v>125877306</v>
       </c>
       <c r="B30" t="n">
-        <v>98361</v>
+        <v>98267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540912</v>
+        <v>540793</v>
       </c>
       <c r="R30" t="n">
-        <v>6964122</v>
+        <v>6964055</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,6 +3468,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3494,7 +3499,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877306</v>
+        <v>125877252</v>
       </c>
       <c r="B31" t="n">
         <v>98267</v>
@@ -3529,10 +3534,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540793</v>
+        <v>540788</v>
       </c>
       <c r="R31" t="n">
-        <v>6964055</v>
+        <v>6964033</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3565,11 +3570,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3596,32 +3596,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877366</v>
+        <v>125877314</v>
       </c>
       <c r="B32" t="n">
-        <v>88654</v>
+        <v>98267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540874</v>
+        <v>540853</v>
       </c>
       <c r="R32" t="n">
-        <v>6964114</v>
+        <v>6964095</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,32 +3693,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877323</v>
+        <v>125877366</v>
       </c>
       <c r="B33" t="n">
-        <v>98267</v>
+        <v>88654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540803</v>
+        <v>540874</v>
       </c>
       <c r="R33" t="n">
-        <v>6964102</v>
+        <v>6964114</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877314</v>
+        <v>125877323</v>
       </c>
       <c r="B34" t="n">
         <v>98267</v>
@@ -3825,10 +3825,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540853</v>
+        <v>540803</v>
       </c>
       <c r="R34" t="n">
-        <v>6964095</v>
+        <v>6964102</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,32 +3887,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877252</v>
+        <v>125877273</v>
       </c>
       <c r="B35" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540788</v>
+        <v>540797</v>
       </c>
       <c r="R35" t="n">
-        <v>6964033</v>
+        <v>6964057</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877273</v>
+        <v>125877266</v>
       </c>
       <c r="B36" t="n">
         <v>80083</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540797</v>
+        <v>540868</v>
       </c>
       <c r="R36" t="n">
-        <v>6964057</v>
+        <v>6964062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4081,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877266</v>
+        <v>125877298</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540868</v>
+        <v>540912</v>
       </c>
       <c r="R37" t="n">
-        <v>6964062</v>
+        <v>6964122</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4178,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877303</v>
+        <v>125877335</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R38" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877335</v>
+        <v>125877317</v>
       </c>
       <c r="B39" t="n">
         <v>98267</v>
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540781</v>
+        <v>540850</v>
       </c>
       <c r="R39" t="n">
-        <v>6964010</v>
+        <v>6964055</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4372,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877317</v>
+        <v>125877303</v>
       </c>
       <c r="B40" t="n">
-        <v>98267</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540850</v>
+        <v>540785</v>
       </c>
       <c r="R40" t="n">
-        <v>6964055</v>
+        <v>6963977</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877267</v>
+        <v>125877307</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>98267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540893</v>
+        <v>540788</v>
       </c>
       <c r="R41" t="n">
-        <v>6964069</v>
+        <v>6964042</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125877307</v>
+        <v>125877267</v>
       </c>
       <c r="B43" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540788</v>
+        <v>540893</v>
       </c>
       <c r="R43" t="n">
-        <v>6964042</v>
+        <v>6964069</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -4760,7 +4760,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877321</v>
+        <v>125877316</v>
       </c>
       <c r="B44" t="n">
         <v>98267</v>
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540855</v>
+        <v>540803</v>
       </c>
       <c r="R44" t="n">
-        <v>6964125</v>
+        <v>6964060</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,7 +4857,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877316</v>
+        <v>125877321</v>
       </c>
       <c r="B45" t="n">
         <v>98267</v>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540803</v>
+        <v>540855</v>
       </c>
       <c r="R45" t="n">
-        <v>6964060</v>
+        <v>6964125</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,32 +4954,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877299</v>
+        <v>125877268</v>
       </c>
       <c r="B46" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540927</v>
+        <v>540907</v>
       </c>
       <c r="R46" t="n">
-        <v>6964119</v>
+        <v>6964097</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5245,32 +5245,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877268</v>
+        <v>125877299</v>
       </c>
       <c r="B49" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540907</v>
+        <v>540927</v>
       </c>
       <c r="R49" t="n">
-        <v>6964097</v>
+        <v>6964119</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5536,32 +5536,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877341</v>
+        <v>125877285</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>80119</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540852</v>
+        <v>540907</v>
       </c>
       <c r="R52" t="n">
-        <v>6964074</v>
+        <v>6964097</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,32 +5633,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877350</v>
+        <v>125877238</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>98384</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540785</v>
+        <v>540793</v>
       </c>
       <c r="R53" t="n">
-        <v>6964039</v>
+        <v>6964055</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,32 +5730,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877285</v>
+        <v>125877341</v>
       </c>
       <c r="B54" t="n">
-        <v>80119</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540907</v>
+        <v>540852</v>
       </c>
       <c r="R54" t="n">
-        <v>6964097</v>
+        <v>6964074</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5827,32 +5827,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877238</v>
+        <v>125877350</v>
       </c>
       <c r="B55" t="n">
-        <v>98384</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5862,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540793</v>
+        <v>540785</v>
       </c>
       <c r="R55" t="n">
-        <v>6964055</v>
+        <v>6964039</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6026,10 +6026,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877309</v>
+        <v>125877292</v>
       </c>
       <c r="B57" t="n">
-        <v>98267</v>
+        <v>80043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6037,21 +6037,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>504</v>
+        <v>229497</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540880</v>
+        <v>540811</v>
       </c>
       <c r="R57" t="n">
-        <v>6964142</v>
+        <v>6964057</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,7 +6123,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877330</v>
+        <v>125877309</v>
       </c>
       <c r="B58" t="n">
         <v>98267</v>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540792</v>
+        <v>540880</v>
       </c>
       <c r="R58" t="n">
-        <v>6964061</v>
+        <v>6964142</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877294</v>
+        <v>125877330</v>
       </c>
       <c r="B59" t="n">
-        <v>98361</v>
+        <v>98267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540750</v>
+        <v>540792</v>
       </c>
       <c r="R59" t="n">
-        <v>6964085</v>
+        <v>6964061</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,32 +6317,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877292</v>
+        <v>125877294</v>
       </c>
       <c r="B60" t="n">
-        <v>80043</v>
+        <v>98361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540811</v>
+        <v>540750</v>
       </c>
       <c r="R60" t="n">
-        <v>6964057</v>
+        <v>6964085</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6608,32 +6608,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877326</v>
+        <v>125877279</v>
       </c>
       <c r="B63" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540801</v>
+        <v>540793</v>
       </c>
       <c r="R63" t="n">
-        <v>6964059</v>
+        <v>6963960</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877279</v>
+        <v>125877282</v>
       </c>
       <c r="B64" t="n">
         <v>80083</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540793</v>
+        <v>540758</v>
       </c>
       <c r="R64" t="n">
-        <v>6963960</v>
+        <v>6963956</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877282</v>
+        <v>125877262</v>
       </c>
       <c r="B65" t="n">
         <v>80083</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540758</v>
+        <v>540818</v>
       </c>
       <c r="R65" t="n">
-        <v>6963956</v>
+        <v>6964054</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,32 +6899,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877262</v>
+        <v>125877235</v>
       </c>
       <c r="B66" t="n">
-        <v>80083</v>
+        <v>98384</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540818</v>
+        <v>540804</v>
       </c>
       <c r="R66" t="n">
-        <v>6964054</v>
+        <v>6964049</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877246</v>
+        <v>125877326</v>
       </c>
       <c r="B67" t="n">
-        <v>98382</v>
+        <v>98267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7007,21 +7007,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540789</v>
+        <v>540801</v>
       </c>
       <c r="R67" t="n">
-        <v>6964012</v>
+        <v>6964059</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7093,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877235</v>
+        <v>125877246</v>
       </c>
       <c r="B68" t="n">
-        <v>98384</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7104,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540804</v>
+        <v>540789</v>
       </c>
       <c r="R68" t="n">
-        <v>6964049</v>
+        <v>6964012</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877354</v>
+        <v>125877270</v>
       </c>
       <c r="B69" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7201,21 +7201,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540781</v>
+        <v>540970</v>
       </c>
       <c r="R69" t="n">
-        <v>6963980</v>
+        <v>6964115</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,10 +7287,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877270</v>
+        <v>125877354</v>
       </c>
       <c r="B70" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7298,21 +7298,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7322,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540970</v>
+        <v>540781</v>
       </c>
       <c r="R70" t="n">
-        <v>6964115</v>
+        <v>6963980</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7481,10 +7481,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877258</v>
+        <v>125877344</v>
       </c>
       <c r="B72" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7492,21 +7492,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540749</v>
+        <v>540975</v>
       </c>
       <c r="R72" t="n">
-        <v>6964056</v>
+        <v>6964085</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877344</v>
+        <v>125877258</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7589,21 +7589,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540975</v>
+        <v>540749</v>
       </c>
       <c r="R73" t="n">
-        <v>6964085</v>
+        <v>6964056</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8160,32 +8160,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877297</v>
+        <v>125877312</v>
       </c>
       <c r="B79" t="n">
-        <v>98361</v>
+        <v>98267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8195,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540874</v>
+        <v>540881</v>
       </c>
       <c r="R79" t="n">
-        <v>6964063</v>
+        <v>6964135</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,7 +8257,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877245</v>
+        <v>125877241</v>
       </c>
       <c r="B80" t="n">
         <v>98382</v>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540964</v>
+        <v>540752</v>
       </c>
       <c r="R80" t="n">
-        <v>6964121</v>
+        <v>6964040</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877241</v>
+        <v>125877245</v>
       </c>
       <c r="B81" t="n">
         <v>98382</v>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540752</v>
+        <v>540964</v>
       </c>
       <c r="R81" t="n">
-        <v>6964040</v>
+        <v>6964121</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877272</v>
+        <v>125877297</v>
       </c>
       <c r="B82" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540806</v>
+        <v>540874</v>
       </c>
       <c r="R82" t="n">
-        <v>6964062</v>
+        <v>6964063</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,7 +8548,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877274</v>
+        <v>125877272</v>
       </c>
       <c r="B83" t="n">
         <v>80083</v>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540794</v>
+        <v>540806</v>
       </c>
       <c r="R83" t="n">
-        <v>6964003</v>
+        <v>6964062</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877312</v>
+        <v>125877274</v>
       </c>
       <c r="B84" t="n">
-        <v>98267</v>
+        <v>80083</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540881</v>
+        <v>540794</v>
       </c>
       <c r="R84" t="n">
-        <v>6964135</v>
+        <v>6964003</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125877322</v>
+        <v>125877252</v>
       </c>
       <c r="B2" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540809</v>
+        <v>540788</v>
       </c>
       <c r="R2" t="n">
-        <v>6964096</v>
+        <v>6964033</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125877332</v>
+        <v>125877306</v>
       </c>
       <c r="B3" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540794</v>
+        <v>540793</v>
       </c>
       <c r="R3" t="n">
-        <v>6964056</v>
+        <v>6964055</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125877310</v>
+        <v>125877307</v>
       </c>
       <c r="B4" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540890</v>
+        <v>540788</v>
       </c>
       <c r="R4" t="n">
-        <v>6964145</v>
+        <v>6964042</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125877304</v>
+        <v>125877308</v>
       </c>
       <c r="B5" t="n">
-        <v>56840</v>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540740</v>
+        <v>540863</v>
       </c>
       <c r="R5" t="n">
-        <v>6964067</v>
+        <v>6964152</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125877296</v>
+        <v>125877309</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540787</v>
+        <v>540880</v>
       </c>
       <c r="R6" t="n">
-        <v>6964017</v>
+        <v>6964142</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125877300</v>
+        <v>125877310</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540937</v>
+        <v>540890</v>
       </c>
       <c r="R7" t="n">
-        <v>6964110</v>
+        <v>6964145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125877339</v>
+        <v>125877311</v>
       </c>
       <c r="B8" t="n">
-        <v>105396</v>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540959</v>
+        <v>540889</v>
       </c>
       <c r="R8" t="n">
-        <v>6964030</v>
+        <v>6964139</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125877259</v>
+        <v>125877312</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540760</v>
+        <v>540881</v>
       </c>
       <c r="R9" t="n">
-        <v>6964020</v>
+        <v>6964135</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125877271</v>
+        <v>125877313</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540996</v>
+        <v>540882</v>
       </c>
       <c r="R10" t="n">
-        <v>6964140</v>
+        <v>6964119</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125877324</v>
+        <v>125877314</v>
       </c>
       <c r="B11" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540804</v>
+        <v>540853</v>
       </c>
       <c r="R11" t="n">
-        <v>6964092</v>
+        <v>6964095</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125877236</v>
+        <v>125877315</v>
       </c>
       <c r="B12" t="n">
-        <v>98384</v>
+        <v>99024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540802</v>
+        <v>540848</v>
       </c>
       <c r="R12" t="n">
-        <v>6964109</v>
+        <v>6964091</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125877315</v>
+        <v>125877316</v>
       </c>
       <c r="B13" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540848</v>
+        <v>540803</v>
       </c>
       <c r="R13" t="n">
-        <v>6964091</v>
+        <v>6964060</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125877275</v>
+        <v>125877317</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540780</v>
+        <v>540850</v>
       </c>
       <c r="R14" t="n">
-        <v>6963983</v>
+        <v>6964055</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125877277</v>
+        <v>125877318</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540786</v>
+        <v>540850</v>
       </c>
       <c r="R15" t="n">
-        <v>6963974</v>
+        <v>6964070</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125877264</v>
+        <v>125877319</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540828</v>
+        <v>540883</v>
       </c>
       <c r="R16" t="n">
-        <v>6964037</v>
+        <v>6964145</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125877318</v>
+        <v>125877320</v>
       </c>
       <c r="B17" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540850</v>
+        <v>540882</v>
       </c>
       <c r="R17" t="n">
-        <v>6964070</v>
+        <v>6964142</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125877311</v>
+        <v>125877321</v>
       </c>
       <c r="B18" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540889</v>
+        <v>540855</v>
       </c>
       <c r="R18" t="n">
-        <v>6964139</v>
+        <v>6964125</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125877240</v>
+        <v>125877322</v>
       </c>
       <c r="B19" t="n">
-        <v>98382</v>
+        <v>99024</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2340,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540848</v>
+        <v>540809</v>
       </c>
       <c r="R19" t="n">
-        <v>6964065</v>
+        <v>6964096</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2408,7 +2408,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2427,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125877295</v>
+        <v>125877323</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>99024</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>504</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2462,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540765</v>
+        <v>540803</v>
       </c>
       <c r="R20" t="n">
-        <v>6964025</v>
+        <v>6964102</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2524,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125877313</v>
+        <v>125877324</v>
       </c>
       <c r="B21" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2559,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540882</v>
+        <v>540804</v>
       </c>
       <c r="R21" t="n">
-        <v>6964119</v>
+        <v>6964092</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2621,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125877284</v>
+        <v>125877326</v>
       </c>
       <c r="B22" t="n">
-        <v>80119</v>
+        <v>99024</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2632,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>504</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2656,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540807</v>
+        <v>540801</v>
       </c>
       <c r="R22" t="n">
-        <v>6964031</v>
+        <v>6964059</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2718,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125877260</v>
+        <v>125877330</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2753,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540800</v>
+        <v>540792</v>
       </c>
       <c r="R23" t="n">
-        <v>6964021</v>
+        <v>6964061</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2815,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125877320</v>
+        <v>125877332</v>
       </c>
       <c r="B24" t="n">
-        <v>98267</v>
+        <v>99024</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540882</v>
+        <v>540794</v>
       </c>
       <c r="R24" t="n">
-        <v>6964142</v>
+        <v>6964056</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2912,32 +2911,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125877276</v>
+        <v>125877335</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>99024</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2947,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540785</v>
+        <v>540781</v>
       </c>
       <c r="R25" t="n">
-        <v>6963977</v>
+        <v>6964010</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3009,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125877278</v>
+        <v>125877366</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>89292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3020,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3044,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540790</v>
+        <v>540874</v>
       </c>
       <c r="R26" t="n">
-        <v>6963972</v>
+        <v>6964114</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3106,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125877269</v>
+        <v>125877232</v>
       </c>
       <c r="B27" t="n">
-        <v>80083</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3117,21 +3116,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540964</v>
+        <v>540989</v>
       </c>
       <c r="R27" t="n">
-        <v>6964121</v>
+        <v>6964130</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3203,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125877261</v>
+        <v>125877341</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3238,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540807</v>
+        <v>540852</v>
       </c>
       <c r="R28" t="n">
-        <v>6964030</v>
+        <v>6964074</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3300,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125877291</v>
+        <v>125877344</v>
       </c>
       <c r="B29" t="n">
-        <v>80043</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3335,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540908</v>
+        <v>540975</v>
       </c>
       <c r="R29" t="n">
-        <v>6964094</v>
+        <v>6964085</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3397,32 +3396,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125877306</v>
+        <v>125877347</v>
       </c>
       <c r="B30" t="n">
-        <v>98267</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3432,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540793</v>
+        <v>540997</v>
       </c>
       <c r="R30" t="n">
-        <v>6964055</v>
+        <v>6964169</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3468,11 +3467,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>God Förekomst</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3499,32 +3493,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125877252</v>
+        <v>125877350</v>
       </c>
       <c r="B31" t="n">
-        <v>98267</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540788</v>
+        <v>540785</v>
       </c>
       <c r="R31" t="n">
-        <v>6964033</v>
+        <v>6964039</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3596,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125877314</v>
+        <v>125877354</v>
       </c>
       <c r="B32" t="n">
-        <v>98267</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540853</v>
+        <v>540781</v>
       </c>
       <c r="R32" t="n">
-        <v>6964095</v>
+        <v>6963980</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3693,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125877366</v>
+        <v>125877357</v>
       </c>
       <c r="B33" t="n">
-        <v>88654</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540874</v>
+        <v>540726</v>
       </c>
       <c r="R33" t="n">
-        <v>6964114</v>
+        <v>6963972</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3790,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125877323</v>
+        <v>125877258</v>
       </c>
       <c r="B34" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540803</v>
+        <v>540749</v>
       </c>
       <c r="R34" t="n">
-        <v>6964102</v>
+        <v>6964056</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3887,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125877273</v>
+        <v>125877259</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540797</v>
+        <v>540760</v>
       </c>
       <c r="R35" t="n">
-        <v>6964057</v>
+        <v>6964020</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3984,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125877266</v>
+        <v>125877260</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540868</v>
+        <v>540800</v>
       </c>
       <c r="R36" t="n">
-        <v>6964062</v>
+        <v>6964021</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4081,32 +4075,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125877298</v>
+        <v>125877261</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540912</v>
+        <v>540807</v>
       </c>
       <c r="R37" t="n">
-        <v>6964122</v>
+        <v>6964030</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4178,32 +4172,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125877335</v>
+        <v>125877262</v>
       </c>
       <c r="B38" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540781</v>
+        <v>540818</v>
       </c>
       <c r="R38" t="n">
-        <v>6964010</v>
+        <v>6964054</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4275,32 +4269,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125877317</v>
+        <v>125877263</v>
       </c>
       <c r="B39" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4310,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540850</v>
+        <v>540824</v>
       </c>
       <c r="R39" t="n">
-        <v>6964055</v>
+        <v>6964042</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4372,32 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125877303</v>
+        <v>125877264</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540785</v>
+        <v>540828</v>
       </c>
       <c r="R40" t="n">
-        <v>6963977</v>
+        <v>6964037</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4469,32 +4463,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125877307</v>
+        <v>125877265</v>
       </c>
       <c r="B41" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540788</v>
+        <v>540834</v>
       </c>
       <c r="R41" t="n">
-        <v>6964042</v>
+        <v>6964036</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4566,10 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125877347</v>
+        <v>125877266</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4577,21 +4571,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4601,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540997</v>
+        <v>540868</v>
       </c>
       <c r="R42" t="n">
-        <v>6964169</v>
+        <v>6964062</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4666,7 +4660,7 @@
         <v>125877267</v>
       </c>
       <c r="B43" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4760,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125877316</v>
+        <v>125877268</v>
       </c>
       <c r="B44" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540803</v>
+        <v>540907</v>
       </c>
       <c r="R44" t="n">
-        <v>6964060</v>
+        <v>6964097</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -4857,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125877321</v>
+        <v>125877269</v>
       </c>
       <c r="B45" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540855</v>
+        <v>540964</v>
       </c>
       <c r="R45" t="n">
-        <v>6964125</v>
+        <v>6964121</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -4954,10 +4948,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125877268</v>
+        <v>125877270</v>
       </c>
       <c r="B46" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4989,10 +4983,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540907</v>
+        <v>540970</v>
       </c>
       <c r="R46" t="n">
-        <v>6964097</v>
+        <v>6964115</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5051,32 +5045,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125877242</v>
+        <v>125877271</v>
       </c>
       <c r="B47" t="n">
-        <v>98382</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5086,10 +5080,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540803</v>
+        <v>540996</v>
       </c>
       <c r="R47" t="n">
-        <v>6964019</v>
+        <v>6964140</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5148,32 +5142,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125877243</v>
+        <v>125877272</v>
       </c>
       <c r="B48" t="n">
-        <v>98382</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5183,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540821</v>
+        <v>540806</v>
       </c>
       <c r="R48" t="n">
-        <v>6964051</v>
+        <v>6964062</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5245,32 +5239,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125877299</v>
+        <v>125877273</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5280,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540927</v>
+        <v>540797</v>
       </c>
       <c r="R49" t="n">
-        <v>6964119</v>
+        <v>6964057</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5342,10 +5336,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125877263</v>
+        <v>125877274</v>
       </c>
       <c r="B50" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5377,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540824</v>
+        <v>540794</v>
       </c>
       <c r="R50" t="n">
-        <v>6964042</v>
+        <v>6964003</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5439,32 +5433,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125877244</v>
+        <v>125877275</v>
       </c>
       <c r="B51" t="n">
-        <v>98382</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5474,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540927</v>
+        <v>540780</v>
       </c>
       <c r="R51" t="n">
-        <v>6964119</v>
+        <v>6963983</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5536,32 +5530,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125877285</v>
+        <v>125877276</v>
       </c>
       <c r="B52" t="n">
-        <v>80119</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5571,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>540907</v>
+        <v>540785</v>
       </c>
       <c r="R52" t="n">
-        <v>6964097</v>
+        <v>6963977</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5633,32 +5627,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125877238</v>
+        <v>125877277</v>
       </c>
       <c r="B53" t="n">
-        <v>98384</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5668,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>540793</v>
+        <v>540786</v>
       </c>
       <c r="R53" t="n">
-        <v>6964055</v>
+        <v>6963974</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -5730,10 +5724,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125877341</v>
+        <v>125877278</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5741,21 +5735,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5765,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>540852</v>
+        <v>540790</v>
       </c>
       <c r="R54" t="n">
-        <v>6964074</v>
+        <v>6963972</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -5827,10 +5821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125877350</v>
+        <v>125877279</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5838,21 +5832,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5862,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>540785</v>
+        <v>540793</v>
       </c>
       <c r="R55" t="n">
-        <v>6964039</v>
+        <v>6963960</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -5924,10 +5918,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125877305</v>
+        <v>125877280</v>
       </c>
       <c r="B56" t="n">
-        <v>56840</v>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5935,21 +5929,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5959,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>540783</v>
+        <v>540799</v>
       </c>
       <c r="R56" t="n">
-        <v>6964091</v>
+        <v>6963950</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -5995,11 +5989,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6026,32 +6015,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125877292</v>
+        <v>125877281</v>
       </c>
       <c r="B57" t="n">
-        <v>80043</v>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6061,10 +6050,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>540811</v>
+        <v>540798</v>
       </c>
       <c r="R57" t="n">
-        <v>6964057</v>
+        <v>6963954</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6123,32 +6112,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125877309</v>
+        <v>125877282</v>
       </c>
       <c r="B58" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6158,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>540880</v>
+        <v>540758</v>
       </c>
       <c r="R58" t="n">
-        <v>6964142</v>
+        <v>6963956</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6220,32 +6209,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125877330</v>
+        <v>125877283</v>
       </c>
       <c r="B59" t="n">
-        <v>98267</v>
+        <v>80432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6255,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>540792</v>
+        <v>540726</v>
       </c>
       <c r="R59" t="n">
-        <v>6964061</v>
+        <v>6963972</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6317,32 +6306,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125877294</v>
+        <v>125877284</v>
       </c>
       <c r="B60" t="n">
-        <v>98361</v>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6352,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>540750</v>
+        <v>540807</v>
       </c>
       <c r="R60" t="n">
-        <v>6964085</v>
+        <v>6964031</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6414,10 +6403,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125877308</v>
+        <v>125877285</v>
       </c>
       <c r="B61" t="n">
-        <v>98267</v>
+        <v>80468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6425,21 +6414,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6449,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>540863</v>
+        <v>540907</v>
       </c>
       <c r="R61" t="n">
-        <v>6964152</v>
+        <v>6964097</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6511,10 +6500,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125877237</v>
+        <v>125877287</v>
       </c>
       <c r="B62" t="n">
-        <v>98384</v>
+        <v>80468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6522,21 +6511,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219847</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6546,10 +6535,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>540794</v>
+        <v>540726</v>
       </c>
       <c r="R62" t="n">
-        <v>6964056</v>
+        <v>6963972</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6608,32 +6597,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125877279</v>
+        <v>125877304</v>
       </c>
       <c r="B63" t="n">
-        <v>80083</v>
+        <v>57132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6643,10 +6632,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>540793</v>
+        <v>540740</v>
       </c>
       <c r="R63" t="n">
-        <v>6963960</v>
+        <v>6964067</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -6679,6 +6668,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Med ungar, upprörd varnande</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6705,32 +6699,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125877282</v>
+        <v>125877305</v>
       </c>
       <c r="B64" t="n">
-        <v>80083</v>
+        <v>57132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6740,10 +6734,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>540758</v>
+        <v>540783</v>
       </c>
       <c r="R64" t="n">
-        <v>6963956</v>
+        <v>6964091</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -6776,6 +6770,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Upprörd varnande</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6802,32 +6801,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125877262</v>
+        <v>125877235</v>
       </c>
       <c r="B65" t="n">
-        <v>80083</v>
+        <v>99142</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6837,10 +6836,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>540818</v>
+        <v>540804</v>
       </c>
       <c r="R65" t="n">
-        <v>6964054</v>
+        <v>6964049</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -6899,10 +6898,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125877235</v>
+        <v>125877236</v>
       </c>
       <c r="B66" t="n">
-        <v>98384</v>
+        <v>99142</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6934,10 +6933,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>540804</v>
+        <v>540802</v>
       </c>
       <c r="R66" t="n">
-        <v>6964049</v>
+        <v>6964109</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -6996,10 +6995,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125877326</v>
+        <v>125877237</v>
       </c>
       <c r="B67" t="n">
-        <v>98267</v>
+        <v>99142</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7007,21 +7006,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>504</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7031,10 +7030,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>540801</v>
+        <v>540794</v>
       </c>
       <c r="R67" t="n">
-        <v>6964059</v>
+        <v>6964056</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7093,10 +7092,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125877246</v>
+        <v>125877238</v>
       </c>
       <c r="B68" t="n">
-        <v>98382</v>
+        <v>99142</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7104,21 +7103,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7128,10 +7127,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>540789</v>
+        <v>540793</v>
       </c>
       <c r="R68" t="n">
-        <v>6964012</v>
+        <v>6964055</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7190,32 +7189,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125877270</v>
+        <v>125877294</v>
       </c>
       <c r="B69" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7225,10 +7224,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>540970</v>
+        <v>540750</v>
       </c>
       <c r="R69" t="n">
-        <v>6964115</v>
+        <v>6964085</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7287,32 +7286,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125877354</v>
+        <v>125877295</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7322,10 +7321,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>540781</v>
+        <v>540765</v>
       </c>
       <c r="R70" t="n">
-        <v>6963980</v>
+        <v>6964025</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7384,32 +7383,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125877247</v>
+        <v>125877296</v>
       </c>
       <c r="B71" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7419,10 +7418,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>540780</v>
+        <v>540787</v>
       </c>
       <c r="R71" t="n">
-        <v>6963984</v>
+        <v>6964017</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7481,32 +7480,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125877344</v>
+        <v>125877297</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7516,10 +7515,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>540975</v>
+        <v>540874</v>
       </c>
       <c r="R72" t="n">
-        <v>6964085</v>
+        <v>6964063</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7578,32 +7577,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125877258</v>
+        <v>125877298</v>
       </c>
       <c r="B73" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7613,10 +7612,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>540749</v>
+        <v>540912</v>
       </c>
       <c r="R73" t="n">
-        <v>6964056</v>
+        <v>6964122</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -7675,10 +7674,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125877302</v>
+        <v>125877299</v>
       </c>
       <c r="B74" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7710,10 +7709,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>540970</v>
+        <v>540927</v>
       </c>
       <c r="R74" t="n">
-        <v>6964115</v>
+        <v>6964119</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -7772,10 +7771,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125877301</v>
+        <v>125877300</v>
       </c>
       <c r="B75" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7807,10 +7806,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>540963</v>
+        <v>540937</v>
       </c>
       <c r="R75" t="n">
-        <v>6964113</v>
+        <v>6964110</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -7869,32 +7868,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125877290</v>
+        <v>125877301</v>
       </c>
       <c r="B76" t="n">
-        <v>80043</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7904,10 +7903,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>540819</v>
+        <v>540963</v>
       </c>
       <c r="R76" t="n">
-        <v>6964057</v>
+        <v>6964113</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -7966,32 +7965,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125877319</v>
+        <v>125877302</v>
       </c>
       <c r="B77" t="n">
-        <v>98267</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>504</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8001,10 +8000,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>540883</v>
+        <v>540970</v>
       </c>
       <c r="R77" t="n">
-        <v>6964145</v>
+        <v>6964115</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8063,32 +8062,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125877232</v>
+        <v>125877303</v>
       </c>
       <c r="B78" t="n">
-        <v>91245</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8098,10 +8097,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>540989</v>
+        <v>540785</v>
       </c>
       <c r="R78" t="n">
-        <v>6964130</v>
+        <v>6963977</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8160,10 +8159,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125877312</v>
+        <v>125877339</v>
       </c>
       <c r="B79" t="n">
-        <v>98267</v>
+        <v>106244</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8171,21 +8170,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>504</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8195,10 +8194,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>540881</v>
+        <v>540959</v>
       </c>
       <c r="R79" t="n">
-        <v>6964135</v>
+        <v>6964030</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8257,10 +8256,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125877241</v>
+        <v>125877240</v>
       </c>
       <c r="B80" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8292,10 +8291,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>540752</v>
+        <v>540848</v>
       </c>
       <c r="R80" t="n">
-        <v>6964040</v>
+        <v>6964065</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8336,6 +8335,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8354,10 +8354,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125877245</v>
+        <v>125877241</v>
       </c>
       <c r="B81" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>540964</v>
+        <v>540752</v>
       </c>
       <c r="R81" t="n">
-        <v>6964121</v>
+        <v>6964040</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8451,32 +8451,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125877297</v>
+        <v>125877242</v>
       </c>
       <c r="B82" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540874</v>
+        <v>540803</v>
       </c>
       <c r="R82" t="n">
-        <v>6964063</v>
+        <v>6964019</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -8548,32 +8548,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125877272</v>
+        <v>125877243</v>
       </c>
       <c r="B83" t="n">
-        <v>80083</v>
+        <v>99140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540806</v>
+        <v>540821</v>
       </c>
       <c r="R83" t="n">
-        <v>6964062</v>
+        <v>6964051</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -8645,32 +8645,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125877274</v>
+        <v>125877244</v>
       </c>
       <c r="B84" t="n">
-        <v>80083</v>
+        <v>99140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540794</v>
+        <v>540927</v>
       </c>
       <c r="R84" t="n">
-        <v>6964003</v>
+        <v>6964119</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -8739,6 +8739,685 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125877245</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>540964</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6964121</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>125877246</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>540789</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6964012</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>125877247</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>540780</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6963984</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>125877248</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>540726</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6963972</v>
+      </c>
+      <c r="S88" t="n">
+        <v>25</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125877290</v>
+      </c>
+      <c r="B89" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>540819</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6964057</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>125877291</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>540908</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6964094</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125877292</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stavselbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>540811</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6964057</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67343-2021 artfynd.xlsx
+++ b/artfynd/A 67343-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877252</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877306</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877307</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877309</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877310</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877311</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877312</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877314</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877315</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877316</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877317</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877318</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877319</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877320</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877322</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877323</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877324</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877326</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877330</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877332</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877335</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877366</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877232</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877341</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877344</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877347</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877350</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877354</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877357</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877258</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877259</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877260</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4169,6 +4349,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877261</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4266,6 +4451,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877262</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4363,6 +4553,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877263</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4460,6 +4655,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877264</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877265</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877266</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877267</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,6 +5063,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877268</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4945,6 +5165,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877269</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5042,6 +5267,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877270</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5139,6 +5369,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877271</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5236,6 +5471,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877272</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5333,6 +5573,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877273</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5430,6 +5675,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877274</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5527,6 +5777,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877275</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5624,6 +5879,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877276</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5721,6 +5981,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877277</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5818,6 +6083,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877278</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5915,6 +6185,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877279</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6012,6 +6287,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877280</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6109,6 +6389,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877281</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6206,6 +6491,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877282</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6303,6 +6593,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877283</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6400,6 +6695,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877284</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6497,6 +6797,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877285</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6594,6 +6899,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877287</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6696,6 +7006,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877304</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6798,6 +7113,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877305</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6895,6 +7215,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877235</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6992,6 +7317,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877236</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7089,6 +7419,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877237</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7186,6 +7521,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877238</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7283,6 +7623,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877294</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7380,6 +7725,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877295</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7477,6 +7827,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877296</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7574,6 +7929,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877297</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7671,6 +8031,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877298</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7768,6 +8133,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877299</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7865,6 +8235,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877300</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7962,6 +8337,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877301</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8059,6 +8439,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877302</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8156,6 +8541,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877303</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8253,6 +8643,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877339</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8351,6 +8746,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877240</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8448,6 +8848,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877241</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8545,6 +8950,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877242</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8642,6 +9052,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877243</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8739,6 +9154,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877244</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8836,6 +9256,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877245</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8933,6 +9358,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877246</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9030,6 +9460,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877247</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9127,6 +9562,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877248</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9224,6 +9664,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877290</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9321,6 +9766,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877291</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9418,8 +9868,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125877292</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>